--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26BD4302-6861-46A9-AB67-B3E4E9E684B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723DE9F1-DBBD-4A8A-BF20-DBF4BD060C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="38">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,99 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 18.08.2025</t>
+  </si>
+  <si>
+    <t>133708211</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>NUP Indexações 18.08.2025</t>
+  </si>
+  <si>
+    <t>133769375</t>
+  </si>
+  <si>
+    <t>129209177</t>
+  </si>
+  <si>
+    <t>133839597</t>
+  </si>
+  <si>
+    <t>133751990</t>
+  </si>
+  <si>
+    <t>133710633</t>
+  </si>
+  <si>
+    <t>129079321</t>
+  </si>
+  <si>
+    <t>133903631</t>
+  </si>
+  <si>
+    <t>133815070</t>
+  </si>
+  <si>
+    <t>133852150</t>
+  </si>
+  <si>
+    <t>129223935</t>
+  </si>
+  <si>
+    <t>130450076</t>
+  </si>
+  <si>
+    <t>133602383</t>
+  </si>
+  <si>
+    <t>129293616</t>
+  </si>
+  <si>
+    <t>133902364</t>
+  </si>
+  <si>
+    <t>133905342</t>
+  </si>
+  <si>
+    <t>131879976</t>
+  </si>
+  <si>
+    <t>133814889</t>
+  </si>
+  <si>
+    <t>133814266</t>
+  </si>
+  <si>
+    <t>132057137</t>
+  </si>
+  <si>
+    <t>133681479</t>
+  </si>
+  <si>
+    <t>132885811</t>
+  </si>
+  <si>
+    <t>133860130</t>
+  </si>
+  <si>
+    <t>133429225</t>
+  </si>
+  <si>
+    <t>133867515</t>
+  </si>
+  <si>
+    <t>133778670</t>
+  </si>
+  <si>
+    <t>133860288</t>
+  </si>
+  <si>
+    <t>133869975</t>
   </si>
 </sst>
 </file>
@@ -444,7 +537,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,7 +568,478 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723DE9F1-DBBD-4A8A-BF20-DBF4BD060C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D13EEE3-F05B-4EB9-A463-C92357A0025E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="49">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,97 +51,130 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Allianz - Cancelamento 18.08.2025</t>
-  </si>
-  <si>
-    <t>133708211</t>
-  </si>
-  <si>
     <t>1070</t>
   </si>
   <si>
-    <t>NUP Indexações 18.08.2025</t>
-  </si>
-  <si>
-    <t>133769375</t>
-  </si>
-  <si>
-    <t>129209177</t>
-  </si>
-  <si>
-    <t>133839597</t>
-  </si>
-  <si>
-    <t>133751990</t>
-  </si>
-  <si>
-    <t>133710633</t>
-  </si>
-  <si>
-    <t>129079321</t>
-  </si>
-  <si>
-    <t>133903631</t>
-  </si>
-  <si>
-    <t>133815070</t>
-  </si>
-  <si>
-    <t>133852150</t>
-  </si>
-  <si>
-    <t>129223935</t>
-  </si>
-  <si>
-    <t>130450076</t>
-  </si>
-  <si>
-    <t>133602383</t>
-  </si>
-  <si>
-    <t>129293616</t>
-  </si>
-  <si>
-    <t>133902364</t>
-  </si>
-  <si>
-    <t>133905342</t>
-  </si>
-  <si>
-    <t>131879976</t>
-  </si>
-  <si>
-    <t>133814889</t>
-  </si>
-  <si>
-    <t>133814266</t>
-  </si>
-  <si>
-    <t>132057137</t>
-  </si>
-  <si>
-    <t>133681479</t>
-  </si>
-  <si>
-    <t>132885811</t>
-  </si>
-  <si>
-    <t>133860130</t>
-  </si>
-  <si>
-    <t>133429225</t>
-  </si>
-  <si>
-    <t>133867515</t>
-  </si>
-  <si>
-    <t>133778670</t>
-  </si>
-  <si>
     <t>133860288</t>
   </si>
   <si>
-    <t>133869975</t>
+    <t>133925756</t>
+  </si>
+  <si>
+    <t>NUP Indexações 19.08.2025</t>
+  </si>
+  <si>
+    <t>133933627</t>
+  </si>
+  <si>
+    <t>133910065</t>
+  </si>
+  <si>
+    <t>129083492</t>
+  </si>
+  <si>
+    <t>133769613</t>
+  </si>
+  <si>
+    <t>133645038</t>
+  </si>
+  <si>
+    <t>129140112</t>
+  </si>
+  <si>
+    <t>133891318 </t>
+  </si>
+  <si>
+    <t>133859952</t>
+  </si>
+  <si>
+    <t>129195979</t>
+  </si>
+  <si>
+    <t>133745819</t>
+  </si>
+  <si>
+    <t>133860209</t>
+  </si>
+  <si>
+    <t>133745490</t>
+  </si>
+  <si>
+    <t>133709104</t>
+  </si>
+  <si>
+    <t>129123142</t>
+  </si>
+  <si>
+    <t>132747520</t>
+  </si>
+  <si>
+    <t>133972428</t>
+  </si>
+  <si>
+    <t>129188639</t>
+  </si>
+  <si>
+    <t>133972455</t>
+  </si>
+  <si>
+    <t>133911512</t>
+  </si>
+  <si>
+    <t>133901871</t>
+  </si>
+  <si>
+    <t>133860184</t>
+  </si>
+  <si>
+    <t>133927826</t>
+  </si>
+  <si>
+    <t>129245480</t>
+  </si>
+  <si>
+    <t>129287344</t>
+  </si>
+  <si>
+    <t>133530416</t>
+  </si>
+  <si>
+    <t>133794058</t>
+  </si>
+  <si>
+    <t>133991674</t>
+  </si>
+  <si>
+    <t>133881831</t>
+  </si>
+  <si>
+    <t>133934098</t>
+  </si>
+  <si>
+    <t>133882572</t>
+  </si>
+  <si>
+    <t>133934319</t>
+  </si>
+  <si>
+    <t>133972500</t>
+  </si>
+  <si>
+    <t>133820804</t>
+  </si>
+  <si>
+    <t>133745510</t>
+  </si>
+  <si>
+    <t>133569694</t>
+  </si>
+  <si>
+    <t>130385663</t>
+  </si>
+  <si>
+    <t>133601352</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 19.08.2025</t>
   </si>
 </sst>
 </file>
@@ -537,7 +570,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -569,16 +602,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -589,13 +622,13 @@
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -606,13 +639,13 @@
         <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -623,13 +656,13 @@
         <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -640,13 +673,13 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -657,13 +690,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -671,16 +704,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -688,16 +721,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -705,16 +738,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -722,16 +755,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -739,16 +772,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -756,16 +789,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -773,16 +806,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -790,16 +823,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -807,16 +840,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -824,16 +857,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -841,16 +874,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -858,16 +891,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -875,16 +908,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -892,16 +925,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -909,16 +942,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -926,16 +959,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -943,16 +976,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -960,16 +993,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -977,16 +1010,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -994,16 +1027,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1011,16 +1044,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1028,18 +1061,205 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D13EEE3-F05B-4EB9-A463-C92357A0025E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D99EC2A-B12D-4A6D-B4D4-B456ADE48A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="55">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,127 +54,145 @@
     <t>1070</t>
   </si>
   <si>
-    <t>133860288</t>
-  </si>
-  <si>
-    <t>133925756</t>
-  </si>
-  <si>
-    <t>NUP Indexações 19.08.2025</t>
-  </si>
-  <si>
-    <t>133933627</t>
-  </si>
-  <si>
-    <t>133910065</t>
-  </si>
-  <si>
-    <t>129083492</t>
-  </si>
-  <si>
-    <t>133769613</t>
-  </si>
-  <si>
-    <t>133645038</t>
-  </si>
-  <si>
-    <t>129140112</t>
-  </si>
-  <si>
-    <t>133891318 </t>
-  </si>
-  <si>
-    <t>133859952</t>
-  </si>
-  <si>
-    <t>129195979</t>
-  </si>
-  <si>
-    <t>133745819</t>
-  </si>
-  <si>
-    <t>133860209</t>
-  </si>
-  <si>
-    <t>133745490</t>
-  </si>
-  <si>
-    <t>133709104</t>
-  </si>
-  <si>
-    <t>129123142</t>
-  </si>
-  <si>
-    <t>132747520</t>
-  </si>
-  <si>
-    <t>133972428</t>
-  </si>
-  <si>
-    <t>129188639</t>
-  </si>
-  <si>
-    <t>133972455</t>
-  </si>
-  <si>
-    <t>133911512</t>
-  </si>
-  <si>
-    <t>133901871</t>
-  </si>
-  <si>
-    <t>133860184</t>
-  </si>
-  <si>
-    <t>133927826</t>
-  </si>
-  <si>
-    <t>129245480</t>
-  </si>
-  <si>
-    <t>129287344</t>
-  </si>
-  <si>
-    <t>133530416</t>
-  </si>
-  <si>
-    <t>133794058</t>
-  </si>
-  <si>
-    <t>133991674</t>
-  </si>
-  <si>
-    <t>133881831</t>
-  </si>
-  <si>
     <t>133934098</t>
   </si>
   <si>
-    <t>133882572</t>
-  </si>
-  <si>
-    <t>133934319</t>
-  </si>
-  <si>
-    <t>133972500</t>
-  </si>
-  <si>
-    <t>133820804</t>
-  </si>
-  <si>
-    <t>133745510</t>
-  </si>
-  <si>
-    <t>133569694</t>
-  </si>
-  <si>
-    <t>130385663</t>
-  </si>
-  <si>
-    <t>133601352</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 19.08.2025</t>
+    <t>Allianz - Cancelamento 20.08.2025</t>
+  </si>
+  <si>
+    <t>NUP Indexações 20.08.2025</t>
+  </si>
+  <si>
+    <t>133795444</t>
+  </si>
+  <si>
+    <t>128971306</t>
+  </si>
+  <si>
+    <t>133934604</t>
+  </si>
+  <si>
+    <t>133751477</t>
+  </si>
+  <si>
+    <t>133818903</t>
+  </si>
+  <si>
+    <t>133860281</t>
+  </si>
+  <si>
+    <t>133902265</t>
+  </si>
+  <si>
+    <t>133936328</t>
+  </si>
+  <si>
+    <t>133911323</t>
+  </si>
+  <si>
+    <t>133813854</t>
+  </si>
+  <si>
+    <t>133784698</t>
+  </si>
+  <si>
+    <t>129273257</t>
+  </si>
+  <si>
+    <t>129351160</t>
+  </si>
+  <si>
+    <t>129142522</t>
+  </si>
+  <si>
+    <t>129009408</t>
+  </si>
+  <si>
+    <t>133972521</t>
+  </si>
+  <si>
+    <t>129450789</t>
+  </si>
+  <si>
+    <t>133925706</t>
+  </si>
+  <si>
+    <t>133908615</t>
+  </si>
+  <si>
+    <t>134005144</t>
+  </si>
+  <si>
+    <t>134018694</t>
+  </si>
+  <si>
+    <t>133932357</t>
+  </si>
+  <si>
+    <t>133931404</t>
+  </si>
+  <si>
+    <t>129114989</t>
+  </si>
+  <si>
+    <t>133972355</t>
+  </si>
+  <si>
+    <t>133753905</t>
+  </si>
+  <si>
+    <t>133972419</t>
+  </si>
+  <si>
+    <t>133791450</t>
+  </si>
+  <si>
+    <t>133972570</t>
+  </si>
+  <si>
+    <t>133814486</t>
+  </si>
+  <si>
+    <t>133927348</t>
+  </si>
+  <si>
+    <t>133972245</t>
+  </si>
+  <si>
+    <t>133926582</t>
+  </si>
+  <si>
+    <t>129092821</t>
+  </si>
+  <si>
+    <t>129207194</t>
+  </si>
+  <si>
+    <t>133814864</t>
+  </si>
+  <si>
+    <t>133972404</t>
+  </si>
+  <si>
+    <t>133908635</t>
+  </si>
+  <si>
+    <t>128996851</t>
+  </si>
+  <si>
+    <t>129158363</t>
+  </si>
+  <si>
+    <t>133672236</t>
+  </si>
+  <si>
+    <t>133931199</t>
+  </si>
+  <si>
+    <t>129256708</t>
+  </si>
+  <si>
+    <t>133918776</t>
   </si>
 </sst>
 </file>
@@ -570,7 +588,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -602,7 +620,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -611,7 +629,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -619,7 +637,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
@@ -628,7 +646,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -636,7 +654,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -645,7 +663,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -653,7 +671,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
@@ -662,7 +680,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -670,7 +688,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
@@ -679,7 +697,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -687,7 +705,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
@@ -696,7 +714,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -704,7 +722,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
@@ -713,7 +731,7 @@
         <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -721,7 +739,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
@@ -730,7 +748,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -738,7 +756,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
@@ -747,7 +765,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -755,7 +773,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
@@ -764,7 +782,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -772,7 +790,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
@@ -781,7 +799,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -789,7 +807,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
@@ -798,7 +816,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -806,7 +824,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
@@ -815,7 +833,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -823,7 +841,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
@@ -832,7 +850,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -840,7 +858,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
@@ -849,7 +867,7 @@
         <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -857,7 +875,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
@@ -866,7 +884,7 @@
         <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -874,7 +892,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
@@ -883,7 +901,7 @@
         <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -891,7 +909,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
@@ -900,7 +918,7 @@
         <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -908,7 +926,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
@@ -917,7 +935,7 @@
         <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -925,7 +943,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
@@ -934,7 +952,7 @@
         <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -942,7 +960,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
@@ -951,7 +969,7 @@
         <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -959,7 +977,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
@@ -968,7 +986,7 @@
         <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -976,7 +994,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
@@ -985,7 +1003,7 @@
         <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -993,7 +1011,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
@@ -1002,7 +1020,7 @@
         <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1010,7 +1028,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
@@ -1019,7 +1037,7 @@
         <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1027,7 +1045,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
@@ -1036,7 +1054,7 @@
         <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1044,7 +1062,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
@@ -1053,7 +1071,7 @@
         <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1061,7 +1079,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
@@ -1070,7 +1088,7 @@
         <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1078,7 +1096,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
@@ -1087,7 +1105,7 @@
         <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1095,7 +1113,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
@@ -1104,7 +1122,7 @@
         <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1112,7 +1130,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
@@ -1121,7 +1139,7 @@
         <v>10</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1129,7 +1147,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
@@ -1138,7 +1156,7 @@
         <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1146,7 +1164,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
@@ -1155,7 +1173,7 @@
         <v>10</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1163,7 +1181,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
@@ -1172,7 +1190,7 @@
         <v>10</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1180,7 +1198,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
@@ -1189,7 +1207,7 @@
         <v>10</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1197,7 +1215,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
@@ -1206,7 +1224,7 @@
         <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1214,7 +1232,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
@@ -1223,7 +1241,7 @@
         <v>10</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1231,7 +1249,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
@@ -1240,7 +1258,7 @@
         <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1248,7 +1266,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
@@ -1257,9 +1275,111 @@
         <v>10</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D99EC2A-B12D-4A6D-B4D4-B456ADE48A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AA6990-471C-47F8-8C0E-9CD82756CE18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="51">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,15 +54,6 @@
     <t>1070</t>
   </si>
   <si>
-    <t>133934098</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 20.08.2025</t>
-  </si>
-  <si>
-    <t>NUP Indexações 20.08.2025</t>
-  </si>
-  <si>
     <t>133795444</t>
   </si>
   <si>
@@ -81,118 +72,115 @@
     <t>133860281</t>
   </si>
   <si>
-    <t>133902265</t>
-  </si>
-  <si>
-    <t>133936328</t>
-  </si>
-  <si>
-    <t>133911323</t>
-  </si>
-  <si>
-    <t>133813854</t>
-  </si>
-  <si>
-    <t>133784698</t>
-  </si>
-  <si>
-    <t>129273257</t>
-  </si>
-  <si>
-    <t>129351160</t>
-  </si>
-  <si>
-    <t>129142522</t>
-  </si>
-  <si>
-    <t>129009408</t>
-  </si>
-  <si>
-    <t>133972521</t>
-  </si>
-  <si>
-    <t>129450789</t>
-  </si>
-  <si>
-    <t>133925706</t>
-  </si>
-  <si>
-    <t>133908615</t>
-  </si>
-  <si>
-    <t>134005144</t>
-  </si>
-  <si>
-    <t>134018694</t>
-  </si>
-  <si>
-    <t>133932357</t>
-  </si>
-  <si>
-    <t>133931404</t>
-  </si>
-  <si>
-    <t>129114989</t>
-  </si>
-  <si>
     <t>133972355</t>
   </si>
   <si>
-    <t>133753905</t>
-  </si>
-  <si>
-    <t>133972419</t>
-  </si>
-  <si>
-    <t>133791450</t>
-  </si>
-  <si>
-    <t>133972570</t>
-  </si>
-  <si>
-    <t>133814486</t>
-  </si>
-  <si>
-    <t>133927348</t>
-  </si>
-  <si>
-    <t>133972245</t>
-  </si>
-  <si>
-    <t>133926582</t>
-  </si>
-  <si>
-    <t>129092821</t>
-  </si>
-  <si>
-    <t>129207194</t>
-  </si>
-  <si>
-    <t>133814864</t>
-  </si>
-  <si>
-    <t>133972404</t>
-  </si>
-  <si>
-    <t>133908635</t>
-  </si>
-  <si>
-    <t>128996851</t>
-  </si>
-  <si>
-    <t>129158363</t>
-  </si>
-  <si>
-    <t>133672236</t>
-  </si>
-  <si>
-    <t>133931199</t>
-  </si>
-  <si>
-    <t>129256708</t>
-  </si>
-  <si>
-    <t>133918776</t>
+    <t>Allianz - Cancelamento 21.08.2025</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 21.08.2025</t>
+  </si>
+  <si>
+    <t>134048216</t>
+  </si>
+  <si>
+    <t>133762102</t>
+  </si>
+  <si>
+    <t>133819620</t>
+  </si>
+  <si>
+    <t>129301283</t>
+  </si>
+  <si>
+    <t>133925874</t>
+  </si>
+  <si>
+    <t>133995171</t>
+  </si>
+  <si>
+    <t>133972454</t>
+  </si>
+  <si>
+    <t>133323588</t>
+  </si>
+  <si>
+    <t>134044251</t>
+  </si>
+  <si>
+    <t>133769742</t>
+  </si>
+  <si>
+    <t>129229319</t>
+  </si>
+  <si>
+    <t>133712803</t>
+  </si>
+  <si>
+    <t>133972655</t>
+  </si>
+  <si>
+    <t>129140501</t>
+  </si>
+  <si>
+    <t>133972220</t>
+  </si>
+  <si>
+    <t>133987523</t>
+  </si>
+  <si>
+    <t>129017135</t>
+  </si>
+  <si>
+    <t>133769677</t>
+  </si>
+  <si>
+    <t>133973908</t>
+  </si>
+  <si>
+    <t>133604331</t>
+  </si>
+  <si>
+    <t>133813799</t>
+  </si>
+  <si>
+    <t>133860138</t>
+  </si>
+  <si>
+    <t>129232860</t>
+  </si>
+  <si>
+    <t>133994234</t>
+  </si>
+  <si>
+    <t>133860086</t>
+  </si>
+  <si>
+    <t>133713450</t>
+  </si>
+  <si>
+    <t>129334408</t>
+  </si>
+  <si>
+    <t>133816009</t>
+  </si>
+  <si>
+    <t>133903659</t>
+  </si>
+  <si>
+    <t>133428057</t>
+  </si>
+  <si>
+    <t>133988082</t>
+  </si>
+  <si>
+    <t>133998849</t>
+  </si>
+  <si>
+    <t>134013696</t>
+  </si>
+  <si>
+    <t>133791424</t>
   </si>
 </sst>
 </file>
@@ -588,7 +576,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -620,16 +608,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -637,16 +625,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -654,16 +642,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -671,16 +659,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -688,16 +676,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -705,16 +693,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -728,10 +716,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -745,10 +733,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -762,10 +750,10 @@
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -779,10 +767,10 @@
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -796,10 +784,10 @@
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -813,10 +801,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -830,10 +818,10 @@
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -847,10 +835,10 @@
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -864,10 +852,10 @@
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -881,10 +869,10 @@
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -898,10 +886,10 @@
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -915,10 +903,10 @@
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -932,10 +920,10 @@
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -949,10 +937,10 @@
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -960,16 +948,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -977,16 +965,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -994,16 +982,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1011,16 +999,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1028,16 +1016,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1045,16 +1033,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1062,16 +1050,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1079,16 +1067,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1096,16 +1084,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1113,16 +1101,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1130,16 +1118,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1147,16 +1135,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1164,16 +1152,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1181,16 +1169,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1198,16 +1186,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1215,16 +1203,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1232,16 +1220,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1249,16 +1237,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1266,16 +1254,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1283,16 +1271,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1300,16 +1288,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1317,69 +1305,18 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AA6990-471C-47F8-8C0E-9CD82756CE18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81346089-381A-44D0-8D9F-7EB13977F829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="72">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,136 +51,199 @@
     <t>Processar</t>
   </si>
   <si>
+    <t>133791434</t>
+  </si>
+  <si>
     <t>1070</t>
   </si>
   <si>
-    <t>133795444</t>
-  </si>
-  <si>
-    <t>128971306</t>
-  </si>
-  <si>
-    <t>133934604</t>
-  </si>
-  <si>
-    <t>133751477</t>
-  </si>
-  <si>
-    <t>133818903</t>
-  </si>
-  <si>
-    <t>133860281</t>
-  </si>
-  <si>
-    <t>133972355</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 21.08.2025</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 21.08.2025</t>
-  </si>
-  <si>
-    <t>134048216</t>
-  </si>
-  <si>
-    <t>133762102</t>
-  </si>
-  <si>
-    <t>133819620</t>
-  </si>
-  <si>
-    <t>129301283</t>
-  </si>
-  <si>
-    <t>133925874</t>
-  </si>
-  <si>
-    <t>133995171</t>
-  </si>
-  <si>
-    <t>133972454</t>
-  </si>
-  <si>
-    <t>133323588</t>
-  </si>
-  <si>
-    <t>134044251</t>
-  </si>
-  <si>
-    <t>133769742</t>
-  </si>
-  <si>
-    <t>129229319</t>
-  </si>
-  <si>
-    <t>133712803</t>
-  </si>
-  <si>
-    <t>133972655</t>
-  </si>
-  <si>
-    <t>129140501</t>
-  </si>
-  <si>
-    <t>133972220</t>
-  </si>
-  <si>
-    <t>133987523</t>
-  </si>
-  <si>
-    <t>129017135</t>
-  </si>
-  <si>
-    <t>133769677</t>
-  </si>
-  <si>
-    <t>133973908</t>
-  </si>
-  <si>
-    <t>133604331</t>
-  </si>
-  <si>
-    <t>133813799</t>
-  </si>
-  <si>
-    <t>133860138</t>
-  </si>
-  <si>
-    <t>129232860</t>
-  </si>
-  <si>
-    <t>133994234</t>
-  </si>
-  <si>
-    <t>133860086</t>
-  </si>
-  <si>
-    <t>133713450</t>
-  </si>
-  <si>
-    <t>129334408</t>
-  </si>
-  <si>
-    <t>133816009</t>
-  </si>
-  <si>
-    <t>133903659</t>
-  </si>
-  <si>
-    <t>133428057</t>
-  </si>
-  <si>
-    <t>133988082</t>
-  </si>
-  <si>
-    <t>133998849</t>
-  </si>
-  <si>
-    <t>134013696</t>
+    <t>NUP indexações 22.08.2025</t>
+  </si>
+  <si>
+    <t>134057618</t>
+  </si>
+  <si>
+    <t>133972449</t>
+  </si>
+  <si>
+    <t>133926626</t>
+  </si>
+  <si>
+    <t>133682511</t>
+  </si>
+  <si>
+    <t>133972590</t>
+  </si>
+  <si>
+    <t>133972335</t>
+  </si>
+  <si>
+    <t>133866698</t>
+  </si>
+  <si>
+    <t>133813997</t>
+  </si>
+  <si>
+    <t>133926028</t>
+  </si>
+  <si>
+    <t>133998773</t>
+  </si>
+  <si>
+    <t>134051881</t>
+  </si>
+  <si>
+    <t>133935295</t>
+  </si>
+  <si>
+    <t>133860058</t>
+  </si>
+  <si>
+    <t>134013590</t>
+  </si>
+  <si>
+    <t>133662933</t>
+  </si>
+  <si>
+    <t>133791805</t>
+  </si>
+  <si>
+    <t>133973340</t>
+  </si>
+  <si>
+    <t>133958216</t>
+  </si>
+  <si>
+    <t>133770514</t>
+  </si>
+  <si>
+    <t>133745557</t>
+  </si>
+  <si>
+    <t>133972534</t>
+  </si>
+  <si>
+    <t>133778077</t>
+  </si>
+  <si>
+    <t>129383317</t>
+  </si>
+  <si>
+    <t>129198775</t>
+  </si>
+  <si>
+    <t>129246052</t>
+  </si>
+  <si>
+    <t>129129064</t>
   </si>
   <si>
     <t>133791424</t>
+  </si>
+  <si>
+    <t>129369370</t>
+  </si>
+  <si>
+    <t>133552109</t>
+  </si>
+  <si>
+    <t>133751517</t>
+  </si>
+  <si>
+    <t>133949785</t>
+  </si>
+  <si>
+    <t>133889080</t>
+  </si>
+  <si>
+    <t>133770779</t>
+  </si>
+  <si>
+    <t>134018506</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2025</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2026</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2027</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2028</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2029</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2030</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2031</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2032</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2033</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2034</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2035</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2036</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2037</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2038</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2039</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2040</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2041</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2042</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2043</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2044</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2045</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2046</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2047</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2048</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2049</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2050</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2051</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.08.2052</t>
   </si>
 </sst>
 </file>
@@ -576,7 +639,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -608,16 +671,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -625,16 +688,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -642,16 +705,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -659,16 +722,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -676,16 +739,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -693,16 +756,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -710,16 +773,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -727,16 +790,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -744,16 +807,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -761,16 +824,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -778,16 +841,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -795,16 +858,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -812,16 +875,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -829,16 +892,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -846,16 +909,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -863,16 +926,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -880,16 +943,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -897,16 +960,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -914,16 +977,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -931,16 +994,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -948,16 +1011,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -965,16 +1028,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -982,16 +1045,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -999,16 +1062,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1016,16 +1079,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1033,16 +1096,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1050,16 +1113,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1067,16 +1130,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1084,16 +1147,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1101,16 +1164,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1118,16 +1181,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1135,16 +1198,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1152,16 +1215,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1169,16 +1232,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1186,137 +1249,18 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E43" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81346089-381A-44D0-8D9F-7EB13977F829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A9D991-DBD1-4001-8CD8-539730716606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="80">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,199 +51,223 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>133791434</t>
-  </si>
-  <si>
     <t>1070</t>
   </si>
   <si>
-    <t>NUP indexações 22.08.2025</t>
-  </si>
-  <si>
-    <t>134057618</t>
-  </si>
-  <si>
-    <t>133972449</t>
-  </si>
-  <si>
-    <t>133926626</t>
-  </si>
-  <si>
-    <t>133682511</t>
-  </si>
-  <si>
-    <t>133972590</t>
-  </si>
-  <si>
-    <t>133972335</t>
-  </si>
-  <si>
-    <t>133866698</t>
-  </si>
-  <si>
-    <t>133813997</t>
-  </si>
-  <si>
-    <t>133926028</t>
-  </si>
-  <si>
-    <t>133998773</t>
-  </si>
-  <si>
-    <t>134051881</t>
-  </si>
-  <si>
-    <t>133935295</t>
-  </si>
-  <si>
-    <t>133860058</t>
-  </si>
-  <si>
-    <t>134013590</t>
-  </si>
-  <si>
-    <t>133662933</t>
-  </si>
-  <si>
-    <t>133791805</t>
-  </si>
-  <si>
-    <t>133973340</t>
-  </si>
-  <si>
-    <t>133958216</t>
-  </si>
-  <si>
-    <t>133770514</t>
-  </si>
-  <si>
-    <t>133745557</t>
-  </si>
-  <si>
-    <t>133972534</t>
-  </si>
-  <si>
-    <t>133778077</t>
-  </si>
-  <si>
-    <t>129383317</t>
-  </si>
-  <si>
-    <t>129198775</t>
-  </si>
-  <si>
-    <t>129246052</t>
-  </si>
-  <si>
-    <t>129129064</t>
-  </si>
-  <si>
-    <t>133791424</t>
-  </si>
-  <si>
-    <t>129369370</t>
-  </si>
-  <si>
-    <t>133552109</t>
-  </si>
-  <si>
-    <t>133751517</t>
-  </si>
-  <si>
-    <t>133949785</t>
-  </si>
-  <si>
-    <t>133889080</t>
-  </si>
-  <si>
-    <t>133770779</t>
-  </si>
-  <si>
-    <t>134018506</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2025</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2026</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2027</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2028</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2029</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2030</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2031</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2032</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2033</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2034</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2035</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2036</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2037</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2038</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2039</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2040</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2041</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2042</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2043</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2044</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2045</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2046</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2047</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2048</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2049</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2050</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2051</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.08.2052</t>
+    <t>134022454</t>
+  </si>
+  <si>
+    <t>NUP Indexações 25.08.2025</t>
+  </si>
+  <si>
+    <t>134062392</t>
+  </si>
+  <si>
+    <t>133861131</t>
+  </si>
+  <si>
+    <t>134069140</t>
+  </si>
+  <si>
+    <t>134019340</t>
+  </si>
+  <si>
+    <t>133997076</t>
+  </si>
+  <si>
+    <t>134090798</t>
+  </si>
+  <si>
+    <t>133903683</t>
+  </si>
+  <si>
+    <t>134025644</t>
+  </si>
+  <si>
+    <t>134018613</t>
+  </si>
+  <si>
+    <t>134071914</t>
+  </si>
+  <si>
+    <t>133903661</t>
+  </si>
+  <si>
+    <t>129389904</t>
+  </si>
+  <si>
+    <t>133934093</t>
+  </si>
+  <si>
+    <t>129010735</t>
+  </si>
+  <si>
+    <t>129010876</t>
+  </si>
+  <si>
+    <t>134075165</t>
+  </si>
+  <si>
+    <t>129401916</t>
+  </si>
+  <si>
+    <t>134032849</t>
+  </si>
+  <si>
+    <t>133925963</t>
+  </si>
+  <si>
+    <t>133636249</t>
+  </si>
+  <si>
+    <t>133871968</t>
+  </si>
+  <si>
+    <t>134003810</t>
+  </si>
+  <si>
+    <t>133490666</t>
+  </si>
+  <si>
+    <t>134025482</t>
+  </si>
+  <si>
+    <t>129106966</t>
+  </si>
+  <si>
+    <t>133972197</t>
+  </si>
+  <si>
+    <t>134061920</t>
+  </si>
+  <si>
+    <t>134062404</t>
+  </si>
+  <si>
+    <t>129315252</t>
+  </si>
+  <si>
+    <t>133860086</t>
+  </si>
+  <si>
+    <t>134020084</t>
+  </si>
+  <si>
+    <t>134054535</t>
+  </si>
+  <si>
+    <t>133866390</t>
+  </si>
+  <si>
+    <t>134018519</t>
+  </si>
+  <si>
+    <t>133751850</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2025</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2026</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2027</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2028</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2029</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2030</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2031</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2032</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2033</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2034</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2035</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2036</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2037</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2038</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2039</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2040</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2041</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2042</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2043</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2044</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2045</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2046</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2047</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2048</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2049</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2050</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2051</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2052</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2053</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2054</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2055</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2056</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2057</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2058</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 25..08.2059</t>
   </si>
 </sst>
 </file>
@@ -639,7 +663,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -671,16 +695,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -691,13 +715,13 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -708,13 +732,13 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -725,13 +749,13 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -742,13 +766,13 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -759,13 +783,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -776,13 +800,13 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -793,13 +817,13 @@
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -810,13 +834,13 @@
         <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -827,13 +851,13 @@
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -844,13 +868,13 @@
         <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -861,13 +885,13 @@
         <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -878,13 +902,13 @@
         <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -895,13 +919,13 @@
         <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -912,13 +936,13 @@
         <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -929,13 +953,13 @@
         <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -946,13 +970,13 @@
         <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -963,13 +987,13 @@
         <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -980,13 +1004,13 @@
         <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -997,13 +1021,13 @@
         <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1014,13 +1038,13 @@
         <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1031,13 +1055,13 @@
         <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1048,13 +1072,13 @@
         <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1065,13 +1089,13 @@
         <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1082,13 +1106,13 @@
         <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1099,13 +1123,13 @@
         <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1116,13 +1140,13 @@
         <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1133,13 +1157,13 @@
         <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1150,13 +1174,13 @@
         <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1167,13 +1191,13 @@
         <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1184,13 +1208,13 @@
         <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1201,13 +1225,13 @@
         <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1218,13 +1242,13 @@
         <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1235,13 +1259,13 @@
         <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1252,15 +1276,32 @@
         <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A9D991-DBD1-4001-8CD8-539730716606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B37696-6F55-4B2E-85AD-4CB88EA085F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="47">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -168,106 +168,7 @@
     <t>Allianz - Cancelamento 25..08.2025</t>
   </si>
   <si>
-    <t>Allianz - Cancelamento 25..08.2026</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2027</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2028</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2029</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2030</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2031</t>
-  </si>
-  <si>
     <t>Allianz - Cancelamento 25..08.2032</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2033</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2034</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2035</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2036</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2037</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2038</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2039</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2040</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2041</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2042</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2043</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2044</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2045</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2046</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2047</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2048</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2049</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2050</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2051</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2052</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2053</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2054</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2055</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2056</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2057</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2058</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2059</t>
   </si>
 </sst>
 </file>
@@ -738,7 +639,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -755,7 +656,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -772,7 +673,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -789,7 +690,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -806,7 +707,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -823,7 +724,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -840,7 +741,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -857,7 +758,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -874,7 +775,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -891,7 +792,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -908,7 +809,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -925,7 +826,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -942,7 +843,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -959,7 +860,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -976,7 +877,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -993,7 +894,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1010,7 +911,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1027,7 +928,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1044,7 +945,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1061,7 +962,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1078,7 +979,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1095,7 +996,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1112,7 +1013,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1129,7 +1030,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1146,7 +1047,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1163,7 +1064,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1180,7 +1081,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1197,7 +1098,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1214,7 +1115,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1231,7 +1132,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1248,7 +1149,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1265,7 +1166,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1282,7 +1183,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1299,7 +1200,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B37696-6F55-4B2E-85AD-4CB88EA085F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1786621D-2B6E-45A3-8C43-AAD98EB8D5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3150" yWindow="2955" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="43">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,121 +54,109 @@
     <t>1070</t>
   </si>
   <si>
-    <t>134022454</t>
-  </si>
-  <si>
-    <t>NUP Indexações 25.08.2025</t>
-  </si>
-  <si>
-    <t>134062392</t>
-  </si>
-  <si>
-    <t>133861131</t>
-  </si>
-  <si>
-    <t>134069140</t>
-  </si>
-  <si>
-    <t>134019340</t>
-  </si>
-  <si>
-    <t>133997076</t>
-  </si>
-  <si>
-    <t>134090798</t>
-  </si>
-  <si>
-    <t>133903683</t>
-  </si>
-  <si>
-    <t>134025644</t>
-  </si>
-  <si>
-    <t>134018613</t>
-  </si>
-  <si>
-    <t>134071914</t>
-  </si>
-  <si>
-    <t>133903661</t>
-  </si>
-  <si>
-    <t>129389904</t>
-  </si>
-  <si>
-    <t>133934093</t>
-  </si>
-  <si>
-    <t>129010735</t>
-  </si>
-  <si>
-    <t>129010876</t>
-  </si>
-  <si>
-    <t>134075165</t>
-  </si>
-  <si>
-    <t>129401916</t>
-  </si>
-  <si>
-    <t>134032849</t>
-  </si>
-  <si>
-    <t>133925963</t>
-  </si>
-  <si>
-    <t>133636249</t>
-  </si>
-  <si>
-    <t>133871968</t>
-  </si>
-  <si>
-    <t>134003810</t>
-  </si>
-  <si>
-    <t>133490666</t>
-  </si>
-  <si>
-    <t>134025482</t>
-  </si>
-  <si>
-    <t>129106966</t>
-  </si>
-  <si>
-    <t>133972197</t>
-  </si>
-  <si>
-    <t>134061920</t>
-  </si>
-  <si>
-    <t>134062404</t>
-  </si>
-  <si>
-    <t>129315252</t>
-  </si>
-  <si>
-    <t>133860086</t>
-  </si>
-  <si>
-    <t>134020084</t>
-  </si>
-  <si>
-    <t>134054535</t>
-  </si>
-  <si>
     <t>133866390</t>
   </si>
   <si>
     <t>134018519</t>
   </si>
   <si>
-    <t>133751850</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2025</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 25..08.2032</t>
+    <t>Allianz - Cancelamento 26..08.2025</t>
+  </si>
+  <si>
+    <t>133860926</t>
+  </si>
+  <si>
+    <t>NUP Indexações 26.08.2025</t>
+  </si>
+  <si>
+    <t>134050773</t>
+  </si>
+  <si>
+    <t>133973270</t>
+  </si>
+  <si>
+    <t>134049284</t>
+  </si>
+  <si>
+    <t>129473123</t>
+  </si>
+  <si>
+    <t>134018569</t>
+  </si>
+  <si>
+    <t>133962422</t>
+  </si>
+  <si>
+    <t>133882218</t>
+  </si>
+  <si>
+    <t>133681003</t>
+  </si>
+  <si>
+    <t>134056159</t>
+  </si>
+  <si>
+    <t>133972170</t>
+  </si>
+  <si>
+    <t>134101522</t>
+  </si>
+  <si>
+    <t>132882890</t>
+  </si>
+  <si>
+    <t>129210586</t>
+  </si>
+  <si>
+    <t>133996936</t>
+  </si>
+  <si>
+    <t>129053752</t>
+  </si>
+  <si>
+    <t>133860222</t>
+  </si>
+  <si>
+    <t>134094458</t>
+  </si>
+  <si>
+    <t>134047895</t>
+  </si>
+  <si>
+    <t>134061903</t>
+  </si>
+  <si>
+    <t>129266551</t>
+  </si>
+  <si>
+    <t>128916297</t>
+  </si>
+  <si>
+    <t>134091582</t>
+  </si>
+  <si>
+    <t>129009598</t>
+  </si>
+  <si>
+    <t>133813717</t>
+  </si>
+  <si>
+    <t>133973312</t>
+  </si>
+  <si>
+    <t>133989708</t>
+  </si>
+  <si>
+    <t>134091604</t>
+  </si>
+  <si>
+    <t>133994247</t>
+  </si>
+  <si>
+    <t>133839364</t>
+  </si>
+  <si>
+    <t>133813678</t>
   </si>
 </sst>
 </file>
@@ -564,7 +552,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -596,16 +584,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -613,16 +601,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -630,16 +618,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -647,16 +635,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -664,16 +652,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -681,16 +669,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -698,16 +686,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -715,16 +703,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -732,16 +720,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -749,16 +737,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -766,16 +754,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -783,16 +771,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -800,16 +788,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -817,16 +805,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -834,16 +822,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -851,16 +839,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -868,16 +856,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -885,16 +873,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -902,16 +890,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -919,16 +907,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -936,16 +924,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -953,16 +941,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -970,16 +958,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -987,16 +975,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1004,16 +992,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1021,16 +1009,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1038,16 +1026,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1055,16 +1043,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1072,16 +1060,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1089,16 +1077,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1106,16 +1094,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1123,16 +1111,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1140,69 +1128,18 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E37" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1786621D-2B6E-45A3-8C43-AAD98EB8D5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4181783-550B-44C6-B708-4DFA0A7AE636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3150" yWindow="2955" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="87">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,109 +54,241 @@
     <t>1070</t>
   </si>
   <si>
-    <t>133866390</t>
-  </si>
-  <si>
-    <t>134018519</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 26..08.2025</t>
-  </si>
-  <si>
-    <t>133860926</t>
-  </si>
-  <si>
-    <t>NUP Indexações 26.08.2025</t>
-  </si>
-  <si>
-    <t>134050773</t>
-  </si>
-  <si>
-    <t>133973270</t>
-  </si>
-  <si>
-    <t>134049284</t>
-  </si>
-  <si>
-    <t>129473123</t>
-  </si>
-  <si>
-    <t>134018569</t>
-  </si>
-  <si>
-    <t>133962422</t>
-  </si>
-  <si>
-    <t>133882218</t>
-  </si>
-  <si>
-    <t>133681003</t>
-  </si>
-  <si>
-    <t>134056159</t>
-  </si>
-  <si>
-    <t>133972170</t>
-  </si>
-  <si>
-    <t>134101522</t>
-  </si>
-  <si>
-    <t>132882890</t>
-  </si>
-  <si>
-    <t>129210586</t>
-  </si>
-  <si>
-    <t>133996936</t>
-  </si>
-  <si>
-    <t>129053752</t>
-  </si>
-  <si>
-    <t>133860222</t>
-  </si>
-  <si>
-    <t>134094458</t>
-  </si>
-  <si>
-    <t>134047895</t>
-  </si>
-  <si>
-    <t>134061903</t>
-  </si>
-  <si>
-    <t>129266551</t>
-  </si>
-  <si>
-    <t>128916297</t>
-  </si>
-  <si>
-    <t>134091582</t>
-  </si>
-  <si>
-    <t>129009598</t>
-  </si>
-  <si>
-    <t>133813717</t>
-  </si>
-  <si>
-    <t>133973312</t>
-  </si>
-  <si>
-    <t>133989708</t>
-  </si>
-  <si>
-    <t>134091604</t>
-  </si>
-  <si>
-    <t>133994247</t>
-  </si>
-  <si>
-    <t>133839364</t>
-  </si>
-  <si>
-    <t>133813678</t>
+    <t>133860269</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 27.08.2025</t>
+  </si>
+  <si>
+    <t>133860234</t>
+  </si>
+  <si>
+    <t>133705899</t>
+  </si>
+  <si>
+    <t>133904187</t>
+  </si>
+  <si>
+    <t>133994593</t>
+  </si>
+  <si>
+    <t>129427799</t>
+  </si>
+  <si>
+    <t>133932786</t>
+  </si>
+  <si>
+    <t>129099507</t>
+  </si>
+  <si>
+    <t>133932933</t>
+  </si>
+  <si>
+    <t>133882448</t>
+  </si>
+  <si>
+    <t>134120044</t>
+  </si>
+  <si>
+    <t>133860841</t>
+  </si>
+  <si>
+    <t>134097859</t>
+  </si>
+  <si>
+    <t>129244096</t>
+  </si>
+  <si>
+    <t>134050099</t>
+  </si>
+  <si>
+    <t>133859997</t>
+  </si>
+  <si>
+    <t>134018597</t>
+  </si>
+  <si>
+    <t>134003629</t>
+  </si>
+  <si>
+    <t>129197376</t>
+  </si>
+  <si>
+    <t>133641267</t>
+  </si>
+  <si>
+    <t>134106242</t>
+  </si>
+  <si>
+    <t>133968156</t>
+  </si>
+  <si>
+    <t>129402314</t>
+  </si>
+  <si>
+    <t>134061544</t>
+  </si>
+  <si>
+    <t>129114812</t>
+  </si>
+  <si>
+    <t>134095512</t>
+  </si>
+  <si>
+    <t>129386725</t>
+  </si>
+  <si>
+    <t>134010523</t>
+  </si>
+  <si>
+    <t>133860080</t>
+  </si>
+  <si>
+    <t>134018830</t>
+  </si>
+  <si>
+    <t>133979860</t>
+  </si>
+  <si>
+    <t>129223336</t>
+  </si>
+  <si>
+    <t>134103149</t>
+  </si>
+  <si>
+    <t>133972252</t>
+  </si>
+  <si>
+    <t>134120327</t>
+  </si>
+  <si>
+    <t>133773684</t>
+  </si>
+  <si>
+    <t>133869064</t>
+  </si>
+  <si>
+    <t>134123005</t>
+  </si>
+  <si>
+    <t>133450281</t>
+  </si>
+  <si>
+    <t>134030410</t>
+  </si>
+  <si>
+    <t>133994576</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2025</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2026</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2027</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2028</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2029</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2030</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2031</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2032</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2033</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2034</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2035</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2036</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2037</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2038</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2039</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2040</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2041</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2042</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2043</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2044</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2045</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2046</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2047</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2048</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2049</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2050</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2051</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2052</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2053</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2054</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2055</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2056</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2057</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2058</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2059</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2060</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.08.2061</t>
   </si>
 </sst>
 </file>
@@ -552,7 +684,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -584,16 +716,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -601,16 +733,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -618,16 +750,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -635,16 +767,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -652,16 +784,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -669,16 +801,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -686,16 +818,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -703,16 +835,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -720,16 +852,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -737,16 +869,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -754,16 +886,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -771,16 +903,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -788,16 +920,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -805,16 +937,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -822,16 +954,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -839,16 +971,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -856,16 +988,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -873,16 +1005,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -890,16 +1022,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -907,16 +1039,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -924,16 +1056,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -941,16 +1073,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -958,16 +1090,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -975,16 +1107,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -992,16 +1124,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1009,16 +1141,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1026,16 +1158,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1043,16 +1175,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1060,16 +1192,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1077,16 +1209,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1094,16 +1226,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1111,16 +1243,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1128,18 +1260,171 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" s="2" t="s">
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4181783-550B-44C6-B708-4DFA0A7AE636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B7CF7B-B44A-4DFF-8571-8B40B0C9EB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="2955" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="51">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -181,114 +181,6 @@
   </si>
   <si>
     <t>Allianz - Cancelamento 27.08.2025</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2026</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2027</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2028</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2029</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2030</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2031</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2032</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2033</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2034</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2035</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2036</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2037</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2038</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2039</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2040</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2041</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2042</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2043</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2044</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2045</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2046</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2047</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2048</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2049</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2050</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2051</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2052</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2053</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2054</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2055</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2056</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2057</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2058</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2059</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2060</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 27.08.2061</t>
   </si>
 </sst>
 </file>
@@ -827,7 +719,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -844,7 +736,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -861,7 +753,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -878,7 +770,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -895,7 +787,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -912,7 +804,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -929,7 +821,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -946,7 +838,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -963,7 +855,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -980,7 +872,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -997,7 +889,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1014,7 +906,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1031,7 +923,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1048,7 +940,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1065,7 +957,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1082,7 +974,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1099,7 +991,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1116,7 +1008,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1133,7 +1025,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1150,7 +1042,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1167,7 +1059,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1184,7 +1076,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1201,7 +1093,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1218,7 +1110,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1235,7 +1127,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1252,7 +1144,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1269,7 +1161,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1286,7 +1178,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1303,7 +1195,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1320,7 +1212,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1337,7 +1229,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1354,7 +1246,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1371,7 +1263,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1388,7 +1280,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1405,7 +1297,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1422,7 +1314,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B7CF7B-B44A-4DFF-8571-8B40B0C9EB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D3AA75-B9C4-48AF-B8B3-005DEF3473D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="39">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,133 +54,97 @@
     <t>1070</t>
   </si>
   <si>
-    <t>133860269</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 27.08.2025</t>
-  </si>
-  <si>
-    <t>133860234</t>
-  </si>
-  <si>
-    <t>133705899</t>
-  </si>
-  <si>
-    <t>133904187</t>
-  </si>
-  <si>
-    <t>133994593</t>
-  </si>
-  <si>
-    <t>129427799</t>
-  </si>
-  <si>
-    <t>133932786</t>
-  </si>
-  <si>
-    <t>129099507</t>
-  </si>
-  <si>
-    <t>133932933</t>
-  </si>
-  <si>
-    <t>133882448</t>
-  </si>
-  <si>
-    <t>134120044</t>
-  </si>
-  <si>
-    <t>133860841</t>
-  </si>
-  <si>
-    <t>134097859</t>
-  </si>
-  <si>
-    <t>129244096</t>
-  </si>
-  <si>
-    <t>134050099</t>
-  </si>
-  <si>
-    <t>133859997</t>
-  </si>
-  <si>
-    <t>134018597</t>
-  </si>
-  <si>
-    <t>134003629</t>
-  </si>
-  <si>
-    <t>129197376</t>
-  </si>
-  <si>
-    <t>133641267</t>
-  </si>
-  <si>
-    <t>134106242</t>
-  </si>
-  <si>
-    <t>133968156</t>
-  </si>
-  <si>
-    <t>129402314</t>
-  </si>
-  <si>
-    <t>134061544</t>
-  </si>
-  <si>
-    <t>129114812</t>
-  </si>
-  <si>
-    <t>134095512</t>
-  </si>
-  <si>
-    <t>129386725</t>
-  </si>
-  <si>
-    <t>134010523</t>
-  </si>
-  <si>
-    <t>133860080</t>
-  </si>
-  <si>
-    <t>134018830</t>
-  </si>
-  <si>
-    <t>133979860</t>
-  </si>
-  <si>
-    <t>129223336</t>
-  </si>
-  <si>
-    <t>134103149</t>
-  </si>
-  <si>
-    <t>133972252</t>
-  </si>
-  <si>
-    <t>134120327</t>
-  </si>
-  <si>
-    <t>133773684</t>
-  </si>
-  <si>
-    <t>133869064</t>
-  </si>
-  <si>
-    <t>134123005</t>
-  </si>
-  <si>
-    <t>133450281</t>
-  </si>
-  <si>
-    <t>134030410</t>
-  </si>
-  <si>
     <t>133994576</t>
   </si>
   <si>
-    <t>Allianz - Cancelamento 27.08.2025</t>
+    <t>Allianz - Cancelamento 28.08.2025</t>
+  </si>
+  <si>
+    <t>134115750</t>
+  </si>
+  <si>
+    <t>NUP Indexações 28.08.2025</t>
+  </si>
+  <si>
+    <t>133933119</t>
+  </si>
+  <si>
+    <t>134053950</t>
+  </si>
+  <si>
+    <t>133905172</t>
+  </si>
+  <si>
+    <t>133869543</t>
+  </si>
+  <si>
+    <t>134051637</t>
+  </si>
+  <si>
+    <t>133897449</t>
+  </si>
+  <si>
+    <t>133523110</t>
+  </si>
+  <si>
+    <t>133754131</t>
+  </si>
+  <si>
+    <t>133860834</t>
+  </si>
+  <si>
+    <t>133881596</t>
+  </si>
+  <si>
+    <t>133972342</t>
+  </si>
+  <si>
+    <t>134094261</t>
+  </si>
+  <si>
+    <t>134091483</t>
+  </si>
+  <si>
+    <t>133926922</t>
+  </si>
+  <si>
+    <t>134027888</t>
+  </si>
+  <si>
+    <t>133994314</t>
+  </si>
+  <si>
+    <t>133867201</t>
+  </si>
+  <si>
+    <t>133980717</t>
+  </si>
+  <si>
+    <t>134137582</t>
+  </si>
+  <si>
+    <t>134062375</t>
+  </si>
+  <si>
+    <t>133972400</t>
+  </si>
+  <si>
+    <t>133793467</t>
+  </si>
+  <si>
+    <t>129320577</t>
+  </si>
+  <si>
+    <t>133977116</t>
+  </si>
+  <si>
+    <t>134007985</t>
+  </si>
+  <si>
+    <t>133867415</t>
+  </si>
+  <si>
+    <t>129849582</t>
   </si>
 </sst>
 </file>
@@ -576,7 +540,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -608,16 +572,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -625,16 +589,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -642,16 +606,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -659,16 +623,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -676,16 +640,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -693,16 +657,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -710,16 +674,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -727,16 +691,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -744,16 +708,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -761,16 +725,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -778,16 +742,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -795,16 +759,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -812,16 +776,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -829,16 +793,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -846,16 +810,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -863,16 +827,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -880,16 +844,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -897,16 +861,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -914,16 +878,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -931,16 +895,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -948,16 +912,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -965,16 +929,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -982,16 +946,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -999,16 +963,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1016,16 +980,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1033,16 +997,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1050,16 +1014,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1067,16 +1031,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1084,239 +1048,18 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E43" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D3AA75-B9C4-48AF-B8B3-005DEF3473D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924BB60B-AB6F-42EE-B2E9-5ACCE4741D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="50">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,97 +54,130 @@
     <t>1070</t>
   </si>
   <si>
-    <t>133994576</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 28.08.2025</t>
-  </si>
-  <si>
-    <t>134115750</t>
-  </si>
-  <si>
-    <t>NUP Indexações 28.08.2025</t>
-  </si>
-  <si>
-    <t>133933119</t>
-  </si>
-  <si>
-    <t>134053950</t>
-  </si>
-  <si>
-    <t>133905172</t>
-  </si>
-  <si>
-    <t>133869543</t>
-  </si>
-  <si>
-    <t>134051637</t>
-  </si>
-  <si>
-    <t>133897449</t>
-  </si>
-  <si>
-    <t>133523110</t>
-  </si>
-  <si>
-    <t>133754131</t>
-  </si>
-  <si>
-    <t>133860834</t>
-  </si>
-  <si>
-    <t>133881596</t>
-  </si>
-  <si>
-    <t>133972342</t>
-  </si>
-  <si>
-    <t>134094261</t>
-  </si>
-  <si>
-    <t>134091483</t>
-  </si>
-  <si>
-    <t>133926922</t>
-  </si>
-  <si>
-    <t>134027888</t>
-  </si>
-  <si>
-    <t>133994314</t>
-  </si>
-  <si>
-    <t>133867201</t>
-  </si>
-  <si>
-    <t>133980717</t>
-  </si>
-  <si>
-    <t>134137582</t>
-  </si>
-  <si>
-    <t>134062375</t>
-  </si>
-  <si>
-    <t>133972400</t>
-  </si>
-  <si>
-    <t>133793467</t>
-  </si>
-  <si>
-    <t>129320577</t>
-  </si>
-  <si>
-    <t>133977116</t>
-  </si>
-  <si>
-    <t>134007985</t>
-  </si>
-  <si>
-    <t>133867415</t>
-  </si>
-  <si>
-    <t>129849582</t>
+    <t>134133747</t>
+  </si>
+  <si>
+    <t>NUP Indexações 29.08.2025</t>
+  </si>
+  <si>
+    <t>129141430</t>
+  </si>
+  <si>
+    <t>134102658</t>
+  </si>
+  <si>
+    <t>129427531</t>
+  </si>
+  <si>
+    <t>133934952</t>
+  </si>
+  <si>
+    <t>134186185</t>
+  </si>
+  <si>
+    <t>134096322</t>
+  </si>
+  <si>
+    <t>129034486</t>
+  </si>
+  <si>
+    <t>133533785</t>
+  </si>
+  <si>
+    <t>134118378</t>
+  </si>
+  <si>
+    <t>129510878</t>
+  </si>
+  <si>
+    <t>133979571</t>
+  </si>
+  <si>
+    <t>129393181</t>
+  </si>
+  <si>
+    <t>133925708</t>
+  </si>
+  <si>
+    <t>134099220</t>
+  </si>
+  <si>
+    <t>132975015</t>
+  </si>
+  <si>
+    <t>133930942</t>
+  </si>
+  <si>
+    <t>134138449</t>
+  </si>
+  <si>
+    <t>134175235</t>
+  </si>
+  <si>
+    <t>134139570</t>
+  </si>
+  <si>
+    <t>134143698</t>
+  </si>
+  <si>
+    <t>133972473</t>
+  </si>
+  <si>
+    <t>134163283</t>
+  </si>
+  <si>
+    <t>134169985</t>
+  </si>
+  <si>
+    <t>133936182</t>
+  </si>
+  <si>
+    <t>133972516</t>
+  </si>
+  <si>
+    <t>134123685</t>
+  </si>
+  <si>
+    <t>129276671</t>
+  </si>
+  <si>
+    <t>134053756</t>
+  </si>
+  <si>
+    <t>129475072</t>
+  </si>
+  <si>
+    <t>129068308</t>
+  </si>
+  <si>
+    <t>133972238</t>
+  </si>
+  <si>
+    <t>129209548</t>
+  </si>
+  <si>
+    <t>134141563</t>
+  </si>
+  <si>
+    <t>134122905</t>
+  </si>
+  <si>
+    <t>134193140</t>
+  </si>
+  <si>
+    <t>132412853</t>
+  </si>
+  <si>
+    <t>134133670</t>
+  </si>
+  <si>
+    <t>133926272</t>
+  </si>
+  <si>
+    <t>133599159</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 29.08.2025 (2)</t>
   </si>
 </sst>
 </file>
@@ -540,7 +573,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -572,16 +605,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -589,16 +622,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -606,16 +639,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -623,16 +656,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -640,16 +673,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -657,16 +690,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -674,16 +707,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -691,16 +724,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -708,16 +741,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -725,16 +758,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -742,16 +775,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -759,16 +792,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -776,16 +809,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -793,16 +826,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -810,16 +843,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -827,16 +860,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -844,16 +877,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -861,16 +894,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -878,16 +911,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -895,16 +928,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -912,16 +945,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -929,16 +962,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -946,16 +979,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -963,16 +996,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -980,16 +1013,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -997,16 +1030,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1014,16 +1047,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1031,16 +1064,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1048,18 +1081,222 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924BB60B-AB6F-42EE-B2E9-5ACCE4741D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCCB60BC-3DAB-4390-A2B7-A5A3C60DE8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="37">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,130 +54,91 @@
     <t>1070</t>
   </si>
   <si>
-    <t>134133747</t>
-  </si>
-  <si>
-    <t>NUP Indexações 29.08.2025</t>
-  </si>
-  <si>
-    <t>129141430</t>
-  </si>
-  <si>
-    <t>134102658</t>
-  </si>
-  <si>
-    <t>129427531</t>
-  </si>
-  <si>
-    <t>133934952</t>
-  </si>
-  <si>
-    <t>134186185</t>
-  </si>
-  <si>
-    <t>134096322</t>
-  </si>
-  <si>
-    <t>129034486</t>
-  </si>
-  <si>
-    <t>133533785</t>
-  </si>
-  <si>
-    <t>134118378</t>
-  </si>
-  <si>
-    <t>129510878</t>
-  </si>
-  <si>
-    <t>133979571</t>
-  </si>
-  <si>
-    <t>129393181</t>
-  </si>
-  <si>
-    <t>133925708</t>
-  </si>
-  <si>
-    <t>134099220</t>
-  </si>
-  <si>
-    <t>132975015</t>
-  </si>
-  <si>
-    <t>133930942</t>
-  </si>
-  <si>
-    <t>134138449</t>
-  </si>
-  <si>
-    <t>134175235</t>
-  </si>
-  <si>
-    <t>134139570</t>
-  </si>
-  <si>
-    <t>134143698</t>
-  </si>
-  <si>
-    <t>133972473</t>
-  </si>
-  <si>
-    <t>134163283</t>
-  </si>
-  <si>
-    <t>134169985</t>
-  </si>
-  <si>
-    <t>133936182</t>
-  </si>
-  <si>
-    <t>133972516</t>
-  </si>
-  <si>
-    <t>134123685</t>
-  </si>
-  <si>
     <t>129276671</t>
   </si>
   <si>
-    <t>134053756</t>
-  </si>
-  <si>
-    <t>129475072</t>
-  </si>
-  <si>
-    <t>129068308</t>
-  </si>
-  <si>
-    <t>133972238</t>
-  </si>
-  <si>
-    <t>129209548</t>
-  </si>
-  <si>
-    <t>134141563</t>
-  </si>
-  <si>
-    <t>134122905</t>
-  </si>
-  <si>
-    <t>134193140</t>
-  </si>
-  <si>
-    <t>132412853</t>
-  </si>
-  <si>
-    <t>134133670</t>
-  </si>
-  <si>
     <t>133926272</t>
   </si>
   <si>
-    <t>133599159</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 29.08.2025 (2)</t>
+    <t>Allianz - Cancelamento 02.09.2025</t>
+  </si>
+  <si>
+    <t>134048544</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 02.09.2025</t>
+  </si>
+  <si>
+    <t>129444403</t>
+  </si>
+  <si>
+    <t>129239077</t>
+  </si>
+  <si>
+    <t>133973269</t>
+  </si>
+  <si>
+    <t>129558773</t>
+  </si>
+  <si>
+    <t>134051488</t>
+  </si>
+  <si>
+    <t>133859982</t>
+  </si>
+  <si>
+    <t>129447191</t>
+  </si>
+  <si>
+    <t>134111484</t>
+  </si>
+  <si>
+    <t>134100099</t>
+  </si>
+  <si>
+    <t>129452370</t>
+  </si>
+  <si>
+    <t>134003861</t>
+  </si>
+  <si>
+    <t>133860289</t>
+  </si>
+  <si>
+    <t>133994237</t>
+  </si>
+  <si>
+    <t>129523315</t>
+  </si>
+  <si>
+    <t>134207033</t>
+  </si>
+  <si>
+    <t>129558973</t>
+  </si>
+  <si>
+    <t>129537920</t>
+  </si>
+  <si>
+    <t>134138433</t>
+  </si>
+  <si>
+    <t>129733520</t>
+  </si>
+  <si>
+    <t>134048759</t>
+  </si>
+  <si>
+    <t>134166001</t>
+  </si>
+  <si>
+    <t>133261755</t>
+  </si>
+  <si>
+    <t>134180763</t>
+  </si>
+  <si>
+    <t>133904761</t>
   </si>
 </sst>
 </file>
@@ -573,7 +534,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -605,16 +566,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -622,16 +583,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -639,16 +600,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -656,16 +617,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -673,16 +634,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -690,16 +651,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -707,16 +668,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -724,16 +685,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -741,16 +702,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -758,16 +719,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -775,16 +736,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -792,16 +753,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -809,16 +770,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -832,10 +793,10 @@
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -843,16 +804,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -860,16 +821,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -877,16 +838,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -894,16 +855,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -911,16 +872,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -928,16 +889,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -945,16 +906,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -962,16 +923,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -979,16 +940,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -996,16 +957,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1013,16 +974,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1030,16 +991,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1047,16 +1008,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1064,16 +1025,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1081,16 +1042,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1098,16 +1059,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1115,16 +1076,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1132,171 +1093,18 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E42" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCCB60BC-3DAB-4390-A2B7-A5A3C60DE8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0B270B-D87A-4D2D-8F85-CA5439A8B4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,96 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>1070</t>
-  </si>
-  <si>
-    <t>129276671</t>
-  </si>
-  <si>
-    <t>133926272</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 02.09.2025</t>
-  </si>
-  <si>
-    <t>134048544</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 02.09.2025</t>
-  </si>
-  <si>
-    <t>129444403</t>
-  </si>
-  <si>
-    <t>129239077</t>
-  </si>
-  <si>
-    <t>133973269</t>
-  </si>
-  <si>
-    <t>129558773</t>
-  </si>
-  <si>
-    <t>134051488</t>
-  </si>
-  <si>
-    <t>133859982</t>
-  </si>
-  <si>
-    <t>129447191</t>
-  </si>
-  <si>
-    <t>134111484</t>
-  </si>
-  <si>
-    <t>134100099</t>
-  </si>
-  <si>
-    <t>129452370</t>
-  </si>
-  <si>
-    <t>134003861</t>
-  </si>
-  <si>
-    <t>133860289</t>
-  </si>
-  <si>
-    <t>133994237</t>
-  </si>
-  <si>
-    <t>129523315</t>
-  </si>
-  <si>
-    <t>134207033</t>
-  </si>
-  <si>
-    <t>129558973</t>
-  </si>
-  <si>
-    <t>129537920</t>
-  </si>
-  <si>
-    <t>134138433</t>
-  </si>
-  <si>
-    <t>129733520</t>
-  </si>
-  <si>
-    <t>134048759</t>
-  </si>
-  <si>
-    <t>134166001</t>
-  </si>
-  <si>
-    <t>133261755</t>
-  </si>
-  <si>
-    <t>134180763</t>
-  </si>
-  <si>
-    <t>133904761</t>
   </si>
 </sst>
 </file>
@@ -565,545 +475,161 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="18" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="19" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="20" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E20" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="21" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E21" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="22" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E22" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="23" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="24" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="25" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="26" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E26" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="27" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E27" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="28" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E28" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="29" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E29" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="30" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E30" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="31" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E31" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="32" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E32" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="33" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E33" s="2" t="s">
         <v>6</v>
       </c>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0B270B-D87A-4D2D-8F85-CA5439A8B4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6A6E11-75FD-4D49-99F4-0BA4B04DFCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="53">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,144 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>134020529</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>NUP indexações 03.09.2025</t>
+  </si>
+  <si>
+    <t>133821139</t>
+  </si>
+  <si>
+    <t>129441641</t>
+  </si>
+  <si>
+    <t>133973613</t>
+  </si>
+  <si>
+    <t>134006816</t>
+  </si>
+  <si>
+    <t>133977527</t>
+  </si>
+  <si>
+    <t>134137687</t>
+  </si>
+  <si>
+    <t>134091284</t>
+  </si>
+  <si>
+    <t>134020595</t>
+  </si>
+  <si>
+    <t>134100269</t>
+  </si>
+  <si>
+    <t>134090904</t>
+  </si>
+  <si>
+    <t>134267254</t>
+  </si>
+  <si>
+    <t>134254410</t>
+  </si>
+  <si>
+    <t>129313385</t>
+  </si>
+  <si>
+    <t>134092675</t>
+  </si>
+  <si>
+    <t>134213641</t>
+  </si>
+  <si>
+    <t>134053179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134155045  </t>
+  </si>
+  <si>
+    <t>134059939</t>
+  </si>
+  <si>
+    <t>134213658</t>
+  </si>
+  <si>
+    <t>134049129</t>
+  </si>
+  <si>
+    <t>134018614</t>
+  </si>
+  <si>
+    <t>133934678</t>
+  </si>
+  <si>
+    <t>129340523</t>
+  </si>
+  <si>
+    <t>133978588</t>
+  </si>
+  <si>
+    <t>134209376</t>
+  </si>
+  <si>
+    <t>134213389</t>
+  </si>
+  <si>
+    <t>129459430</t>
+  </si>
+  <si>
+    <t>134163677</t>
+  </si>
+  <si>
+    <t>134161578</t>
+  </si>
+  <si>
+    <t>129409575</t>
+  </si>
+  <si>
+    <t>130475971</t>
+  </si>
+  <si>
+    <t>129303590</t>
+  </si>
+  <si>
+    <t>134051102</t>
+  </si>
+  <si>
+    <t>134195795</t>
+  </si>
+  <si>
+    <t>133972531</t>
+  </si>
+  <si>
+    <t>134018488</t>
+  </si>
+  <si>
+    <t>133906774</t>
+  </si>
+  <si>
+    <t>133883803</t>
+  </si>
+  <si>
+    <t>133761513</t>
+  </si>
+  <si>
+    <t>134163650</t>
+  </si>
+  <si>
+    <t>129275793</t>
+  </si>
+  <si>
+    <t>134079280</t>
+  </si>
+  <si>
+    <t>NUP Indexações 03.09.2025</t>
   </si>
 </sst>
 </file>
@@ -444,7 +582,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,162 +613,750 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6A6E11-75FD-4D49-99F4-0BA4B04DFCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD8BC64-D76D-4E5E-9326-257399443006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="70">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,142 +51,193 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>134020529</t>
-  </si>
-  <si>
-    <t>1070</t>
-  </si>
-  <si>
-    <t>NUP indexações 03.09.2025</t>
-  </si>
-  <si>
-    <t>133821139</t>
-  </si>
-  <si>
-    <t>129441641</t>
-  </si>
-  <si>
-    <t>133973613</t>
-  </si>
-  <si>
-    <t>134006816</t>
-  </si>
-  <si>
-    <t>133977527</t>
-  </si>
-  <si>
-    <t>134137687</t>
-  </si>
-  <si>
-    <t>134091284</t>
-  </si>
-  <si>
-    <t>134020595</t>
-  </si>
-  <si>
-    <t>134100269</t>
-  </si>
-  <si>
-    <t>134090904</t>
-  </si>
-  <si>
-    <t>134267254</t>
-  </si>
-  <si>
-    <t>134254410</t>
-  </si>
-  <si>
-    <t>129313385</t>
-  </si>
-  <si>
-    <t>134092675</t>
-  </si>
-  <si>
-    <t>134213641</t>
-  </si>
-  <si>
-    <t>134053179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134155045  </t>
-  </si>
-  <si>
-    <t>134059939</t>
-  </si>
-  <si>
-    <t>134213658</t>
-  </si>
-  <si>
-    <t>134049129</t>
-  </si>
-  <si>
-    <t>134018614</t>
-  </si>
-  <si>
-    <t>133934678</t>
-  </si>
-  <si>
-    <t>129340523</t>
-  </si>
-  <si>
-    <t>133978588</t>
-  </si>
-  <si>
-    <t>134209376</t>
-  </si>
-  <si>
-    <t>134213389</t>
-  </si>
-  <si>
-    <t>129459430</t>
-  </si>
-  <si>
-    <t>134163677</t>
-  </si>
-  <si>
-    <t>134161578</t>
-  </si>
-  <si>
-    <t>129409575</t>
-  </si>
-  <si>
-    <t>130475971</t>
-  </si>
-  <si>
-    <t>129303590</t>
-  </si>
-  <si>
-    <t>134051102</t>
-  </si>
-  <si>
-    <t>134195795</t>
-  </si>
-  <si>
-    <t>133972531</t>
-  </si>
-  <si>
-    <t>134018488</t>
-  </si>
-  <si>
-    <t>133906774</t>
-  </si>
-  <si>
-    <t>133883803</t>
-  </si>
-  <si>
-    <t>133761513</t>
-  </si>
-  <si>
-    <t>134163650</t>
-  </si>
-  <si>
-    <t>129275793</t>
-  </si>
-  <si>
-    <t>134079280</t>
-  </si>
-  <si>
-    <t>NUP Indexações 03.09.2025</t>
+    <t>NUP Indexações 05.09.2025</t>
+  </si>
+  <si>
+    <t>130457650</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 05.09.2025</t>
+  </si>
+  <si>
+    <t>131738740</t>
+  </si>
+  <si>
+    <t>134175897</t>
+  </si>
+  <si>
+    <t>134179594</t>
+  </si>
+  <si>
+    <t>134182035</t>
+  </si>
+  <si>
+    <t>134169989</t>
+  </si>
+  <si>
+    <t>134195711</t>
+  </si>
+  <si>
+    <t>134193991</t>
+  </si>
+  <si>
+    <t>134220924</t>
+  </si>
+  <si>
+    <t>134228900</t>
+  </si>
+  <si>
+    <t>134230113</t>
+  </si>
+  <si>
+    <t>134221049</t>
+  </si>
+  <si>
+    <t>134222066</t>
+  </si>
+  <si>
+    <t>134248162</t>
+  </si>
+  <si>
+    <t>134266356</t>
+  </si>
+  <si>
+    <t>134271509</t>
+  </si>
+  <si>
+    <t>132840380</t>
+  </si>
+  <si>
+    <t>134292495</t>
+  </si>
+  <si>
+    <t>134290386</t>
+  </si>
+  <si>
+    <t>134296010</t>
+  </si>
+  <si>
+    <t>134296014</t>
+  </si>
+  <si>
+    <t>134290239</t>
+  </si>
+  <si>
+    <t>133228541</t>
+  </si>
+  <si>
+    <t>134179346</t>
+  </si>
+  <si>
+    <t>130126461</t>
+  </si>
+  <si>
+    <t>134306485</t>
+  </si>
+  <si>
+    <t>134305208</t>
+  </si>
+  <si>
+    <t>134307492</t>
+  </si>
+  <si>
+    <t>134307520</t>
+  </si>
+  <si>
+    <t>134308152</t>
+  </si>
+  <si>
+    <t>134175557</t>
+  </si>
+  <si>
+    <t>134310509</t>
+  </si>
+  <si>
+    <t>134310218</t>
+  </si>
+  <si>
+    <t>134311322</t>
+  </si>
+  <si>
+    <t>134199610</t>
+  </si>
+  <si>
+    <t>134081146</t>
+  </si>
+  <si>
+    <t>134077378</t>
+  </si>
+  <si>
+    <t>134168562</t>
+  </si>
+  <si>
+    <t>134175153</t>
+  </si>
+  <si>
+    <t>134198915</t>
+  </si>
+  <si>
+    <t>134314829</t>
+  </si>
+  <si>
+    <t>134315998</t>
+  </si>
+  <si>
+    <t>134224375</t>
+  </si>
+  <si>
+    <t>134310894</t>
+  </si>
+  <si>
+    <t>130917854</t>
+  </si>
+  <si>
+    <t>134163042</t>
+  </si>
+  <si>
+    <t>134164610</t>
+  </si>
+  <si>
+    <t>134321994</t>
+  </si>
+  <si>
+    <t>134170221</t>
+  </si>
+  <si>
+    <t>134321403</t>
+  </si>
+  <si>
+    <t>134174611</t>
+  </si>
+  <si>
+    <t>134176042</t>
+  </si>
+  <si>
+    <t>134177281</t>
+  </si>
+  <si>
+    <t>134177699</t>
+  </si>
+  <si>
+    <t>134179042</t>
+  </si>
+  <si>
+    <t>134179176</t>
+  </si>
+  <si>
+    <t>134179634</t>
+  </si>
+  <si>
+    <t>134179819</t>
+  </si>
+  <si>
+    <t>134180008</t>
+  </si>
+  <si>
+    <t>134206581</t>
   </si>
 </sst>
 </file>
@@ -582,7 +633,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -614,16 +665,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -631,16 +682,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -648,16 +699,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -665,16 +716,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -682,16 +733,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -699,16 +750,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -716,16 +767,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -733,16 +784,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -750,16 +801,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -767,16 +818,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -784,16 +835,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -801,16 +852,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -818,16 +869,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -835,16 +886,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -852,16 +903,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -869,16 +920,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -886,16 +937,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -903,16 +954,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -920,16 +971,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -937,16 +988,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -954,16 +1005,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -971,16 +1022,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -988,16 +1039,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1005,16 +1056,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1022,16 +1073,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1039,16 +1090,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1056,16 +1107,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1073,16 +1124,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1090,16 +1141,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1107,16 +1158,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1124,16 +1175,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1141,16 +1192,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1158,16 +1209,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1175,16 +1226,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1192,16 +1243,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1209,16 +1260,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1226,16 +1277,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1243,16 +1294,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1260,16 +1311,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1277,16 +1328,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1294,16 +1345,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1311,16 +1362,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1328,16 +1379,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1345,18 +1396,290 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD8BC64-D76D-4E5E-9326-257399443006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE7772A-3BA0-422A-9A1D-8538B263957A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="45">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,193 +51,118 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>NUP Indexações 05.09.2025</t>
-  </si>
-  <si>
-    <t>130457650</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 05.09.2025</t>
-  </si>
-  <si>
-    <t>131738740</t>
-  </si>
-  <si>
-    <t>134175897</t>
-  </si>
-  <si>
-    <t>134179594</t>
-  </si>
-  <si>
-    <t>134182035</t>
-  </si>
-  <si>
-    <t>134169989</t>
-  </si>
-  <si>
-    <t>134195711</t>
-  </si>
-  <si>
-    <t>134193991</t>
-  </si>
-  <si>
-    <t>134220924</t>
-  </si>
-  <si>
-    <t>134228900</t>
-  </si>
-  <si>
-    <t>134230113</t>
-  </si>
-  <si>
-    <t>134221049</t>
-  </si>
-  <si>
-    <t>134222066</t>
-  </si>
-  <si>
-    <t>134248162</t>
-  </si>
-  <si>
-    <t>134266356</t>
-  </si>
-  <si>
-    <t>134271509</t>
-  </si>
-  <si>
-    <t>132840380</t>
-  </si>
-  <si>
-    <t>134292495</t>
-  </si>
-  <si>
-    <t>134290386</t>
-  </si>
-  <si>
-    <t>134296010</t>
-  </si>
-  <si>
-    <t>134296014</t>
-  </si>
-  <si>
-    <t>134290239</t>
-  </si>
-  <si>
-    <t>133228541</t>
-  </si>
-  <si>
-    <t>134179346</t>
-  </si>
-  <si>
-    <t>130126461</t>
-  </si>
-  <si>
-    <t>134306485</t>
-  </si>
-  <si>
-    <t>134305208</t>
-  </si>
-  <si>
-    <t>134307492</t>
-  </si>
-  <si>
-    <t>134307520</t>
-  </si>
-  <si>
-    <t>134308152</t>
-  </si>
-  <si>
-    <t>134175557</t>
-  </si>
-  <si>
-    <t>134310509</t>
-  </si>
-  <si>
-    <t>134310218</t>
-  </si>
-  <si>
-    <t>134311322</t>
-  </si>
-  <si>
-    <t>134199610</t>
-  </si>
-  <si>
-    <t>134081146</t>
-  </si>
-  <si>
-    <t>134077378</t>
-  </si>
-  <si>
-    <t>134168562</t>
-  </si>
-  <si>
-    <t>134175153</t>
-  </si>
-  <si>
-    <t>134198915</t>
-  </si>
-  <si>
-    <t>134314829</t>
-  </si>
-  <si>
-    <t>134315998</t>
-  </si>
-  <si>
-    <t>134224375</t>
-  </si>
-  <si>
-    <t>134310894</t>
-  </si>
-  <si>
-    <t>130917854</t>
-  </si>
-  <si>
-    <t>134163042</t>
-  </si>
-  <si>
-    <t>134164610</t>
-  </si>
-  <si>
-    <t>134321994</t>
-  </si>
-  <si>
-    <t>134170221</t>
-  </si>
-  <si>
-    <t>134321403</t>
-  </si>
-  <si>
-    <t>134174611</t>
-  </si>
-  <si>
-    <t>134176042</t>
-  </si>
-  <si>
-    <t>134177281</t>
-  </si>
-  <si>
-    <t>134177699</t>
-  </si>
-  <si>
-    <t>134179042</t>
-  </si>
-  <si>
-    <t>134179176</t>
-  </si>
-  <si>
-    <t>134179634</t>
-  </si>
-  <si>
-    <t>134179819</t>
-  </si>
-  <si>
-    <t>134180008</t>
-  </si>
-  <si>
-    <t>134206581</t>
+    <t>Allianz - Cancelamento 05.09.2025.xlsx</t>
+  </si>
+  <si>
+    <t>134234931</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>NUP Indexações  05.09.2025</t>
+  </si>
+  <si>
+    <t>134234823</t>
+  </si>
+  <si>
+    <t>129567687</t>
+  </si>
+  <si>
+    <t>134281027</t>
+  </si>
+  <si>
+    <t>134166703</t>
+  </si>
+  <si>
+    <t>134328187</t>
+  </si>
+  <si>
+    <t>134280707</t>
+  </si>
+  <si>
+    <t>129256614</t>
+  </si>
+  <si>
+    <t>129521545</t>
+  </si>
+  <si>
+    <t>133706154</t>
+  </si>
+  <si>
+    <t>129590345</t>
+  </si>
+  <si>
+    <t>134090741</t>
+  </si>
+  <si>
+    <t>129316056</t>
+  </si>
+  <si>
+    <t>129288685</t>
+  </si>
+  <si>
+    <t>134165386</t>
+  </si>
+  <si>
+    <t>134236465</t>
+  </si>
+  <si>
+    <t>134283389</t>
+  </si>
+  <si>
+    <t>129580322</t>
+  </si>
+  <si>
+    <t>130588533</t>
+  </si>
+  <si>
+    <t>134167913</t>
+  </si>
+  <si>
+    <t>134288439</t>
+  </si>
+  <si>
+    <t>134241585</t>
+  </si>
+  <si>
+    <t>134157346</t>
+  </si>
+  <si>
+    <t>134213813</t>
+  </si>
+  <si>
+    <t>129444982</t>
+  </si>
+  <si>
+    <t>134164802</t>
+  </si>
+  <si>
+    <t>129636698</t>
+  </si>
+  <si>
+    <t>133860261</t>
+  </si>
+  <si>
+    <t>134135029</t>
+  </si>
+  <si>
+    <t>133785579</t>
+  </si>
+  <si>
+    <t>129587364</t>
+  </si>
+  <si>
+    <t>134114510</t>
+  </si>
+  <si>
+    <t>134059481</t>
+  </si>
+  <si>
+    <t>134050485</t>
+  </si>
+  <si>
+    <t>133994271</t>
   </si>
 </sst>
 </file>
@@ -633,7 +558,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -1260,7 +1185,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>9</v>
@@ -1277,7 +1202,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>9</v>
@@ -1289,397 +1214,6 @@
         <v>7</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E61" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE7772A-3BA0-422A-9A1D-8538B263957A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96C8810-0ECB-4DFB-92A3-40165C3BADB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,9 +51,6 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Allianz - Cancelamento 05.09.2025.xlsx</t>
-  </si>
-  <si>
     <t>134234931</t>
   </si>
   <si>
@@ -163,6 +160,9 @@
   </si>
   <si>
     <t>133994271</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 05.09.2025</t>
   </si>
 </sst>
 </file>
@@ -590,16 +590,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -607,16 +607,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -624,16 +624,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -641,16 +641,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -658,16 +658,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -675,16 +675,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -692,16 +692,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -709,16 +709,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -726,16 +726,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -743,16 +743,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -760,16 +760,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -777,16 +777,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -794,16 +794,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -811,16 +811,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -828,16 +828,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -845,16 +845,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -862,16 +862,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -879,16 +879,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -896,16 +896,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -913,16 +913,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -930,16 +930,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -947,16 +947,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -964,16 +964,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -981,16 +981,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -998,16 +998,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1015,16 +1015,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1032,16 +1032,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1049,16 +1049,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1066,16 +1066,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1083,16 +1083,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1100,16 +1100,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1117,16 +1117,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1151,16 +1151,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1168,16 +1168,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1185,16 +1185,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1202,16 +1202,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96C8810-0ECB-4DFB-92A3-40165C3BADB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C62A52B-385F-4F8B-B3EC-AFB9275FDA1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="50">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,105 +51,12 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>134234931</t>
-  </si>
-  <si>
     <t>1070</t>
   </si>
   <si>
-    <t>NUP Indexações  05.09.2025</t>
-  </si>
-  <si>
-    <t>134234823</t>
-  </si>
-  <si>
-    <t>129567687</t>
-  </si>
-  <si>
-    <t>134281027</t>
-  </si>
-  <si>
-    <t>134166703</t>
-  </si>
-  <si>
-    <t>134328187</t>
-  </si>
-  <si>
-    <t>134280707</t>
-  </si>
-  <si>
-    <t>129256614</t>
-  </si>
-  <si>
-    <t>129521545</t>
-  </si>
-  <si>
-    <t>133706154</t>
-  </si>
-  <si>
-    <t>129590345</t>
-  </si>
-  <si>
-    <t>134090741</t>
-  </si>
-  <si>
-    <t>129316056</t>
-  </si>
-  <si>
-    <t>129288685</t>
-  </si>
-  <si>
     <t>134165386</t>
   </si>
   <si>
-    <t>134236465</t>
-  </si>
-  <si>
-    <t>134283389</t>
-  </si>
-  <si>
-    <t>129580322</t>
-  </si>
-  <si>
-    <t>130588533</t>
-  </si>
-  <si>
-    <t>134167913</t>
-  </si>
-  <si>
-    <t>134288439</t>
-  </si>
-  <si>
-    <t>134241585</t>
-  </si>
-  <si>
-    <t>134157346</t>
-  </si>
-  <si>
-    <t>134213813</t>
-  </si>
-  <si>
-    <t>129444982</t>
-  </si>
-  <si>
-    <t>134164802</t>
-  </si>
-  <si>
-    <t>129636698</t>
-  </si>
-  <si>
-    <t>133860261</t>
-  </si>
-  <si>
-    <t>134135029</t>
-  </si>
-  <si>
-    <t>133785579</t>
-  </si>
-  <si>
-    <t>129587364</t>
-  </si>
-  <si>
     <t>134114510</t>
   </si>
   <si>
@@ -162,7 +69,115 @@
     <t>133994271</t>
   </si>
   <si>
-    <t>Allianz - Cancelamento 05.09.2025</t>
+    <t>Allianz - Cancelamento 08.09.2025</t>
+  </si>
+  <si>
+    <t>129671595</t>
+  </si>
+  <si>
+    <t>NUP Indexações 08.09.2025</t>
+  </si>
+  <si>
+    <t>133973375</t>
+  </si>
+  <si>
+    <t>129595978</t>
+  </si>
+  <si>
+    <t>134280490</t>
+  </si>
+  <si>
+    <t>129147419</t>
+  </si>
+  <si>
+    <t>133972478</t>
+  </si>
+  <si>
+    <t>129253625</t>
+  </si>
+  <si>
+    <t>129585764</t>
+  </si>
+  <si>
+    <t>134280343</t>
+  </si>
+  <si>
+    <t>134137925</t>
+  </si>
+  <si>
+    <t>129305532</t>
+  </si>
+  <si>
+    <t>129613300</t>
+  </si>
+  <si>
+    <t>129204973</t>
+  </si>
+  <si>
+    <t>133907824</t>
+  </si>
+  <si>
+    <t>134213681</t>
+  </si>
+  <si>
+    <t>134104016</t>
+  </si>
+  <si>
+    <t>134051516</t>
+  </si>
+  <si>
+    <t>129162280</t>
+  </si>
+  <si>
+    <t>134047864</t>
+  </si>
+  <si>
+    <t>134050873</t>
+  </si>
+  <si>
+    <t>134050734</t>
+  </si>
+  <si>
+    <t>134060858</t>
+  </si>
+  <si>
+    <t>129225962</t>
+  </si>
+  <si>
+    <t>134221183</t>
+  </si>
+  <si>
+    <t>133994945</t>
+  </si>
+  <si>
+    <t>129622828</t>
+  </si>
+  <si>
+    <t>134217366</t>
+  </si>
+  <si>
+    <t>129703532</t>
+  </si>
+  <si>
+    <t>129626747</t>
+  </si>
+  <si>
+    <t>134258022</t>
+  </si>
+  <si>
+    <t>134161801</t>
+  </si>
+  <si>
+    <t>134114272</t>
+  </si>
+  <si>
+    <t>134280572</t>
+  </si>
+  <si>
+    <t>134144303</t>
+  </si>
+  <si>
+    <t>134263262</t>
   </si>
 </sst>
 </file>
@@ -558,7 +573,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -590,16 +605,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -607,16 +622,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -624,16 +639,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -641,16 +656,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -658,16 +673,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -675,16 +690,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -692,16 +707,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -709,16 +724,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -726,16 +741,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -743,16 +758,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -760,16 +775,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -777,16 +792,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -794,16 +809,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -811,16 +826,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -828,16 +843,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -845,16 +860,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -862,16 +877,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -879,16 +894,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -896,16 +911,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -913,16 +928,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -930,16 +945,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -947,16 +962,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -964,16 +979,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -981,16 +996,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -998,16 +1013,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1015,16 +1030,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1032,16 +1047,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1049,16 +1064,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1066,16 +1081,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1083,16 +1098,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1100,16 +1115,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1117,16 +1132,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1134,16 +1149,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1151,16 +1166,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1168,16 +1183,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1185,16 +1200,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1202,18 +1217,86 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E38" s="2" t="s">
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C62A52B-385F-4F8B-B3EC-AFB9275FDA1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20305A21-6A85-40C8-9FDE-9859AC774220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="53">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,130 +54,139 @@
     <t>1070</t>
   </si>
   <si>
-    <t>134165386</t>
-  </si>
-  <si>
-    <t>134114510</t>
-  </si>
-  <si>
-    <t>134059481</t>
-  </si>
-  <si>
-    <t>134050485</t>
-  </si>
-  <si>
-    <t>133994271</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 08.09.2025</t>
-  </si>
-  <si>
-    <t>129671595</t>
-  </si>
-  <si>
-    <t>NUP Indexações 08.09.2025</t>
-  </si>
-  <si>
-    <t>133973375</t>
-  </si>
-  <si>
-    <t>129595978</t>
-  </si>
-  <si>
-    <t>134280490</t>
-  </si>
-  <si>
-    <t>129147419</t>
-  </si>
-  <si>
-    <t>133972478</t>
-  </si>
-  <si>
-    <t>129253625</t>
-  </si>
-  <si>
-    <t>129585764</t>
-  </si>
-  <si>
-    <t>134280343</t>
-  </si>
-  <si>
-    <t>134137925</t>
-  </si>
-  <si>
-    <t>129305532</t>
-  </si>
-  <si>
-    <t>129613300</t>
-  </si>
-  <si>
-    <t>129204973</t>
-  </si>
-  <si>
-    <t>133907824</t>
-  </si>
-  <si>
-    <t>134213681</t>
-  </si>
-  <si>
-    <t>134104016</t>
-  </si>
-  <si>
-    <t>134051516</t>
-  </si>
-  <si>
-    <t>129162280</t>
-  </si>
-  <si>
-    <t>134047864</t>
-  </si>
-  <si>
-    <t>134050873</t>
-  </si>
-  <si>
-    <t>134050734</t>
-  </si>
-  <si>
-    <t>134060858</t>
-  </si>
-  <si>
-    <t>129225962</t>
-  </si>
-  <si>
-    <t>134221183</t>
-  </si>
-  <si>
-    <t>133994945</t>
-  </si>
-  <si>
-    <t>129622828</t>
-  </si>
-  <si>
-    <t>134217366</t>
-  </si>
-  <si>
-    <t>129703532</t>
-  </si>
-  <si>
-    <t>129626747</t>
-  </si>
-  <si>
-    <t>134258022</t>
-  </si>
-  <si>
-    <t>134161801</t>
-  </si>
-  <si>
-    <t>134114272</t>
-  </si>
-  <si>
-    <t>134280572</t>
-  </si>
-  <si>
-    <t>134144303</t>
-  </si>
-  <si>
-    <t>134263262</t>
+    <t>Allianz - Cancelamento 10.09.2025</t>
+  </si>
+  <si>
+    <t>134328160</t>
+  </si>
+  <si>
+    <t>NUP Indexações 10.09.2025</t>
+  </si>
+  <si>
+    <t>134234815</t>
+  </si>
+  <si>
+    <t>134280120</t>
+  </si>
+  <si>
+    <t>134100294</t>
+  </si>
+  <si>
+    <t>129524114</t>
+  </si>
+  <si>
+    <t>134202624</t>
+  </si>
+  <si>
+    <t>134327883</t>
+  </si>
+  <si>
+    <t>134349706</t>
+  </si>
+  <si>
+    <t>134165136</t>
+  </si>
+  <si>
+    <t>134140441</t>
+  </si>
+  <si>
+    <t>129486803</t>
+  </si>
+  <si>
+    <t>134366595</t>
+  </si>
+  <si>
+    <t>129980470</t>
+  </si>
+  <si>
+    <t>134290414</t>
+  </si>
+  <si>
+    <t>134216435</t>
+  </si>
+  <si>
+    <t>134288746</t>
+  </si>
+  <si>
+    <t>129534933</t>
+  </si>
+  <si>
+    <t>129588067</t>
+  </si>
+  <si>
+    <t>134137626</t>
+  </si>
+  <si>
+    <t>129661669</t>
+  </si>
+  <si>
+    <t>134171730</t>
+  </si>
+  <si>
+    <t>134091463</t>
+  </si>
+  <si>
+    <t>134337683</t>
+  </si>
+  <si>
+    <t>129559442</t>
+  </si>
+  <si>
+    <t>129917396</t>
+  </si>
+  <si>
+    <t>129659191</t>
+  </si>
+  <si>
+    <t>134140943</t>
+  </si>
+  <si>
+    <t>134355910</t>
+  </si>
+  <si>
+    <t>134328199</t>
+  </si>
+  <si>
+    <t>129541265</t>
+  </si>
+  <si>
+    <t>134269504</t>
+  </si>
+  <si>
+    <t>134245786</t>
+  </si>
+  <si>
+    <t>129595692</t>
+  </si>
+  <si>
+    <t>134263269</t>
+  </si>
+  <si>
+    <t>134140038</t>
+  </si>
+  <si>
+    <t>129595616</t>
+  </si>
+  <si>
+    <t>134279980</t>
+  </si>
+  <si>
+    <t>134370823</t>
+  </si>
+  <si>
+    <t>131795229</t>
+  </si>
+  <si>
+    <t>129515390</t>
+  </si>
+  <si>
+    <t>134350228</t>
+  </si>
+  <si>
+    <t>133637660</t>
+  </si>
+  <si>
+    <t>129600874</t>
   </si>
 </sst>
 </file>
@@ -573,7 +582,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -605,16 +614,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -622,16 +631,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -639,16 +648,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -656,16 +665,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -673,16 +682,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -690,16 +699,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -707,16 +716,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -724,16 +733,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -741,16 +750,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -758,16 +767,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -775,16 +784,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -792,16 +801,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -809,16 +818,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -826,16 +835,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -843,16 +852,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -860,16 +869,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -877,16 +886,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -894,16 +903,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -911,16 +920,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -928,16 +937,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -945,16 +954,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -962,16 +971,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -979,16 +988,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -996,16 +1005,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1013,16 +1022,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1030,16 +1039,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1047,16 +1056,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1064,16 +1073,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1081,16 +1090,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1098,16 +1107,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1115,16 +1124,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1132,16 +1141,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1149,16 +1158,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1166,16 +1175,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1183,16 +1192,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1200,16 +1209,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1217,16 +1226,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1234,16 +1243,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1251,16 +1260,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1268,16 +1277,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1285,18 +1294,86 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20305A21-6A85-40C8-9FDE-9859AC774220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABDE5F9-12FD-4EA4-8680-3320FBC55893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="45">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,139 +54,115 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Allianz - Cancelamento 10.09.2025</t>
-  </si>
-  <si>
-    <t>134328160</t>
-  </si>
-  <si>
-    <t>NUP Indexações 10.09.2025</t>
-  </si>
-  <si>
-    <t>134234815</t>
-  </si>
-  <si>
-    <t>134280120</t>
-  </si>
-  <si>
-    <t>134100294</t>
-  </si>
-  <si>
-    <t>129524114</t>
-  </si>
-  <si>
-    <t>134202624</t>
-  </si>
-  <si>
-    <t>134327883</t>
-  </si>
-  <si>
-    <t>134349706</t>
-  </si>
-  <si>
-    <t>134165136</t>
-  </si>
-  <si>
-    <t>134140441</t>
-  </si>
-  <si>
-    <t>129486803</t>
-  </si>
-  <si>
-    <t>134366595</t>
-  </si>
-  <si>
-    <t>129980470</t>
-  </si>
-  <si>
-    <t>134290414</t>
-  </si>
-  <si>
-    <t>134216435</t>
-  </si>
-  <si>
-    <t>134288746</t>
-  </si>
-  <si>
-    <t>129534933</t>
-  </si>
-  <si>
-    <t>129588067</t>
-  </si>
-  <si>
-    <t>134137626</t>
-  </si>
-  <si>
-    <t>129661669</t>
-  </si>
-  <si>
-    <t>134171730</t>
-  </si>
-  <si>
-    <t>134091463</t>
-  </si>
-  <si>
-    <t>134337683</t>
-  </si>
-  <si>
-    <t>129559442</t>
-  </si>
-  <si>
-    <t>129917396</t>
-  </si>
-  <si>
-    <t>129659191</t>
-  </si>
-  <si>
-    <t>134140943</t>
-  </si>
-  <si>
-    <t>134355910</t>
-  </si>
-  <si>
-    <t>134328199</t>
-  </si>
-  <si>
-    <t>129541265</t>
-  </si>
-  <si>
-    <t>134269504</t>
-  </si>
-  <si>
-    <t>134245786</t>
-  </si>
-  <si>
-    <t>129595692</t>
-  </si>
-  <si>
-    <t>134263269</t>
-  </si>
-  <si>
-    <t>134140038</t>
-  </si>
-  <si>
-    <t>129595616</t>
-  </si>
-  <si>
-    <t>134279980</t>
-  </si>
-  <si>
-    <t>134370823</t>
-  </si>
-  <si>
-    <t>131795229</t>
-  </si>
-  <si>
-    <t>129515390</t>
-  </si>
-  <si>
-    <t>134350228</t>
-  </si>
-  <si>
-    <t>133637660</t>
-  </si>
-  <si>
-    <t>129600874</t>
+    <t>134349868</t>
+  </si>
+  <si>
+    <t>NUP Indexações 11.09.2025</t>
+  </si>
+  <si>
+    <t>134282360</t>
+  </si>
+  <si>
+    <t>134289918</t>
+  </si>
+  <si>
+    <t>134138767</t>
+  </si>
+  <si>
+    <t>134114262</t>
+  </si>
+  <si>
+    <t>133861138</t>
+  </si>
+  <si>
+    <t>134161635</t>
+  </si>
+  <si>
+    <t>129692708</t>
+  </si>
+  <si>
+    <t>134378726</t>
+  </si>
+  <si>
+    <t>133994223</t>
+  </si>
+  <si>
+    <t>134396769</t>
+  </si>
+  <si>
+    <t>129403526</t>
+  </si>
+  <si>
+    <t>134376954</t>
+  </si>
+  <si>
+    <t>134260292</t>
+  </si>
+  <si>
+    <t>134373639</t>
+  </si>
+  <si>
+    <t>134328853</t>
+  </si>
+  <si>
+    <t>129439369</t>
+  </si>
+  <si>
+    <t>129316466</t>
+  </si>
+  <si>
+    <t>129587517</t>
+  </si>
+  <si>
+    <t>134243812</t>
+  </si>
+  <si>
+    <t>134143720</t>
+  </si>
+  <si>
+    <t>134329451</t>
+  </si>
+  <si>
+    <t>134289632</t>
+  </si>
+  <si>
+    <t>134379546</t>
+  </si>
+  <si>
+    <t>134360058</t>
+  </si>
+  <si>
+    <t>134328243</t>
+  </si>
+  <si>
+    <t>129671071</t>
+  </si>
+  <si>
+    <t>134378652</t>
+  </si>
+  <si>
+    <t>134337365</t>
+  </si>
+  <si>
+    <t>134399175</t>
+  </si>
+  <si>
+    <t>134289061</t>
+  </si>
+  <si>
+    <t>134395394</t>
+  </si>
+  <si>
+    <t>134388724</t>
+  </si>
+  <si>
+    <t>134020026</t>
+  </si>
+  <si>
+    <t>134178491</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 11.09.2025</t>
   </si>
 </sst>
 </file>
@@ -582,7 +558,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -614,16 +590,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -631,16 +607,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -648,16 +624,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -665,16 +641,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -682,16 +658,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -699,16 +675,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -716,16 +692,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -733,16 +709,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -750,16 +726,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -767,16 +743,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -784,16 +760,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -801,16 +777,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -818,16 +794,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -835,16 +811,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -852,16 +828,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -869,16 +845,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -886,16 +862,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -903,16 +879,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -920,16 +896,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -937,16 +913,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -954,16 +930,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -971,16 +947,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -988,16 +964,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1005,16 +981,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1022,16 +998,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1039,16 +1015,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1056,16 +1032,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1073,16 +1049,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1090,16 +1066,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1107,16 +1083,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1124,16 +1100,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1141,16 +1117,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1158,16 +1134,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1175,16 +1151,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1192,16 +1168,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1209,171 +1185,18 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABDE5F9-12FD-4EA4-8680-3320FBC55893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{658F5E2D-9A24-479C-9CB1-1C0ED930DD9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="50">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,112 +57,127 @@
     <t>134349868</t>
   </si>
   <si>
-    <t>NUP Indexações 11.09.2025</t>
-  </si>
-  <si>
-    <t>134282360</t>
-  </si>
-  <si>
-    <t>134289918</t>
-  </si>
-  <si>
-    <t>134138767</t>
-  </si>
-  <si>
-    <t>134114262</t>
-  </si>
-  <si>
     <t>133861138</t>
   </si>
   <si>
-    <t>134161635</t>
-  </si>
-  <si>
-    <t>129692708</t>
-  </si>
-  <si>
-    <t>134378726</t>
-  </si>
-  <si>
-    <t>133994223</t>
-  </si>
-  <si>
-    <t>134396769</t>
-  </si>
-  <si>
-    <t>129403526</t>
-  </si>
-  <si>
-    <t>134376954</t>
-  </si>
-  <si>
-    <t>134260292</t>
-  </si>
-  <si>
-    <t>134373639</t>
-  </si>
-  <si>
-    <t>134328853</t>
-  </si>
-  <si>
-    <t>129439369</t>
-  </si>
-  <si>
-    <t>129316466</t>
-  </si>
-  <si>
-    <t>129587517</t>
-  </si>
-  <si>
-    <t>134243812</t>
-  </si>
-  <si>
-    <t>134143720</t>
-  </si>
-  <si>
-    <t>134329451</t>
-  </si>
-  <si>
-    <t>134289632</t>
-  </si>
-  <si>
-    <t>134379546</t>
-  </si>
-  <si>
-    <t>134360058</t>
-  </si>
-  <si>
-    <t>134328243</t>
-  </si>
-  <si>
-    <t>129671071</t>
-  </si>
-  <si>
-    <t>134378652</t>
-  </si>
-  <si>
-    <t>134337365</t>
-  </si>
-  <si>
-    <t>134399175</t>
-  </si>
-  <si>
-    <t>134289061</t>
-  </si>
-  <si>
-    <t>134395394</t>
-  </si>
-  <si>
-    <t>134388724</t>
-  </si>
-  <si>
     <t>134020026</t>
   </si>
   <si>
-    <t>134178491</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 11.09.2025</t>
+    <t>134328055</t>
+  </si>
+  <si>
+    <t>NUP Cancelamento 12.09.2025</t>
+  </si>
+  <si>
+    <t>134328176</t>
+  </si>
+  <si>
+    <t>134137701</t>
+  </si>
+  <si>
+    <t>134327868</t>
+  </si>
+  <si>
+    <t>134372332</t>
+  </si>
+  <si>
+    <t>134214498</t>
+  </si>
+  <si>
+    <t>133983609</t>
+  </si>
+  <si>
+    <t>134221255</t>
+  </si>
+  <si>
+    <t>134370120</t>
+  </si>
+  <si>
+    <t>129755187</t>
+  </si>
+  <si>
+    <t>134172386</t>
+  </si>
+  <si>
+    <t>129320366</t>
+  </si>
+  <si>
+    <t>134147432</t>
+  </si>
+  <si>
+    <t>129572425</t>
+  </si>
+  <si>
+    <t>134164348</t>
+  </si>
+  <si>
+    <t>134374670</t>
+  </si>
+  <si>
+    <t>129887582</t>
+  </si>
+  <si>
+    <t>129648781</t>
+  </si>
+  <si>
+    <t>134256105</t>
+  </si>
+  <si>
+    <t>134235955</t>
+  </si>
+  <si>
+    <t>134255312</t>
+  </si>
+  <si>
+    <t>134145391</t>
+  </si>
+  <si>
+    <t>129319316</t>
+  </si>
+  <si>
+    <t>129718137</t>
+  </si>
+  <si>
+    <t>134280143</t>
+  </si>
+  <si>
+    <t>134391642</t>
+  </si>
+  <si>
+    <t>134300788</t>
+  </si>
+  <si>
+    <t>134159233</t>
+  </si>
+  <si>
+    <t>134305172</t>
+  </si>
+  <si>
+    <t>129677033</t>
+  </si>
+  <si>
+    <t>134224883</t>
+  </si>
+  <si>
+    <t>134376182</t>
+  </si>
+  <si>
+    <t>134293168</t>
+  </si>
+  <si>
+    <t>134390711</t>
+  </si>
+  <si>
+    <t>134357107</t>
+  </si>
+  <si>
+    <t>134261021</t>
+  </si>
+  <si>
+    <t>134368867</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 12.09.2025</t>
   </si>
 </sst>
 </file>
@@ -558,7 +573,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -590,16 +605,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -607,16 +622,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -624,16 +639,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -641,16 +656,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -658,16 +673,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -675,16 +690,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -692,16 +707,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -709,16 +724,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -726,16 +741,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -743,16 +758,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -760,16 +775,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -777,16 +792,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -794,16 +809,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -811,16 +826,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -828,16 +843,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -845,16 +860,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -862,16 +877,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -879,16 +894,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -896,16 +911,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -913,16 +928,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -930,16 +945,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -947,16 +962,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -964,16 +979,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -981,16 +996,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -998,16 +1013,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1015,16 +1030,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1032,16 +1047,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1049,16 +1064,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1066,16 +1081,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1083,16 +1098,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1100,16 +1115,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1117,16 +1132,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1134,16 +1149,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1151,16 +1166,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1168,16 +1183,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1185,18 +1200,86 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{658F5E2D-9A24-479C-9CB1-1C0ED930DD9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD16390-3399-4302-9519-55C46D813FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="47">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,130 +54,121 @@
     <t>1070</t>
   </si>
   <si>
-    <t>134349868</t>
-  </si>
-  <si>
-    <t>133861138</t>
-  </si>
-  <si>
-    <t>134020026</t>
-  </si>
-  <si>
-    <t>134328055</t>
-  </si>
-  <si>
-    <t>NUP Cancelamento 12.09.2025</t>
-  </si>
-  <si>
-    <t>134328176</t>
-  </si>
-  <si>
-    <t>134137701</t>
-  </si>
-  <si>
-    <t>134327868</t>
-  </si>
-  <si>
-    <t>134372332</t>
-  </si>
-  <si>
     <t>134214498</t>
   </si>
   <si>
-    <t>133983609</t>
-  </si>
-  <si>
-    <t>134221255</t>
-  </si>
-  <si>
-    <t>134370120</t>
-  </si>
-  <si>
-    <t>129755187</t>
-  </si>
-  <si>
-    <t>134172386</t>
-  </si>
-  <si>
-    <t>129320366</t>
-  </si>
-  <si>
-    <t>134147432</t>
-  </si>
-  <si>
-    <t>129572425</t>
-  </si>
-  <si>
-    <t>134164348</t>
-  </si>
-  <si>
-    <t>134374670</t>
-  </si>
-  <si>
-    <t>129887582</t>
-  </si>
-  <si>
-    <t>129648781</t>
-  </si>
-  <si>
-    <t>134256105</t>
-  </si>
-  <si>
-    <t>134235955</t>
-  </si>
-  <si>
-    <t>134255312</t>
-  </si>
-  <si>
-    <t>134145391</t>
-  </si>
-  <si>
-    <t>129319316</t>
-  </si>
-  <si>
-    <t>129718137</t>
-  </si>
-  <si>
-    <t>134280143</t>
-  </si>
-  <si>
-    <t>134391642</t>
-  </si>
-  <si>
-    <t>134300788</t>
-  </si>
-  <si>
-    <t>134159233</t>
-  </si>
-  <si>
-    <t>134305172</t>
-  </si>
-  <si>
-    <t>129677033</t>
-  </si>
-  <si>
-    <t>134224883</t>
-  </si>
-  <si>
-    <t>134376182</t>
-  </si>
-  <si>
-    <t>134293168</t>
-  </si>
-  <si>
-    <t>134390711</t>
-  </si>
-  <si>
-    <t>134357107</t>
-  </si>
-  <si>
-    <t>134261021</t>
-  </si>
-  <si>
-    <t>134368867</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 12.09.2025</t>
+    <t>134328041</t>
+  </si>
+  <si>
+    <t>NUP Indexações 15.09.2025</t>
+  </si>
+  <si>
+    <t>133967919</t>
+  </si>
+  <si>
+    <t>129736243</t>
+  </si>
+  <si>
+    <t>134335530</t>
+  </si>
+  <si>
+    <t>134430990</t>
+  </si>
+  <si>
+    <t>134393801</t>
+  </si>
+  <si>
+    <t>134402071</t>
+  </si>
+  <si>
+    <t>129377148</t>
+  </si>
+  <si>
+    <t>129179263</t>
+  </si>
+  <si>
+    <t>129438418</t>
+  </si>
+  <si>
+    <t>134161549</t>
+  </si>
+  <si>
+    <t>134398866</t>
+  </si>
+  <si>
+    <t>134404468</t>
+  </si>
+  <si>
+    <t>129739927</t>
+  </si>
+  <si>
+    <t>129316474</t>
+  </si>
+  <si>
+    <t>134405589</t>
+  </si>
+  <si>
+    <t>134021078</t>
+  </si>
+  <si>
+    <t>129603844</t>
+  </si>
+  <si>
+    <t>134163083</t>
+  </si>
+  <si>
+    <t>129325471</t>
+  </si>
+  <si>
+    <t>134213751</t>
+  </si>
+  <si>
+    <t>134328126</t>
+  </si>
+  <si>
+    <t>129602222</t>
+  </si>
+  <si>
+    <t>134394013</t>
+  </si>
+  <si>
+    <t>134290008</t>
+  </si>
+  <si>
+    <t>134372061</t>
+  </si>
+  <si>
+    <t>129639212</t>
+  </si>
+  <si>
+    <t>129146161</t>
+  </si>
+  <si>
+    <t>134366299</t>
+  </si>
+  <si>
+    <t>134372068</t>
+  </si>
+  <si>
+    <t>134234883</t>
+  </si>
+  <si>
+    <t>134282935</t>
+  </si>
+  <si>
+    <t>134416980</t>
+  </si>
+  <si>
+    <t>133595415</t>
+  </si>
+  <si>
+    <t>132791342</t>
+  </si>
+  <si>
+    <t>134405948</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 15.09.2025</t>
   </si>
 </sst>
 </file>
@@ -573,7 +564,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -605,16 +596,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -622,16 +613,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -639,16 +630,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -656,16 +647,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -673,16 +664,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -690,16 +681,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -707,16 +698,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -724,16 +715,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -741,16 +732,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -758,16 +749,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -775,16 +766,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -792,16 +783,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -809,16 +800,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -826,16 +817,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -843,16 +834,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -860,16 +851,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -877,16 +868,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -894,16 +885,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -911,16 +902,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -928,16 +919,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -945,16 +936,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -962,16 +953,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -979,16 +970,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -996,16 +987,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1013,16 +1004,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1030,16 +1021,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1047,16 +1038,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1064,16 +1055,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1081,16 +1072,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1098,16 +1089,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1115,16 +1106,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1132,16 +1123,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1149,16 +1140,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1166,16 +1157,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1183,16 +1174,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1200,16 +1191,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1217,16 +1208,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1234,52 +1225,18 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E41" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD16390-3399-4302-9519-55C46D813FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F4747A-8545-432A-BFBB-34DC7B2EF0E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="67">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,121 +54,181 @@
     <t>1070</t>
   </si>
   <si>
-    <t>134214498</t>
-  </si>
-  <si>
-    <t>134328041</t>
-  </si>
-  <si>
-    <t>NUP Indexações 15.09.2025</t>
-  </si>
-  <si>
-    <t>133967919</t>
-  </si>
-  <si>
-    <t>129736243</t>
-  </si>
-  <si>
-    <t>134335530</t>
-  </si>
-  <si>
-    <t>134430990</t>
-  </si>
-  <si>
     <t>134393801</t>
   </si>
   <si>
-    <t>134402071</t>
-  </si>
-  <si>
-    <t>129377148</t>
-  </si>
-  <si>
-    <t>129179263</t>
-  </si>
-  <si>
-    <t>129438418</t>
-  </si>
-  <si>
-    <t>134161549</t>
-  </si>
-  <si>
-    <t>134398866</t>
-  </si>
-  <si>
-    <t>134404468</t>
-  </si>
-  <si>
-    <t>129739927</t>
-  </si>
-  <si>
-    <t>129316474</t>
-  </si>
-  <si>
-    <t>134405589</t>
-  </si>
-  <si>
-    <t>134021078</t>
-  </si>
-  <si>
-    <t>129603844</t>
-  </si>
-  <si>
-    <t>134163083</t>
-  </si>
-  <si>
-    <t>129325471</t>
-  </si>
-  <si>
-    <t>134213751</t>
-  </si>
-  <si>
-    <t>134328126</t>
-  </si>
-  <si>
-    <t>129602222</t>
-  </si>
-  <si>
-    <t>134394013</t>
-  </si>
-  <si>
-    <t>134290008</t>
-  </si>
-  <si>
-    <t>134372061</t>
-  </si>
-  <si>
-    <t>129639212</t>
-  </si>
-  <si>
-    <t>129146161</t>
-  </si>
-  <si>
-    <t>134366299</t>
-  </si>
-  <si>
-    <t>134372068</t>
-  </si>
-  <si>
-    <t>134234883</t>
-  </si>
-  <si>
-    <t>134282935</t>
-  </si>
-  <si>
-    <t>134416980</t>
-  </si>
-  <si>
-    <t>133595415</t>
-  </si>
-  <si>
-    <t>132791342</t>
-  </si>
-  <si>
-    <t>134405948</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 15.09.2025</t>
+    <t>134279905</t>
+  </si>
+  <si>
+    <t>NUP Indexações 16.09.2025</t>
+  </si>
+  <si>
+    <t>134294012</t>
+  </si>
+  <si>
+    <t>133819938</t>
+  </si>
+  <si>
+    <t>129566165</t>
+  </si>
+  <si>
+    <t>134256464</t>
+  </si>
+  <si>
+    <t>134289996</t>
+  </si>
+  <si>
+    <t>134300052</t>
+  </si>
+  <si>
+    <t>129319049</t>
+  </si>
+  <si>
+    <t>134279904</t>
+  </si>
+  <si>
+    <t>129503033</t>
+  </si>
+  <si>
+    <t>134350807</t>
+  </si>
+  <si>
+    <t>134398687</t>
+  </si>
+  <si>
+    <t>134281107</t>
+  </si>
+  <si>
+    <t>134285463</t>
+  </si>
+  <si>
+    <t>134443930</t>
+  </si>
+  <si>
+    <t>134416448</t>
+  </si>
+  <si>
+    <t>134443286</t>
+  </si>
+  <si>
+    <t>134354051</t>
+  </si>
+  <si>
+    <t>134091041</t>
+  </si>
+  <si>
+    <t>134349686</t>
+  </si>
+  <si>
+    <t>134349794</t>
+  </si>
+  <si>
+    <t>134165403</t>
+  </si>
+  <si>
+    <t>134403892</t>
+  </si>
+  <si>
+    <t>129508602</t>
+  </si>
+  <si>
+    <t>134493289</t>
+  </si>
+  <si>
+    <t>134349693</t>
+  </si>
+  <si>
+    <t>134401026</t>
+  </si>
+  <si>
+    <t>134399281</t>
+  </si>
+  <si>
+    <t>129416642</t>
+  </si>
+  <si>
+    <t>129638362</t>
+  </si>
+  <si>
+    <t>134349727</t>
+  </si>
+  <si>
+    <t>134171654</t>
+  </si>
+  <si>
+    <t>134287349</t>
+  </si>
+  <si>
+    <t>134330051</t>
+  </si>
+  <si>
+    <t>134340939</t>
+  </si>
+  <si>
+    <t>134471044</t>
+  </si>
+  <si>
+    <t>134403171</t>
+  </si>
+  <si>
+    <t>129372228</t>
+  </si>
+  <si>
+    <t>129628856</t>
+  </si>
+  <si>
+    <t>133994280</t>
+  </si>
+  <si>
+    <t>134369974</t>
+  </si>
+  <si>
+    <t>134258307</t>
+  </si>
+  <si>
+    <t>134402763</t>
+  </si>
+  <si>
+    <t>134362167</t>
+  </si>
+  <si>
+    <t>134403482</t>
+  </si>
+  <si>
+    <t>129570593</t>
+  </si>
+  <si>
+    <t>132248078</t>
+  </si>
+  <si>
+    <t>134290806</t>
+  </si>
+  <si>
+    <t>134234886</t>
+  </si>
+  <si>
+    <t>134404455</t>
+  </si>
+  <si>
+    <t>134401121</t>
+  </si>
+  <si>
+    <t>134284044</t>
+  </si>
+  <si>
+    <t>133072575</t>
+  </si>
+  <si>
+    <t>129494560</t>
+  </si>
+  <si>
+    <t>133859986</t>
+  </si>
+  <si>
+    <t>134164348</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 16.09.2025.xlsx</t>
   </si>
 </sst>
 </file>
@@ -564,7 +624,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -605,7 +665,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -622,7 +682,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -639,7 +699,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -656,7 +716,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -673,7 +733,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -690,7 +750,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -707,7 +767,7 @@
         <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -724,7 +784,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -741,7 +801,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -758,7 +818,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -775,7 +835,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -792,7 +852,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -809,7 +869,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -826,7 +886,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -843,7 +903,7 @@
         <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -860,7 +920,7 @@
         <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -877,7 +937,7 @@
         <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -894,7 +954,7 @@
         <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -911,7 +971,7 @@
         <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -928,7 +988,7 @@
         <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -945,7 +1005,7 @@
         <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -962,7 +1022,7 @@
         <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -979,7 +1039,7 @@
         <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -987,7 +1047,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
@@ -996,7 +1056,7 @@
         <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1004,7 +1064,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
@@ -1013,7 +1073,7 @@
         <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1021,7 +1081,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
@@ -1030,7 +1090,7 @@
         <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1038,7 +1098,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
@@ -1047,7 +1107,7 @@
         <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1055,7 +1115,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
@@ -1064,7 +1124,7 @@
         <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1072,7 +1132,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
@@ -1081,7 +1141,7 @@
         <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1089,7 +1149,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
@@ -1098,7 +1158,7 @@
         <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1106,7 +1166,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
@@ -1115,7 +1175,7 @@
         <v>10</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1123,7 +1183,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
@@ -1132,7 +1192,7 @@
         <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1140,7 +1200,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
@@ -1149,7 +1209,7 @@
         <v>10</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1157,7 +1217,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
@@ -1166,7 +1226,7 @@
         <v>10</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1174,7 +1234,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
@@ -1183,7 +1243,7 @@
         <v>10</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1191,7 +1251,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
@@ -1200,7 +1260,7 @@
         <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1208,7 +1268,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
@@ -1217,7 +1277,7 @@
         <v>10</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1225,7 +1285,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
@@ -1234,9 +1294,349 @@
         <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F4747A-8545-432A-BFBB-34DC7B2EF0E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A3D3C2-E50D-4CAD-9E00-4B2041F97F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -228,7 +228,7 @@
     <t>134164348</t>
   </si>
   <si>
-    <t>Allianz - Cancelamento 16.09.2025.xlsx</t>
+    <t>Allianz - Cancelamento 16.09.2025</t>
   </si>
 </sst>
 </file>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A3D3C2-E50D-4CAD-9E00-4B2041F97F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDDCCB1-4C83-4F4A-933F-19E5C03FF9AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="57">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,181 +54,151 @@
     <t>1070</t>
   </si>
   <si>
-    <t>134393801</t>
-  </si>
-  <si>
-    <t>134279905</t>
-  </si>
-  <si>
-    <t>NUP Indexações 16.09.2025</t>
-  </si>
-  <si>
-    <t>134294012</t>
-  </si>
-  <si>
     <t>133819938</t>
   </si>
   <si>
-    <t>129566165</t>
-  </si>
-  <si>
-    <t>134256464</t>
-  </si>
-  <si>
-    <t>134289996</t>
-  </si>
-  <si>
-    <t>134300052</t>
-  </si>
-  <si>
-    <t>129319049</t>
-  </si>
-  <si>
-    <t>134279904</t>
-  </si>
-  <si>
-    <t>129503033</t>
-  </si>
-  <si>
-    <t>134350807</t>
-  </si>
-  <si>
-    <t>134398687</t>
-  </si>
-  <si>
-    <t>134281107</t>
-  </si>
-  <si>
-    <t>134285463</t>
-  </si>
-  <si>
-    <t>134443930</t>
-  </si>
-  <si>
-    <t>134416448</t>
-  </si>
-  <si>
-    <t>134443286</t>
-  </si>
-  <si>
-    <t>134354051</t>
-  </si>
-  <si>
-    <t>134091041</t>
-  </si>
-  <si>
-    <t>134349686</t>
-  </si>
-  <si>
-    <t>134349794</t>
-  </si>
-  <si>
-    <t>134165403</t>
-  </si>
-  <si>
-    <t>134403892</t>
-  </si>
-  <si>
-    <t>129508602</t>
-  </si>
-  <si>
-    <t>134493289</t>
-  </si>
-  <si>
-    <t>134349693</t>
-  </si>
-  <si>
-    <t>134401026</t>
-  </si>
-  <si>
-    <t>134399281</t>
-  </si>
-  <si>
-    <t>129416642</t>
-  </si>
-  <si>
-    <t>129638362</t>
-  </si>
-  <si>
-    <t>134349727</t>
-  </si>
-  <si>
-    <t>134171654</t>
-  </si>
-  <si>
-    <t>134287349</t>
-  </si>
-  <si>
-    <t>134330051</t>
-  </si>
-  <si>
-    <t>134340939</t>
-  </si>
-  <si>
-    <t>134471044</t>
-  </si>
-  <si>
     <t>134403171</t>
   </si>
   <si>
-    <t>129372228</t>
-  </si>
-  <si>
-    <t>129628856</t>
-  </si>
-  <si>
-    <t>133994280</t>
-  </si>
-  <si>
-    <t>134369974</t>
-  </si>
-  <si>
-    <t>134258307</t>
-  </si>
-  <si>
     <t>134402763</t>
   </si>
   <si>
-    <t>134362167</t>
-  </si>
-  <si>
-    <t>134403482</t>
-  </si>
-  <si>
-    <t>129570593</t>
-  </si>
-  <si>
-    <t>132248078</t>
-  </si>
-  <si>
-    <t>134290806</t>
-  </si>
-  <si>
     <t>134234886</t>
   </si>
   <si>
-    <t>134404455</t>
-  </si>
-  <si>
-    <t>134401121</t>
-  </si>
-  <si>
-    <t>134284044</t>
-  </si>
-  <si>
-    <t>133072575</t>
-  </si>
-  <si>
-    <t>129494560</t>
-  </si>
-  <si>
-    <t>133859986</t>
-  </si>
-  <si>
-    <t>134164348</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 16.09.2025</t>
+    <t>Allianz - Cancelamento 17.09.2025</t>
+  </si>
+  <si>
+    <t>129385667</t>
+  </si>
+  <si>
+    <t>NUP Indexações 17.09.2025</t>
+  </si>
+  <si>
+    <t>134334091</t>
+  </si>
+  <si>
+    <t>134281403</t>
+  </si>
+  <si>
+    <t>134369222</t>
+  </si>
+  <si>
+    <t>134264981</t>
+  </si>
+  <si>
+    <t>134400578</t>
+  </si>
+  <si>
+    <t>129788781</t>
+  </si>
+  <si>
+    <t>129799586</t>
+  </si>
+  <si>
+    <t>129474513</t>
+  </si>
+  <si>
+    <t>134318246</t>
+  </si>
+  <si>
+    <t>134215801</t>
+  </si>
+  <si>
+    <t>129651254</t>
+  </si>
+  <si>
+    <t>134396254</t>
+  </si>
+  <si>
+    <t>129657783</t>
+  </si>
+  <si>
+    <t>134469190</t>
+  </si>
+  <si>
+    <t>133973261</t>
+  </si>
+  <si>
+    <t>134421442</t>
+  </si>
+  <si>
+    <t>134335823</t>
+  </si>
+  <si>
+    <t>134161615</t>
+  </si>
+  <si>
+    <t>134400171</t>
+  </si>
+  <si>
+    <t>134406609</t>
+  </si>
+  <si>
+    <t>134379626</t>
+  </si>
+  <si>
+    <t>129706351</t>
+  </si>
+  <si>
+    <t>134423679</t>
+  </si>
+  <si>
+    <t>134280325</t>
+  </si>
+  <si>
+    <t>129769864</t>
+  </si>
+  <si>
+    <t>129706851</t>
+  </si>
+  <si>
+    <t>129659267</t>
+  </si>
+  <si>
+    <t>134419808</t>
+  </si>
+  <si>
+    <t>134391349</t>
+  </si>
+  <si>
+    <t>129799589</t>
+  </si>
+  <si>
+    <t>129799463</t>
+  </si>
+  <si>
+    <t>129425158</t>
+  </si>
+  <si>
+    <t>129630132</t>
+  </si>
+  <si>
+    <t>134354255</t>
+  </si>
+  <si>
+    <t>134451389</t>
+  </si>
+  <si>
+    <t>134404295</t>
+  </si>
+  <si>
+    <t>134461520</t>
+  </si>
+  <si>
+    <t>134466249</t>
+  </si>
+  <si>
+    <t>134161656</t>
+  </si>
+  <si>
+    <t>130172699</t>
+  </si>
+  <si>
+    <t>134458947</t>
+  </si>
+  <si>
+    <t>133428566</t>
   </si>
 </sst>
 </file>
@@ -624,7 +594,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -656,16 +626,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -673,16 +643,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -690,16 +660,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -707,16 +677,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -724,16 +694,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -741,16 +711,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -758,16 +728,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -775,16 +745,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -792,16 +762,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -809,16 +779,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -826,16 +796,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -843,16 +813,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -860,16 +830,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -877,16 +847,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -894,16 +864,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -911,16 +881,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -928,16 +898,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -945,16 +915,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -962,16 +932,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -979,16 +949,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -996,16 +966,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1013,16 +983,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1030,16 +1000,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1047,16 +1017,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1064,16 +1034,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1081,16 +1051,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1098,16 +1068,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1115,16 +1085,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1132,16 +1102,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1149,16 +1119,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1166,16 +1136,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1183,16 +1153,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1200,16 +1170,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1217,16 +1187,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1234,16 +1204,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1251,16 +1221,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1268,16 +1238,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1285,16 +1255,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1302,16 +1272,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1319,16 +1289,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1336,16 +1306,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1353,16 +1323,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1376,10 +1346,10 @@
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1393,10 +1363,10 @@
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1410,10 +1380,10 @@
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1421,16 +1391,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1438,205 +1408,18 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E59" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDDCCB1-4C83-4F4A-933F-19E5C03FF9AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF592F7-7CC3-4D7A-8380-C0842C0D5422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="40">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,151 +54,100 @@
     <t>1070</t>
   </si>
   <si>
-    <t>133819938</t>
-  </si>
-  <si>
-    <t>134403171</t>
-  </si>
-  <si>
-    <t>134402763</t>
-  </si>
-  <si>
-    <t>134234886</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 17.09.2025</t>
-  </si>
-  <si>
-    <t>129385667</t>
-  </si>
-  <si>
-    <t>NUP Indexações 17.09.2025</t>
-  </si>
-  <si>
-    <t>134334091</t>
-  </si>
-  <si>
-    <t>134281403</t>
-  </si>
-  <si>
-    <t>134369222</t>
-  </si>
-  <si>
-    <t>134264981</t>
-  </si>
-  <si>
-    <t>134400578</t>
-  </si>
-  <si>
-    <t>129788781</t>
-  </si>
-  <si>
-    <t>129799586</t>
-  </si>
-  <si>
-    <t>129474513</t>
-  </si>
-  <si>
-    <t>134318246</t>
-  </si>
-  <si>
-    <t>134215801</t>
-  </si>
-  <si>
-    <t>129651254</t>
-  </si>
-  <si>
-    <t>134396254</t>
-  </si>
-  <si>
-    <t>129657783</t>
-  </si>
-  <si>
-    <t>134469190</t>
-  </si>
-  <si>
-    <t>133973261</t>
-  </si>
-  <si>
-    <t>134421442</t>
-  </si>
-  <si>
-    <t>134335823</t>
-  </si>
-  <si>
-    <t>134161615</t>
-  </si>
-  <si>
-    <t>134400171</t>
-  </si>
-  <si>
     <t>134406609</t>
   </si>
   <si>
-    <t>134379626</t>
-  </si>
-  <si>
-    <t>129706351</t>
-  </si>
-  <si>
-    <t>134423679</t>
-  </si>
-  <si>
-    <t>134280325</t>
-  </si>
-  <si>
-    <t>129769864</t>
-  </si>
-  <si>
-    <t>129706851</t>
-  </si>
-  <si>
-    <t>129659267</t>
-  </si>
-  <si>
-    <t>134419808</t>
-  </si>
-  <si>
-    <t>134391349</t>
-  </si>
-  <si>
-    <t>129799589</t>
-  </si>
-  <si>
-    <t>129799463</t>
-  </si>
-  <si>
-    <t>129425158</t>
-  </si>
-  <si>
-    <t>129630132</t>
-  </si>
-  <si>
-    <t>134354255</t>
-  </si>
-  <si>
-    <t>134451389</t>
-  </si>
-  <si>
-    <t>134404295</t>
-  </si>
-  <si>
-    <t>134461520</t>
-  </si>
-  <si>
-    <t>134466249</t>
-  </si>
-  <si>
-    <t>134161656</t>
-  </si>
-  <si>
-    <t>130172699</t>
-  </si>
-  <si>
-    <t>134458947</t>
-  </si>
-  <si>
-    <t>133428566</t>
+    <t>134378547</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 18.09.2025</t>
+  </si>
+  <si>
+    <t>134520873</t>
+  </si>
+  <si>
+    <t>134442327</t>
+  </si>
+  <si>
+    <t>129588573</t>
+  </si>
+  <si>
+    <t>134474595</t>
+  </si>
+  <si>
+    <t>134443465</t>
+  </si>
+  <si>
+    <t>134376135</t>
+  </si>
+  <si>
+    <t>134451322</t>
+  </si>
+  <si>
+    <t>134094310</t>
+  </si>
+  <si>
+    <t>134170051</t>
+  </si>
+  <si>
+    <t>134358908</t>
+  </si>
+  <si>
+    <t>134349709</t>
+  </si>
+  <si>
+    <t>134295508</t>
+  </si>
+  <si>
+    <t>134328097</t>
+  </si>
+  <si>
+    <t>134397921</t>
+  </si>
+  <si>
+    <t>134490302</t>
+  </si>
+  <si>
+    <t>129517469</t>
+  </si>
+  <si>
+    <t>134487892</t>
+  </si>
+  <si>
+    <t>134360604</t>
+  </si>
+  <si>
+    <t>134450150</t>
+  </si>
+  <si>
+    <t>130800995</t>
+  </si>
+  <si>
+    <t>129549819</t>
+  </si>
+  <si>
+    <t>134443134</t>
+  </si>
+  <si>
+    <t>134496427</t>
+  </si>
+  <si>
+    <t>134403642</t>
+  </si>
+  <si>
+    <t>134300238</t>
+  </si>
+  <si>
+    <t>129803363</t>
+  </si>
+  <si>
+    <t>133932723</t>
+  </si>
+  <si>
+    <t>134383363</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 18.09.2025</t>
   </si>
 </sst>
 </file>
@@ -594,7 +543,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -626,16 +575,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -643,16 +592,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -660,16 +609,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -677,16 +626,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -694,16 +643,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -711,16 +660,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -728,16 +677,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -745,16 +694,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -762,16 +711,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -779,16 +728,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -796,16 +745,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -813,16 +762,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -830,16 +779,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -847,16 +796,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -864,16 +813,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -881,16 +830,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -898,16 +847,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -915,16 +864,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -932,16 +881,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -949,16 +898,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -966,16 +915,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -983,16 +932,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1000,16 +949,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1017,16 +966,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1034,16 +983,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1051,16 +1000,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1068,16 +1017,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1085,16 +1034,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1102,16 +1051,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1119,307 +1068,18 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E48" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF592F7-7CC3-4D7A-8380-C0842C0D5422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA8BD9D-6231-4326-899F-7B72D46082BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="55">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,100 +54,145 @@
     <t>1070</t>
   </si>
   <si>
-    <t>134406609</t>
-  </si>
-  <si>
-    <t>134378547</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 18.09.2025</t>
-  </si>
-  <si>
-    <t>134520873</t>
-  </si>
-  <si>
-    <t>134442327</t>
-  </si>
-  <si>
-    <t>129588573</t>
-  </si>
-  <si>
-    <t>134474595</t>
-  </si>
-  <si>
-    <t>134443465</t>
-  </si>
-  <si>
-    <t>134376135</t>
-  </si>
-  <si>
-    <t>134451322</t>
-  </si>
-  <si>
-    <t>134094310</t>
-  </si>
-  <si>
-    <t>134170051</t>
-  </si>
-  <si>
-    <t>134358908</t>
-  </si>
-  <si>
-    <t>134349709</t>
-  </si>
-  <si>
-    <t>134295508</t>
-  </si>
-  <si>
-    <t>134328097</t>
-  </si>
-  <si>
-    <t>134397921</t>
-  </si>
-  <si>
-    <t>134490302</t>
-  </si>
-  <si>
-    <t>129517469</t>
-  </si>
-  <si>
-    <t>134487892</t>
-  </si>
-  <si>
-    <t>134360604</t>
-  </si>
-  <si>
-    <t>134450150</t>
-  </si>
-  <si>
-    <t>130800995</t>
-  </si>
-  <si>
-    <t>129549819</t>
-  </si>
-  <si>
-    <t>134443134</t>
-  </si>
-  <si>
-    <t>134496427</t>
-  </si>
-  <si>
-    <t>134403642</t>
-  </si>
-  <si>
-    <t>134300238</t>
-  </si>
-  <si>
-    <t>129803363</t>
-  </si>
-  <si>
-    <t>133932723</t>
-  </si>
-  <si>
-    <t>134383363</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 18.09.2025</t>
+    <t>Allianz - Cancelamento 19.09.2025</t>
+  </si>
+  <si>
+    <t>134328091</t>
+  </si>
+  <si>
+    <t>NUP Indexações 19.09.2025</t>
+  </si>
+  <si>
+    <t>134393891</t>
+  </si>
+  <si>
+    <t>134327861</t>
+  </si>
+  <si>
+    <t>130185722</t>
+  </si>
+  <si>
+    <t>129789520</t>
+  </si>
+  <si>
+    <t>134493601</t>
+  </si>
+  <si>
+    <t>133862346</t>
+  </si>
+  <si>
+    <t>130754593</t>
+  </si>
+  <si>
+    <t>134404976</t>
+  </si>
+  <si>
+    <t>129997629</t>
+  </si>
+  <si>
+    <t>129770694</t>
+  </si>
+  <si>
+    <t>134561292</t>
+  </si>
+  <si>
+    <t>134236293</t>
+  </si>
+  <si>
+    <t>133860036</t>
+  </si>
+  <si>
+    <t>134442276</t>
+  </si>
+  <si>
+    <t>129740478</t>
+  </si>
+  <si>
+    <t>134287257</t>
+  </si>
+  <si>
+    <t>130740339</t>
+  </si>
+  <si>
+    <t>129627968</t>
+  </si>
+  <si>
+    <t>134511725</t>
+  </si>
+  <si>
+    <t>133972271</t>
+  </si>
+  <si>
+    <t>134334129</t>
+  </si>
+  <si>
+    <t>134442371</t>
+  </si>
+  <si>
+    <t>134442380</t>
+  </si>
+  <si>
+    <t>134380292</t>
+  </si>
+  <si>
+    <t>134289016</t>
+  </si>
+  <si>
+    <t>134138762</t>
+  </si>
+  <si>
+    <t>129870085</t>
+  </si>
+  <si>
+    <t>134394644</t>
+  </si>
+  <si>
+    <t>129452115</t>
+  </si>
+  <si>
+    <t>134147206</t>
+  </si>
+  <si>
+    <t>134469704</t>
+  </si>
+  <si>
+    <t>134330754</t>
+  </si>
+  <si>
+    <t>134485456</t>
+  </si>
+  <si>
+    <t>134521309</t>
+  </si>
+  <si>
+    <t>134386138</t>
+  </si>
+  <si>
+    <t>133978917</t>
+  </si>
+  <si>
+    <t>134496238</t>
+  </si>
+  <si>
+    <t>134432163</t>
+  </si>
+  <si>
+    <t>134288494</t>
+  </si>
+  <si>
+    <t>134090939</t>
+  </si>
+  <si>
+    <t>134500969</t>
+  </si>
+  <si>
+    <t>134466361</t>
+  </si>
+  <si>
+    <t>130291524</t>
+  </si>
+  <si>
+    <t>134418914</t>
   </si>
 </sst>
 </file>
@@ -543,7 +588,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -584,7 +629,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -601,7 +646,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -618,7 +663,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -635,7 +680,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -652,7 +697,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -669,7 +714,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -686,7 +731,7 @@
         <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -703,7 +748,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -720,7 +765,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -737,7 +782,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -754,7 +799,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -771,7 +816,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -788,7 +833,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -805,7 +850,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -822,7 +867,7 @@
         <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -839,7 +884,7 @@
         <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -856,7 +901,7 @@
         <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -873,7 +918,7 @@
         <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -890,7 +935,7 @@
         <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -907,7 +952,7 @@
         <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -924,7 +969,7 @@
         <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -941,7 +986,7 @@
         <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -958,7 +1003,7 @@
         <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -975,7 +1020,7 @@
         <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -992,7 +1037,7 @@
         <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1009,7 +1054,7 @@
         <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1026,7 +1071,7 @@
         <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1043,7 +1088,7 @@
         <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1051,7 +1096,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
@@ -1060,7 +1105,7 @@
         <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1068,7 +1113,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
@@ -1077,9 +1122,281 @@
         <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA8BD9D-6231-4326-899F-7B72D46082BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A2EF90-C897-44A5-9353-770BD5B35629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="43">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,145 +54,109 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Allianz - Cancelamento 19.09.2025</t>
-  </si>
-  <si>
-    <t>134328091</t>
-  </si>
-  <si>
-    <t>NUP Indexações 19.09.2025</t>
-  </si>
-  <si>
-    <t>134393891</t>
-  </si>
-  <si>
-    <t>134327861</t>
-  </si>
-  <si>
-    <t>130185722</t>
-  </si>
-  <si>
-    <t>129789520</t>
-  </si>
-  <si>
-    <t>134493601</t>
-  </si>
-  <si>
-    <t>133862346</t>
-  </si>
-  <si>
-    <t>130754593</t>
-  </si>
-  <si>
-    <t>134404976</t>
-  </si>
-  <si>
-    <t>129997629</t>
-  </si>
-  <si>
-    <t>129770694</t>
-  </si>
-  <si>
-    <t>134561292</t>
-  </si>
-  <si>
-    <t>134236293</t>
-  </si>
-  <si>
-    <t>133860036</t>
-  </si>
-  <si>
-    <t>134442276</t>
-  </si>
-  <si>
-    <t>129740478</t>
-  </si>
-  <si>
-    <t>134287257</t>
-  </si>
-  <si>
-    <t>130740339</t>
-  </si>
-  <si>
-    <t>129627968</t>
-  </si>
-  <si>
-    <t>134511725</t>
-  </si>
-  <si>
-    <t>133972271</t>
-  </si>
-  <si>
-    <t>134334129</t>
-  </si>
-  <si>
-    <t>134442371</t>
-  </si>
-  <si>
-    <t>134442380</t>
-  </si>
-  <si>
-    <t>134380292</t>
-  </si>
-  <si>
-    <t>134289016</t>
-  </si>
-  <si>
-    <t>134138762</t>
-  </si>
-  <si>
-    <t>129870085</t>
-  </si>
-  <si>
-    <t>134394644</t>
-  </si>
-  <si>
-    <t>129452115</t>
-  </si>
-  <si>
-    <t>134147206</t>
-  </si>
-  <si>
-    <t>134469704</t>
-  </si>
-  <si>
-    <t>134330754</t>
-  </si>
-  <si>
-    <t>134485456</t>
-  </si>
-  <si>
-    <t>134521309</t>
-  </si>
-  <si>
-    <t>134386138</t>
-  </si>
-  <si>
-    <t>133978917</t>
-  </si>
-  <si>
-    <t>134496238</t>
-  </si>
-  <si>
-    <t>134432163</t>
-  </si>
-  <si>
-    <t>134288494</t>
-  </si>
-  <si>
-    <t>134090939</t>
-  </si>
-  <si>
-    <t>134500969</t>
-  </si>
-  <si>
-    <t>134466361</t>
-  </si>
-  <si>
-    <t>130291524</t>
-  </si>
-  <si>
-    <t>134418914</t>
+    <t>Allianz - Cancelamento 22.09.2025</t>
+  </si>
+  <si>
+    <t>134469064</t>
+  </si>
+  <si>
+    <t>NUP Indexações 22.09.2025</t>
+  </si>
+  <si>
+    <t>134372256</t>
+  </si>
+  <si>
+    <t>129141430</t>
+  </si>
+  <si>
+    <t>134399043</t>
+  </si>
+  <si>
+    <t>134441984</t>
+  </si>
+  <si>
+    <t>134465134</t>
+  </si>
+  <si>
+    <t>129404810</t>
+  </si>
+  <si>
+    <t>134511232</t>
+  </si>
+  <si>
+    <t>134512531</t>
+  </si>
+  <si>
+    <t>134492532</t>
+  </si>
+  <si>
+    <t>134275803</t>
+  </si>
+  <si>
+    <t>133751836</t>
+  </si>
+  <si>
+    <t>134488152</t>
+  </si>
+  <si>
+    <t>134090874</t>
+  </si>
+  <si>
+    <t>129949446</t>
+  </si>
+  <si>
+    <t>134264550</t>
+  </si>
+  <si>
+    <t>134490507</t>
+  </si>
+  <si>
+    <t>134264728</t>
+  </si>
+  <si>
+    <t>134511498</t>
+  </si>
+  <si>
+    <t>134401090</t>
+  </si>
+  <si>
+    <t>129405681</t>
+  </si>
+  <si>
+    <t>129590001</t>
+  </si>
+  <si>
+    <t>133972511</t>
+  </si>
+  <si>
+    <t>134466277</t>
+  </si>
+  <si>
+    <t>134444767</t>
+  </si>
+  <si>
+    <t>134442534</t>
+  </si>
+  <si>
+    <t>134542608</t>
+  </si>
+  <si>
+    <t>134516120</t>
+  </si>
+  <si>
+    <t>129343864</t>
+  </si>
+  <si>
+    <t>134359809</t>
+  </si>
+  <si>
+    <t>130858717</t>
+  </si>
+  <si>
+    <t>134498760</t>
+  </si>
+  <si>
+    <t>134521331</t>
   </si>
 </sst>
 </file>
@@ -588,7 +552,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -1176,227 +1140,6 @@
         <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A2EF90-C897-44A5-9353-770BD5B35629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DABFF06-C6D6-4F9B-A9C6-735B634AEE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="36">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,109 +54,88 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Allianz - Cancelamento 22.09.2025</t>
-  </si>
-  <si>
-    <t>134469064</t>
-  </si>
-  <si>
-    <t>NUP Indexações 22.09.2025</t>
-  </si>
-  <si>
-    <t>134372256</t>
-  </si>
-  <si>
-    <t>129141430</t>
-  </si>
-  <si>
-    <t>134399043</t>
-  </si>
-  <si>
-    <t>134441984</t>
-  </si>
-  <si>
-    <t>134465134</t>
-  </si>
-  <si>
-    <t>129404810</t>
-  </si>
-  <si>
-    <t>134511232</t>
-  </si>
-  <si>
-    <t>134512531</t>
-  </si>
-  <si>
-    <t>134492532</t>
-  </si>
-  <si>
-    <t>134275803</t>
-  </si>
-  <si>
-    <t>133751836</t>
-  </si>
-  <si>
-    <t>134488152</t>
-  </si>
-  <si>
-    <t>134090874</t>
-  </si>
-  <si>
-    <t>129949446</t>
-  </si>
-  <si>
-    <t>134264550</t>
-  </si>
-  <si>
-    <t>134490507</t>
-  </si>
-  <si>
-    <t>134264728</t>
-  </si>
-  <si>
-    <t>134511498</t>
-  </si>
-  <si>
-    <t>134401090</t>
-  </si>
-  <si>
-    <t>129405681</t>
-  </si>
-  <si>
-    <t>129590001</t>
-  </si>
-  <si>
-    <t>133972511</t>
-  </si>
-  <si>
-    <t>134466277</t>
-  </si>
-  <si>
-    <t>134444767</t>
-  </si>
-  <si>
-    <t>134442534</t>
-  </si>
-  <si>
-    <t>134542608</t>
-  </si>
-  <si>
-    <t>134516120</t>
-  </si>
-  <si>
-    <t>129343864</t>
-  </si>
-  <si>
-    <t>134359809</t>
-  </si>
-  <si>
-    <t>130858717</t>
-  </si>
-  <si>
-    <t>134498760</t>
-  </si>
-  <si>
-    <t>134521331</t>
+    <t>Allianz - Cancelamento 23.09.2025</t>
+  </si>
+  <si>
+    <t>129857823</t>
+  </si>
+  <si>
+    <t>NUP Indexações 23.09.2025</t>
+  </si>
+  <si>
+    <t>134519897</t>
+  </si>
+  <si>
+    <t>134444236</t>
+  </si>
+  <si>
+    <t>134560919</t>
+  </si>
+  <si>
+    <t>129812725</t>
+  </si>
+  <si>
+    <t>129728355</t>
+  </si>
+  <si>
+    <t>129469237</t>
+  </si>
+  <si>
+    <t>134421698</t>
+  </si>
+  <si>
+    <t>129449700</t>
+  </si>
+  <si>
+    <t>134251567</t>
+  </si>
+  <si>
+    <t>129812900</t>
+  </si>
+  <si>
+    <t>134378130</t>
+  </si>
+  <si>
+    <t>134445548</t>
+  </si>
+  <si>
+    <t>129608329</t>
+  </si>
+  <si>
+    <t>134585345</t>
+  </si>
+  <si>
+    <t>134511759</t>
+  </si>
+  <si>
+    <t>134561324</t>
+  </si>
+  <si>
+    <t>134395740</t>
+  </si>
+  <si>
+    <t>134511088</t>
+  </si>
+  <si>
+    <t>134512476</t>
+  </si>
+  <si>
+    <t>129542063</t>
+  </si>
+  <si>
+    <t>134280266</t>
+  </si>
+  <si>
+    <t>131972626</t>
+  </si>
+  <si>
+    <t>129936712</t>
+  </si>
+  <si>
+    <t>130494794</t>
+  </si>
+  <si>
+    <t>134460915</t>
   </si>
 </sst>
 </file>
@@ -552,7 +531,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -1021,125 +1000,6 @@
         <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DABFF06-C6D6-4F9B-A9C6-735B634AEE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0DF538-0478-4C93-8584-1EC1CCD4C2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="55">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,88 +54,145 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Allianz - Cancelamento 23.09.2025</t>
-  </si>
-  <si>
-    <t>129857823</t>
-  </si>
-  <si>
-    <t>NUP Indexações 23.09.2025</t>
-  </si>
-  <si>
-    <t>134519897</t>
-  </si>
-  <si>
-    <t>134444236</t>
-  </si>
-  <si>
-    <t>134560919</t>
-  </si>
-  <si>
-    <t>129812725</t>
-  </si>
-  <si>
-    <t>129728355</t>
-  </si>
-  <si>
-    <t>129469237</t>
-  </si>
-  <si>
-    <t>134421698</t>
-  </si>
-  <si>
-    <t>129449700</t>
-  </si>
-  <si>
-    <t>134251567</t>
-  </si>
-  <si>
-    <t>129812900</t>
-  </si>
-  <si>
-    <t>134378130</t>
-  </si>
-  <si>
-    <t>134445548</t>
-  </si>
-  <si>
-    <t>129608329</t>
-  </si>
-  <si>
-    <t>134585345</t>
-  </si>
-  <si>
-    <t>134511759</t>
-  </si>
-  <si>
-    <t>134561324</t>
-  </si>
-  <si>
-    <t>134395740</t>
-  </si>
-  <si>
-    <t>134511088</t>
-  </si>
-  <si>
-    <t>134512476</t>
-  </si>
-  <si>
     <t>129542063</t>
   </si>
   <si>
-    <t>134280266</t>
-  </si>
-  <si>
-    <t>131972626</t>
-  </si>
-  <si>
-    <t>129936712</t>
-  </si>
-  <si>
-    <t>130494794</t>
-  </si>
-  <si>
     <t>134460915</t>
+  </si>
+  <si>
+    <t>134603878</t>
+  </si>
+  <si>
+    <t>NUP Cancelamento 24.09.2025</t>
+  </si>
+  <si>
+    <t>133481091</t>
+  </si>
+  <si>
+    <t>134609443 </t>
+  </si>
+  <si>
+    <t>134404805</t>
+  </si>
+  <si>
+    <t>129629036</t>
+  </si>
+  <si>
+    <t>129906410</t>
+  </si>
+  <si>
+    <t>134450616</t>
+  </si>
+  <si>
+    <t>134561001</t>
+  </si>
+  <si>
+    <t>134511756</t>
+  </si>
+  <si>
+    <t>129850054</t>
+  </si>
+  <si>
+    <t>134518717</t>
+  </si>
+  <si>
+    <t>134393775</t>
+  </si>
+  <si>
+    <t>134561161</t>
+  </si>
+  <si>
+    <t>129865546</t>
+  </si>
+  <si>
+    <t>134465500</t>
+  </si>
+  <si>
+    <t>134393812</t>
+  </si>
+  <si>
+    <t>134520275</t>
+  </si>
+  <si>
+    <t>134517009</t>
+  </si>
+  <si>
+    <t>134442282</t>
+  </si>
+  <si>
+    <t>134328028</t>
+  </si>
+  <si>
+    <t>129549830</t>
+  </si>
+  <si>
+    <t>134565453</t>
+  </si>
+  <si>
+    <t>134586739</t>
+  </si>
+  <si>
+    <t>134369115</t>
+  </si>
+  <si>
+    <t>133582816</t>
+  </si>
+  <si>
+    <t>129855056</t>
+  </si>
+  <si>
+    <t>134450691</t>
+  </si>
+  <si>
+    <t>134522130</t>
+  </si>
+  <si>
+    <t>134373283</t>
+  </si>
+  <si>
+    <t>134597431</t>
+  </si>
+  <si>
+    <t>134169810</t>
+  </si>
+  <si>
+    <t>134572748</t>
+  </si>
+  <si>
+    <t>134520891</t>
+  </si>
+  <si>
+    <t>129809098</t>
+  </si>
+  <si>
+    <t>134561252</t>
+  </si>
+  <si>
+    <t>134465132</t>
+  </si>
+  <si>
+    <t>129614414</t>
+  </si>
+  <si>
+    <t>134398768</t>
+  </si>
+  <si>
+    <t>134561341</t>
+  </si>
+  <si>
+    <t>129412795</t>
+  </si>
+  <si>
+    <t>134393917</t>
+  </si>
+  <si>
+    <t>134511449</t>
+  </si>
+  <si>
+    <t>134170384</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 24.09.2025</t>
   </si>
 </sst>
 </file>
@@ -531,7 +588,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -563,16 +620,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -580,16 +637,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -597,16 +654,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -614,16 +671,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -631,16 +688,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -648,16 +705,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -665,16 +722,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -682,16 +739,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -699,16 +756,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -716,16 +773,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -733,16 +790,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -750,16 +807,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -767,16 +824,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -784,16 +841,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -801,16 +858,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -824,10 +881,10 @@
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -841,10 +898,10 @@
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -858,10 +915,10 @@
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -875,10 +932,10 @@
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -892,10 +949,10 @@
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -909,10 +966,10 @@
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -926,10 +983,10 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -943,10 +1000,10 @@
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -960,10 +1017,10 @@
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -977,10 +1034,10 @@
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -994,12 +1051,352 @@
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0DF538-0478-4C93-8584-1EC1CCD4C2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A59A99C6-2B8A-4F9C-BB62-C8FA2BFC0A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="46">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,145 +54,118 @@
     <t>1070</t>
   </si>
   <si>
-    <t>129542063</t>
-  </si>
-  <si>
-    <t>134460915</t>
-  </si>
-  <si>
-    <t>134603878</t>
-  </si>
-  <si>
-    <t>NUP Cancelamento 24.09.2025</t>
-  </si>
-  <si>
-    <t>133481091</t>
-  </si>
-  <si>
-    <t>134609443 </t>
-  </si>
-  <si>
-    <t>134404805</t>
-  </si>
-  <si>
-    <t>129629036</t>
-  </si>
-  <si>
-    <t>129906410</t>
-  </si>
-  <si>
-    <t>134450616</t>
-  </si>
-  <si>
-    <t>134561001</t>
-  </si>
-  <si>
-    <t>134511756</t>
-  </si>
-  <si>
-    <t>129850054</t>
-  </si>
-  <si>
-    <t>134518717</t>
-  </si>
-  <si>
-    <t>134393775</t>
-  </si>
-  <si>
-    <t>134561161</t>
-  </si>
-  <si>
-    <t>129865546</t>
-  </si>
-  <si>
-    <t>134465500</t>
-  </si>
-  <si>
-    <t>134393812</t>
-  </si>
-  <si>
-    <t>134520275</t>
-  </si>
-  <si>
-    <t>134517009</t>
-  </si>
-  <si>
-    <t>134442282</t>
-  </si>
-  <si>
-    <t>134328028</t>
-  </si>
-  <si>
-    <t>129549830</t>
-  </si>
-  <si>
-    <t>134565453</t>
-  </si>
-  <si>
-    <t>134586739</t>
-  </si>
-  <si>
-    <t>134369115</t>
-  </si>
-  <si>
-    <t>133582816</t>
-  </si>
-  <si>
-    <t>129855056</t>
-  </si>
-  <si>
-    <t>134450691</t>
-  </si>
-  <si>
-    <t>134522130</t>
-  </si>
-  <si>
-    <t>134373283</t>
-  </si>
-  <si>
-    <t>134597431</t>
-  </si>
-  <si>
-    <t>134169810</t>
-  </si>
-  <si>
-    <t>134572748</t>
-  </si>
-  <si>
-    <t>134520891</t>
-  </si>
-  <si>
-    <t>129809098</t>
-  </si>
-  <si>
-    <t>134561252</t>
-  </si>
-  <si>
-    <t>134465132</t>
-  </si>
-  <si>
-    <t>129614414</t>
-  </si>
-  <si>
-    <t>134398768</t>
-  </si>
-  <si>
-    <t>134561341</t>
-  </si>
-  <si>
-    <t>129412795</t>
-  </si>
-  <si>
-    <t>134393917</t>
-  </si>
-  <si>
-    <t>134511449</t>
-  </si>
-  <si>
-    <t>134170384</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 24.09.2025</t>
+    <t>134741008</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 06.10.2025</t>
+  </si>
+  <si>
+    <t>134775095</t>
+  </si>
+  <si>
+    <t>134759226</t>
+  </si>
+  <si>
+    <t>134511344</t>
+  </si>
+  <si>
+    <t>134754391</t>
+  </si>
+  <si>
+    <t>134650998</t>
+  </si>
+  <si>
+    <t>134639925</t>
+  </si>
+  <si>
+    <t>129640671</t>
+  </si>
+  <si>
+    <t>134465259</t>
+  </si>
+  <si>
+    <t>129665815</t>
+  </si>
+  <si>
+    <t>134681011</t>
+  </si>
+  <si>
+    <t>129973218</t>
+  </si>
+  <si>
+    <t>134647171</t>
+  </si>
+  <si>
+    <t>134635562</t>
+  </si>
+  <si>
+    <t>134561362</t>
+  </si>
+  <si>
+    <t>134471871</t>
+  </si>
+  <si>
+    <t>134760376</t>
+  </si>
+  <si>
+    <t>134700932</t>
+  </si>
+  <si>
+    <t>134630273</t>
+  </si>
+  <si>
+    <t>134718753</t>
+  </si>
+  <si>
+    <t>129929069</t>
+  </si>
+  <si>
+    <t>129850740</t>
+  </si>
+  <si>
+    <t>134222260</t>
+  </si>
+  <si>
+    <t>134487894</t>
+  </si>
+  <si>
+    <t>129646624</t>
+  </si>
+  <si>
+    <t>134514978</t>
+  </si>
+  <si>
+    <t>131929933</t>
+  </si>
+  <si>
+    <t>134745729</t>
+  </si>
+  <si>
+    <t>134680144</t>
+  </si>
+  <si>
+    <t>134515912</t>
+  </si>
+  <si>
+    <t>134517030</t>
+  </si>
+  <si>
+    <t>134757544</t>
+  </si>
+  <si>
+    <t>132904240</t>
+  </si>
+  <si>
+    <t>129668884</t>
+  </si>
+  <si>
+    <t>134606532</t>
+  </si>
+  <si>
+    <t>134748848</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 06.10.2025</t>
   </si>
 </sst>
 </file>
@@ -588,7 +561,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -620,16 +593,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -637,16 +610,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -654,16 +627,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -671,16 +644,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -688,16 +661,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -705,16 +678,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -722,16 +695,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -739,16 +712,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -756,16 +729,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -773,16 +746,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -790,16 +763,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -807,16 +780,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -824,16 +797,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -841,16 +814,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -858,16 +831,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -875,16 +848,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -892,16 +865,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -909,16 +882,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -926,16 +899,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -943,16 +916,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -960,16 +933,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -977,16 +950,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -994,16 +967,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1011,16 +984,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1028,16 +1001,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1045,16 +1018,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1062,16 +1035,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1079,16 +1052,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1096,16 +1069,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1113,16 +1086,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1130,16 +1103,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1147,16 +1120,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1164,16 +1137,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1181,16 +1154,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1198,16 +1171,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1215,188 +1188,18 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E47" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1414,31 +1217,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A59A99C6-2B8A-4F9C-BB62-C8FA2BFC0A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68F905E-5ADF-4362-B21C-C09F1FF8EC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="50">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,118 +54,130 @@
     <t>1070</t>
   </si>
   <si>
-    <t>134741008</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 06.10.2025</t>
-  </si>
-  <si>
-    <t>134775095</t>
-  </si>
-  <si>
-    <t>134759226</t>
-  </si>
-  <si>
-    <t>134511344</t>
-  </si>
-  <si>
-    <t>134754391</t>
-  </si>
-  <si>
-    <t>134650998</t>
-  </si>
-  <si>
-    <t>134639925</t>
-  </si>
-  <si>
-    <t>129640671</t>
-  </si>
-  <si>
-    <t>134465259</t>
-  </si>
-  <si>
-    <t>129665815</t>
-  </si>
-  <si>
-    <t>134681011</t>
-  </si>
-  <si>
-    <t>129973218</t>
-  </si>
-  <si>
-    <t>134647171</t>
-  </si>
-  <si>
-    <t>134635562</t>
-  </si>
-  <si>
-    <t>134561362</t>
-  </si>
-  <si>
-    <t>134471871</t>
-  </si>
-  <si>
-    <t>134760376</t>
-  </si>
-  <si>
-    <t>134700932</t>
-  </si>
-  <si>
-    <t>134630273</t>
-  </si>
-  <si>
-    <t>134718753</t>
-  </si>
-  <si>
-    <t>129929069</t>
-  </si>
-  <si>
-    <t>129850740</t>
-  </si>
-  <si>
-    <t>134222260</t>
-  </si>
-  <si>
-    <t>134487894</t>
-  </si>
-  <si>
-    <t>129646624</t>
-  </si>
-  <si>
-    <t>134514978</t>
-  </si>
-  <si>
-    <t>131929933</t>
-  </si>
-  <si>
-    <t>134745729</t>
-  </si>
-  <si>
-    <t>134680144</t>
-  </si>
-  <si>
-    <t>134515912</t>
-  </si>
-  <si>
-    <t>134517030</t>
-  </si>
-  <si>
-    <t>134757544</t>
-  </si>
-  <si>
-    <t>132904240</t>
-  </si>
-  <si>
-    <t>129668884</t>
-  </si>
-  <si>
-    <t>134606532</t>
-  </si>
-  <si>
-    <t>134748848</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 06.10.2025</t>
+    <t>134487891</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 07.10.2025</t>
+  </si>
+  <si>
+    <t>129722365</t>
+  </si>
+  <si>
+    <t>134746260</t>
+  </si>
+  <si>
+    <t>134442097</t>
+  </si>
+  <si>
+    <t>134800087</t>
+  </si>
+  <si>
+    <t>129843424</t>
+  </si>
+  <si>
+    <t>129652160</t>
+  </si>
+  <si>
+    <t>134741219</t>
+  </si>
+  <si>
+    <t>134742574</t>
+  </si>
+  <si>
+    <t>134718739</t>
+  </si>
+  <si>
+    <t>134683049</t>
+  </si>
+  <si>
+    <t>129483950</t>
+  </si>
+  <si>
+    <t>129724078</t>
+  </si>
+  <si>
+    <t>134728235</t>
+  </si>
+  <si>
+    <t>134740755</t>
+  </si>
+  <si>
+    <t>134830300</t>
+  </si>
+  <si>
+    <t>130064407</t>
+  </si>
+  <si>
+    <t>134721190</t>
+  </si>
+  <si>
+    <t>134789303</t>
+  </si>
+  <si>
+    <t>134829864</t>
+  </si>
+  <si>
+    <t>134718740</t>
+  </si>
+  <si>
+    <t>134561205</t>
+  </si>
+  <si>
+    <t>130004793</t>
+  </si>
+  <si>
+    <t>129736229</t>
+  </si>
+  <si>
+    <t>134696415</t>
+  </si>
+  <si>
+    <t>129851493</t>
+  </si>
+  <si>
+    <t>134565933</t>
+  </si>
+  <si>
+    <t>134759099</t>
+  </si>
+  <si>
+    <t>134677986</t>
+  </si>
+  <si>
+    <t>129653137</t>
+  </si>
+  <si>
+    <t>134379493</t>
+  </si>
+  <si>
+    <t>134789206</t>
+  </si>
+  <si>
+    <t>129772214</t>
+  </si>
+  <si>
+    <t>134627655</t>
+  </si>
+  <si>
+    <t>129926336</t>
+  </si>
+  <si>
+    <t>134740919</t>
+  </si>
+  <si>
+    <t>131618898</t>
+  </si>
+  <si>
+    <t>134693268</t>
+  </si>
+  <si>
+    <t>129683866</t>
+  </si>
+  <si>
+    <t>134222759</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 07.10.2025</t>
   </si>
 </sst>
 </file>
@@ -561,7 +573,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -602,7 +614,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -619,7 +631,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -636,7 +648,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -653,7 +665,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -670,7 +682,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -687,7 +699,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -704,7 +716,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -721,7 +733,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -738,7 +750,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -755,7 +767,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -772,7 +784,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -789,7 +801,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -806,7 +818,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -823,7 +835,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -840,7 +852,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -857,7 +869,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -874,7 +886,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -891,7 +903,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -908,7 +920,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -925,7 +937,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -942,7 +954,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -959,7 +971,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -976,7 +988,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -993,7 +1005,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1010,7 +1022,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1027,7 +1039,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1044,7 +1056,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1061,7 +1073,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1078,7 +1090,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1095,7 +1107,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1112,7 +1124,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1129,7 +1141,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1146,7 +1158,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1163,7 +1175,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1180,7 +1192,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1197,9 +1209,94 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1217,31 +1314,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68F905E-5ADF-4362-B21C-C09F1FF8EC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F158E47E-F08A-4B84-AC41-40D9ED67701B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="46">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,130 +54,118 @@
     <t>1070</t>
   </si>
   <si>
-    <t>134487891</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 07.10.2025</t>
-  </si>
-  <si>
-    <t>129722365</t>
-  </si>
-  <si>
-    <t>134746260</t>
-  </si>
-  <si>
-    <t>134442097</t>
-  </si>
-  <si>
-    <t>134800087</t>
-  </si>
-  <si>
-    <t>129843424</t>
-  </si>
-  <si>
-    <t>129652160</t>
-  </si>
-  <si>
-    <t>134741219</t>
-  </si>
-  <si>
-    <t>134742574</t>
-  </si>
-  <si>
-    <t>134718739</t>
-  </si>
-  <si>
-    <t>134683049</t>
-  </si>
-  <si>
-    <t>129483950</t>
-  </si>
-  <si>
-    <t>129724078</t>
-  </si>
-  <si>
-    <t>134728235</t>
-  </si>
-  <si>
-    <t>134740755</t>
-  </si>
-  <si>
-    <t>134830300</t>
-  </si>
-  <si>
-    <t>130064407</t>
-  </si>
-  <si>
-    <t>134721190</t>
-  </si>
-  <si>
-    <t>134789303</t>
-  </si>
-  <si>
-    <t>134829864</t>
-  </si>
-  <si>
-    <t>134718740</t>
-  </si>
-  <si>
-    <t>134561205</t>
-  </si>
-  <si>
-    <t>130004793</t>
-  </si>
-  <si>
-    <t>129736229</t>
-  </si>
-  <si>
-    <t>134696415</t>
-  </si>
-  <si>
-    <t>129851493</t>
-  </si>
-  <si>
-    <t>134565933</t>
-  </si>
-  <si>
-    <t>134759099</t>
-  </si>
-  <si>
-    <t>134677986</t>
-  </si>
-  <si>
-    <t>129653137</t>
-  </si>
-  <si>
-    <t>134379493</t>
-  </si>
-  <si>
-    <t>134789206</t>
-  </si>
-  <si>
-    <t>129772214</t>
-  </si>
-  <si>
-    <t>134627655</t>
-  </si>
-  <si>
-    <t>129926336</t>
-  </si>
-  <si>
-    <t>134740919</t>
-  </si>
-  <si>
-    <t>131618898</t>
-  </si>
-  <si>
-    <t>134693268</t>
-  </si>
-  <si>
-    <t>129683866</t>
-  </si>
-  <si>
-    <t>134222759</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 07.10.2025</t>
+    <t>134789222</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 08.10.2025</t>
+  </si>
+  <si>
+    <t>134797684</t>
+  </si>
+  <si>
+    <t>130186297</t>
+  </si>
+  <si>
+    <t>134674399</t>
+  </si>
+  <si>
+    <t>134740650</t>
+  </si>
+  <si>
+    <t>129851470</t>
+  </si>
+  <si>
+    <t>134748329</t>
+  </si>
+  <si>
+    <t>134830816</t>
+  </si>
+  <si>
+    <t>134759616</t>
+  </si>
+  <si>
+    <t>134587195</t>
+  </si>
+  <si>
+    <t>134674316</t>
+  </si>
+  <si>
+    <t>134562209</t>
+  </si>
+  <si>
+    <t>134742290</t>
+  </si>
+  <si>
+    <t>130029551</t>
+  </si>
+  <si>
+    <t>134615250</t>
+  </si>
+  <si>
+    <t>134566451</t>
+  </si>
+  <si>
+    <t>134749663</t>
+  </si>
+  <si>
+    <t>134615613</t>
+  </si>
+  <si>
+    <t>134627851</t>
+  </si>
+  <si>
+    <t>134752726</t>
+  </si>
+  <si>
+    <t>134789292</t>
+  </si>
+  <si>
+    <t>134631620</t>
+  </si>
+  <si>
+    <t>134705705</t>
+  </si>
+  <si>
+    <t>134716592</t>
+  </si>
+  <si>
+    <t>134770798</t>
+  </si>
+  <si>
+    <t>129763087</t>
+  </si>
+  <si>
+    <t>134562269</t>
+  </si>
+  <si>
+    <t>134748562</t>
+  </si>
+  <si>
+    <t>134191294</t>
+  </si>
+  <si>
+    <t>132369209</t>
+  </si>
+  <si>
+    <t>134442090</t>
+  </si>
+  <si>
+    <t>134700416</t>
+  </si>
+  <si>
+    <t>134698450</t>
+  </si>
+  <si>
+    <t>134833192</t>
+  </si>
+  <si>
+    <t>130649986</t>
+  </si>
+  <si>
+    <t>133636112</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 08.10.2025</t>
   </si>
 </sst>
 </file>
@@ -573,7 +561,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -614,7 +602,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -631,7 +619,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -648,7 +636,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -665,7 +653,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -682,7 +670,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -699,7 +687,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -716,7 +704,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -733,7 +721,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -750,7 +738,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -767,7 +755,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -784,7 +772,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -801,7 +789,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -818,7 +806,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -835,7 +823,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -852,7 +840,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -869,7 +857,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -886,7 +874,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -903,7 +891,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -920,7 +908,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -937,7 +925,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -954,7 +942,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -971,7 +959,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -988,7 +976,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1005,7 +993,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1022,7 +1010,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1039,7 +1027,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1056,7 +1044,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1073,7 +1061,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1090,7 +1078,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1107,7 +1095,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1124,7 +1112,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1132,7 +1120,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
@@ -1141,7 +1129,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1149,7 +1137,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
@@ -1158,7 +1146,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1166,7 +1154,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
@@ -1175,7 +1163,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1183,7 +1171,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
@@ -1192,7 +1180,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1200,7 +1188,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
@@ -1209,7 +1197,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1217,7 +1205,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
@@ -1226,77 +1214,9 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E42" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1314,31 +1234,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F158E47E-F08A-4B84-AC41-40D9ED67701B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8FBBA7-2761-4D8E-9936-17A980F936F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="41">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -45,127 +45,112 @@
     <t xml:space="preserve">Modelo/Descrição </t>
   </si>
   <si>
-    <t xml:space="preserve">Anexo </t>
-  </si>
-  <si>
     <t>Processar</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>134789222</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 08.10.2025</t>
-  </si>
-  <si>
-    <t>134797684</t>
-  </si>
-  <si>
-    <t>130186297</t>
-  </si>
-  <si>
-    <t>134674399</t>
-  </si>
-  <si>
-    <t>134740650</t>
-  </si>
-  <si>
-    <t>129851470</t>
-  </si>
-  <si>
-    <t>134748329</t>
-  </si>
-  <si>
-    <t>134830816</t>
-  </si>
-  <si>
-    <t>134759616</t>
-  </si>
-  <si>
-    <t>134587195</t>
-  </si>
-  <si>
-    <t>134674316</t>
-  </si>
-  <si>
-    <t>134562209</t>
-  </si>
-  <si>
-    <t>134742290</t>
-  </si>
-  <si>
-    <t>130029551</t>
-  </si>
-  <si>
-    <t>134615250</t>
-  </si>
-  <si>
-    <t>134566451</t>
-  </si>
-  <si>
-    <t>134749663</t>
-  </si>
-  <si>
-    <t>134615613</t>
-  </si>
-  <si>
-    <t>134627851</t>
-  </si>
-  <si>
-    <t>134752726</t>
-  </si>
-  <si>
-    <t>134789292</t>
-  </si>
-  <si>
-    <t>134631620</t>
-  </si>
-  <si>
-    <t>134705705</t>
-  </si>
-  <si>
-    <t>134716592</t>
-  </si>
-  <si>
-    <t>134770798</t>
-  </si>
-  <si>
-    <t>129763087</t>
-  </si>
-  <si>
-    <t>134562269</t>
-  </si>
-  <si>
-    <t>134748562</t>
-  </si>
-  <si>
-    <t>134191294</t>
-  </si>
-  <si>
-    <t>132369209</t>
-  </si>
-  <si>
-    <t>134442090</t>
-  </si>
-  <si>
-    <t>134700416</t>
-  </si>
-  <si>
-    <t>134698450</t>
-  </si>
-  <si>
-    <t>134833192</t>
-  </si>
-  <si>
-    <t>130649986</t>
-  </si>
-  <si>
-    <t>133636112</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 08.10.2025</t>
+    <t>134724588</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 10.10.2025</t>
+  </si>
+  <si>
+    <t>134852233</t>
+  </si>
+  <si>
+    <t>129924150</t>
+  </si>
+  <si>
+    <t>134675342</t>
+  </si>
+  <si>
+    <t>134706757</t>
+  </si>
+  <si>
+    <t>134675259</t>
+  </si>
+  <si>
+    <t>134511234</t>
+  </si>
+  <si>
+    <t>134608782</t>
+  </si>
+  <si>
+    <t>134606070</t>
+  </si>
+  <si>
+    <t>134789363</t>
+  </si>
+  <si>
+    <t>129681327</t>
+  </si>
+  <si>
+    <t>134397406</t>
+  </si>
+  <si>
+    <t>129819776</t>
+  </si>
+  <si>
+    <t>134831551</t>
+  </si>
+  <si>
+    <t>130134751</t>
+  </si>
+  <si>
+    <t>134584174</t>
+  </si>
+  <si>
+    <t>134611536</t>
+  </si>
+  <si>
+    <t>134704565</t>
+  </si>
+  <si>
+    <t>134643280</t>
+  </si>
+  <si>
+    <t>134836207</t>
+  </si>
+  <si>
+    <t>134216265</t>
+  </si>
+  <si>
+    <t>130086579</t>
+  </si>
+  <si>
+    <t>129890045</t>
+  </si>
+  <si>
+    <t>134740525</t>
+  </si>
+  <si>
+    <t>134724187</t>
+  </si>
+  <si>
+    <t>129665125</t>
+  </si>
+  <si>
+    <t>134834516</t>
+  </si>
+  <si>
+    <t>134696622</t>
+  </si>
+  <si>
+    <t>134811284</t>
+  </si>
+  <si>
+    <t>134631743</t>
+  </si>
+  <si>
+    <t>134611067</t>
+  </si>
+  <si>
+    <t>133953754</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 10.10.2025</t>
   </si>
 </sst>
 </file>
@@ -561,7 +546,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -582,7 +567,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>0</v>
@@ -593,631 +578,546 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1234,31 +1134,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8FBBA7-2761-4D8E-9936-17A980F936F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FEF2575-C210-4DF3-8A68-591BDE6718A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="54">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,106 +51,145 @@
     <t>1070</t>
   </si>
   <si>
-    <t>134724588</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 10.10.2025</t>
-  </si>
-  <si>
-    <t>134852233</t>
-  </si>
-  <si>
-    <t>129924150</t>
-  </si>
-  <si>
-    <t>134675342</t>
-  </si>
-  <si>
-    <t>134706757</t>
-  </si>
-  <si>
-    <t>134675259</t>
-  </si>
-  <si>
-    <t>134511234</t>
-  </si>
-  <si>
-    <t>134608782</t>
-  </si>
-  <si>
-    <t>134606070</t>
-  </si>
-  <si>
-    <t>134789363</t>
-  </si>
-  <si>
-    <t>129681327</t>
-  </si>
-  <si>
-    <t>134397406</t>
-  </si>
-  <si>
-    <t>129819776</t>
-  </si>
-  <si>
-    <t>134831551</t>
-  </si>
-  <si>
-    <t>130134751</t>
-  </si>
-  <si>
-    <t>134584174</t>
-  </si>
-  <si>
-    <t>134611536</t>
-  </si>
-  <si>
-    <t>134704565</t>
-  </si>
-  <si>
-    <t>134643280</t>
-  </si>
-  <si>
-    <t>134836207</t>
-  </si>
-  <si>
-    <t>134216265</t>
-  </si>
-  <si>
-    <t>130086579</t>
-  </si>
-  <si>
-    <t>129890045</t>
-  </si>
-  <si>
-    <t>134740525</t>
-  </si>
-  <si>
-    <t>134724187</t>
-  </si>
-  <si>
-    <t>129665125</t>
-  </si>
-  <si>
-    <t>134834516</t>
-  </si>
-  <si>
-    <t>134696622</t>
-  </si>
-  <si>
     <t>134811284</t>
   </si>
   <si>
-    <t>134631743</t>
-  </si>
-  <si>
-    <t>134611067</t>
-  </si>
-  <si>
-    <t>133953754</t>
-  </si>
-  <si>
     <t>Allianz - Cancelamento 10.10.2025</t>
+  </si>
+  <si>
+    <t>134808129</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 13.10.2025</t>
+  </si>
+  <si>
+    <t>134918400</t>
+  </si>
+  <si>
+    <t>129862585</t>
+  </si>
+  <si>
+    <t>129817435</t>
+  </si>
+  <si>
+    <t>130111327</t>
+  </si>
+  <si>
+    <t>134855824</t>
+  </si>
+  <si>
+    <t>134720998</t>
+  </si>
+  <si>
+    <t>134817346</t>
+  </si>
+  <si>
+    <t>134853191</t>
+  </si>
+  <si>
+    <t>134897150</t>
+  </si>
+  <si>
+    <t>130000313</t>
+  </si>
+  <si>
+    <t>129925764</t>
+  </si>
+  <si>
+    <t>129792674</t>
+  </si>
+  <si>
+    <t>134832064</t>
+  </si>
+  <si>
+    <t>134656494</t>
+  </si>
+  <si>
+    <t>133712252</t>
+  </si>
+  <si>
+    <t>134852350</t>
+  </si>
+  <si>
+    <t>134718813</t>
+  </si>
+  <si>
+    <t>134515318</t>
+  </si>
+  <si>
+    <t>134810746</t>
+  </si>
+  <si>
+    <t>129717315</t>
+  </si>
+  <si>
+    <t>129867976</t>
+  </si>
+  <si>
+    <t>134616354</t>
+  </si>
+  <si>
+    <t>130097063</t>
+  </si>
+  <si>
+    <t>134641862</t>
+  </si>
+  <si>
+    <t>134789281</t>
+  </si>
+  <si>
+    <t>134588132</t>
+  </si>
+  <si>
+    <t>134852316</t>
+  </si>
+  <si>
+    <t>129879949</t>
+  </si>
+  <si>
+    <t>134875744</t>
+  </si>
+  <si>
+    <t>134844875</t>
+  </si>
+  <si>
+    <t>134898420</t>
+  </si>
+  <si>
+    <t>134678799</t>
+  </si>
+  <si>
+    <t>134642404</t>
+  </si>
+  <si>
+    <t>134868191</t>
+  </si>
+  <si>
+    <t>134765510</t>
+  </si>
+  <si>
+    <t>134719056</t>
+  </si>
+  <si>
+    <t>134758174</t>
+  </si>
+  <si>
+    <t>134093483</t>
+  </si>
+  <si>
+    <t>134859553</t>
+  </si>
+  <si>
+    <t>131182685</t>
+  </si>
+  <si>
+    <t>134561293</t>
+  </si>
+  <si>
+    <t>134467425</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 13.10.2025</t>
   </si>
 </sst>
 </file>
@@ -546,7 +585,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -567,7 +606,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>0</v>
@@ -578,16 +617,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -595,16 +634,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -612,16 +651,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -629,16 +668,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -646,16 +685,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -663,16 +702,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -680,16 +719,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -697,16 +736,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -714,16 +753,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -731,16 +770,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -748,16 +787,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -765,16 +804,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -782,16 +821,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>5</v>
@@ -799,16 +838,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>5</v>
@@ -816,16 +855,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>5</v>
@@ -833,16 +872,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>5</v>
@@ -850,16 +889,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>5</v>
@@ -867,16 +906,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>5</v>
@@ -884,16 +923,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>5</v>
@@ -901,16 +940,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>5</v>
@@ -918,16 +957,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>5</v>
@@ -935,16 +974,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>5</v>
@@ -952,16 +991,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>5</v>
@@ -969,16 +1008,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>5</v>
@@ -986,16 +1025,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>5</v>
@@ -1003,16 +1042,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>5</v>
@@ -1020,16 +1059,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>5</v>
@@ -1037,16 +1076,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>5</v>
@@ -1054,16 +1093,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>5</v>
@@ -1071,16 +1110,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>5</v>
@@ -1088,16 +1127,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>5</v>
@@ -1105,18 +1144,239 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E33" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1134,31 +1394,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FEF2575-C210-4DF3-8A68-591BDE6718A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C461C1D-75C5-453A-822E-C925E2EE60F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="102">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,145 +51,289 @@
     <t>1070</t>
   </si>
   <si>
-    <t>134811284</t>
-  </si>
-  <si>
     <t>Allianz - Cancelamento 10.10.2025</t>
   </si>
   <si>
-    <t>134808129</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 13.10.2025</t>
-  </si>
-  <si>
-    <t>134918400</t>
-  </si>
-  <si>
-    <t>129862585</t>
-  </si>
-  <si>
-    <t>129817435</t>
-  </si>
-  <si>
-    <t>130111327</t>
-  </si>
-  <si>
-    <t>134855824</t>
-  </si>
-  <si>
-    <t>134720998</t>
-  </si>
-  <si>
-    <t>134817346</t>
-  </si>
-  <si>
-    <t>134853191</t>
-  </si>
-  <si>
-    <t>134897150</t>
-  </si>
-  <si>
-    <t>130000313</t>
-  </si>
-  <si>
-    <t>129925764</t>
-  </si>
-  <si>
-    <t>129792674</t>
-  </si>
-  <si>
-    <t>134832064</t>
-  </si>
-  <si>
-    <t>134656494</t>
-  </si>
-  <si>
-    <t>133712252</t>
-  </si>
-  <si>
-    <t>134852350</t>
-  </si>
-  <si>
-    <t>134718813</t>
-  </si>
-  <si>
-    <t>134515318</t>
-  </si>
-  <si>
-    <t>134810746</t>
-  </si>
-  <si>
-    <t>129717315</t>
-  </si>
-  <si>
-    <t>129867976</t>
-  </si>
-  <si>
-    <t>134616354</t>
-  </si>
-  <si>
-    <t>130097063</t>
-  </si>
-  <si>
-    <t>134641862</t>
-  </si>
-  <si>
-    <t>134789281</t>
-  </si>
-  <si>
-    <t>134588132</t>
-  </si>
-  <si>
-    <t>134852316</t>
-  </si>
-  <si>
-    <t>129879949</t>
-  </si>
-  <si>
-    <t>134875744</t>
-  </si>
-  <si>
-    <t>134844875</t>
-  </si>
-  <si>
-    <t>134898420</t>
-  </si>
-  <si>
-    <t>134678799</t>
-  </si>
-  <si>
-    <t>134642404</t>
-  </si>
-  <si>
-    <t>134868191</t>
-  </si>
-  <si>
-    <t>134765510</t>
-  </si>
-  <si>
-    <t>134719056</t>
-  </si>
-  <si>
-    <t>134758174</t>
-  </si>
-  <si>
-    <t>134093483</t>
-  </si>
-  <si>
     <t>134859553</t>
   </si>
   <si>
-    <t>131182685</t>
-  </si>
-  <si>
-    <t>134561293</t>
-  </si>
-  <si>
-    <t>134467425</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 13.10.2025</t>
+    <t>134747872</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 14.10.2025</t>
+  </si>
+  <si>
+    <t>130095508</t>
+  </si>
+  <si>
+    <t>134789918</t>
+  </si>
+  <si>
+    <t>134699292</t>
+  </si>
+  <si>
+    <t>134746733</t>
+  </si>
+  <si>
+    <t>134769633</t>
+  </si>
+  <si>
+    <t>134748446</t>
+  </si>
+  <si>
+    <t>129662823</t>
+  </si>
+  <si>
+    <t>134811751</t>
+  </si>
+  <si>
+    <t>134791148</t>
+  </si>
+  <si>
+    <t>134681936</t>
+  </si>
+  <si>
+    <t>129752196</t>
+  </si>
+  <si>
+    <t>134586179</t>
+  </si>
+  <si>
+    <t>134860006</t>
+  </si>
+  <si>
+    <t>134904106</t>
+  </si>
+  <si>
+    <t>134718800</t>
+  </si>
+  <si>
+    <t>134696334</t>
+  </si>
+  <si>
+    <t>134759916</t>
+  </si>
+  <si>
+    <t>134897266</t>
+  </si>
+  <si>
+    <t>15900638</t>
+  </si>
+  <si>
+    <t>134900492</t>
+  </si>
+  <si>
+    <t>130056551</t>
+  </si>
+  <si>
+    <t>134897128</t>
+  </si>
+  <si>
+    <t>134817449</t>
+  </si>
+  <si>
+    <t>130147718</t>
+  </si>
+  <si>
+    <t>130150963</t>
+  </si>
+  <si>
+    <t>134935090</t>
+  </si>
+  <si>
+    <t>134335110</t>
+  </si>
+  <si>
+    <t>134930925</t>
+  </si>
+  <si>
+    <t>134852372</t>
+  </si>
+  <si>
+    <t>134696688</t>
+  </si>
+  <si>
+    <t>134852411</t>
+  </si>
+  <si>
+    <t>129916097</t>
+  </si>
+  <si>
+    <t>130113828</t>
+  </si>
+  <si>
+    <t>134858363</t>
+  </si>
+  <si>
+    <t>134863611</t>
+  </si>
+  <si>
+    <t>130139501</t>
+  </si>
+  <si>
+    <t>134831941</t>
+  </si>
+  <si>
+    <t>134909691</t>
+  </si>
+  <si>
+    <t>134922632</t>
+  </si>
+  <si>
+    <t>129838914</t>
+  </si>
+  <si>
+    <t>133798386</t>
+  </si>
+  <si>
+    <t>134920113</t>
+  </si>
+  <si>
+    <t>134718773</t>
+  </si>
+  <si>
+    <t>134675245</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 14.10.2025</t>
+  </si>
+  <si>
+    <t>130059533</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 15.10.2025</t>
+  </si>
+  <si>
+    <t>134917959</t>
+  </si>
+  <si>
+    <t>134921585</t>
+  </si>
+  <si>
+    <t>129888010</t>
+  </si>
+  <si>
+    <t>130134514</t>
+  </si>
+  <si>
+    <t>134852344</t>
+  </si>
+  <si>
+    <t>130118281</t>
+  </si>
+  <si>
+    <t>130082282</t>
+  </si>
+  <si>
+    <t>134897069</t>
+  </si>
+  <si>
+    <t>134835808</t>
+  </si>
+  <si>
+    <t>134937643</t>
+  </si>
+  <si>
+    <t>129916238</t>
+  </si>
+  <si>
+    <t>134904606</t>
+  </si>
+  <si>
+    <t>134013888</t>
+  </si>
+  <si>
+    <t>134852240</t>
+  </si>
+  <si>
+    <t>134852918</t>
+  </si>
+  <si>
+    <t>134718741</t>
+  </si>
+  <si>
+    <t>134856754</t>
+  </si>
+  <si>
+    <t>134744076</t>
+  </si>
+  <si>
+    <t>129821352</t>
+  </si>
+  <si>
+    <t>134897849</t>
+  </si>
+  <si>
+    <t>129832217</t>
+  </si>
+  <si>
+    <t>129916214</t>
+  </si>
+  <si>
+    <t>134647400</t>
+  </si>
+  <si>
+    <t>134897221</t>
+  </si>
+  <si>
+    <t>134903499</t>
+  </si>
+  <si>
+    <t>134747764</t>
+  </si>
+  <si>
+    <t>134916648</t>
+  </si>
+  <si>
+    <t>129786031</t>
+  </si>
+  <si>
+    <t>134674554</t>
+  </si>
+  <si>
+    <t>130105678</t>
+  </si>
+  <si>
+    <t>134760190</t>
+  </si>
+  <si>
+    <t>134943916</t>
+  </si>
+  <si>
+    <t>129892628</t>
+  </si>
+  <si>
+    <t>130136660</t>
+  </si>
+  <si>
+    <t>134827666</t>
+  </si>
+  <si>
+    <t>131989408</t>
+  </si>
+  <si>
+    <t>129600703</t>
+  </si>
+  <si>
+    <t>134574381</t>
+  </si>
+  <si>
+    <t>134156654</t>
+  </si>
+  <si>
+    <t>134920051</t>
+  </si>
+  <si>
+    <t>129971237</t>
+  </si>
+  <si>
+    <t>129850492</t>
+  </si>
+  <si>
+    <t>134562221</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 15.10.2025</t>
   </si>
 </sst>
 </file>
@@ -585,7 +729,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F1048576"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -606,7 +750,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>0</v>
@@ -626,7 +770,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -643,7 +787,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -660,7 +804,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -677,7 +821,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -694,7 +838,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -711,7 +855,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -728,7 +872,7 @@
         <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -745,7 +889,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -762,7 +906,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -779,7 +923,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -796,7 +940,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -813,7 +957,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -830,7 +974,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>5</v>
@@ -847,7 +991,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>5</v>
@@ -864,7 +1008,7 @@
         <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>5</v>
@@ -881,7 +1025,7 @@
         <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>5</v>
@@ -898,7 +1042,7 @@
         <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>5</v>
@@ -915,7 +1059,7 @@
         <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>5</v>
@@ -932,7 +1076,7 @@
         <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>5</v>
@@ -949,7 +1093,7 @@
         <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>5</v>
@@ -966,7 +1110,7 @@
         <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>5</v>
@@ -974,7 +1118,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>6</v>
@@ -983,7 +1127,7 @@
         <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>5</v>
@@ -991,7 +1135,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>6</v>
@@ -1000,7 +1144,7 @@
         <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>5</v>
@@ -1008,7 +1152,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>6</v>
@@ -1017,7 +1161,7 @@
         <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>5</v>
@@ -1025,7 +1169,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>6</v>
@@ -1034,7 +1178,7 @@
         <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>5</v>
@@ -1042,7 +1186,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>6</v>
@@ -1051,7 +1195,7 @@
         <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>5</v>
@@ -1059,7 +1203,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>6</v>
@@ -1068,7 +1212,7 @@
         <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>5</v>
@@ -1076,7 +1220,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>6</v>
@@ -1085,7 +1229,7 @@
         <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>5</v>
@@ -1093,7 +1237,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>6</v>
@@ -1102,7 +1246,7 @@
         <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>5</v>
@@ -1110,7 +1254,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>6</v>
@@ -1119,7 +1263,7 @@
         <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>5</v>
@@ -1127,7 +1271,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>6</v>
@@ -1136,7 +1280,7 @@
         <v>10</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>5</v>
@@ -1144,7 +1288,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>6</v>
@@ -1153,7 +1297,7 @@
         <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>5</v>
@@ -1161,7 +1305,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>6</v>
@@ -1170,7 +1314,7 @@
         <v>10</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>5</v>
@@ -1178,7 +1322,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>6</v>
@@ -1187,7 +1331,7 @@
         <v>10</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>5</v>
@@ -1195,7 +1339,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>6</v>
@@ -1204,7 +1348,7 @@
         <v>10</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>5</v>
@@ -1212,7 +1356,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>6</v>
@@ -1221,7 +1365,7 @@
         <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>5</v>
@@ -1229,7 +1373,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>6</v>
@@ -1238,7 +1382,7 @@
         <v>10</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>5</v>
@@ -1246,7 +1390,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>6</v>
@@ -1255,7 +1399,7 @@
         <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>5</v>
@@ -1263,7 +1407,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>6</v>
@@ -1272,7 +1416,7 @@
         <v>10</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>5</v>
@@ -1280,7 +1424,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>6</v>
@@ -1289,7 +1433,7 @@
         <v>10</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>5</v>
@@ -1297,7 +1441,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>6</v>
@@ -1306,7 +1450,7 @@
         <v>10</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>5</v>
@@ -1314,7 +1458,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>6</v>
@@ -1323,7 +1467,7 @@
         <v>10</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>5</v>
@@ -1331,7 +1475,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>6</v>
@@ -1340,7 +1484,7 @@
         <v>10</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>5</v>
@@ -1348,7 +1492,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>6</v>
@@ -1357,7 +1501,7 @@
         <v>10</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>5</v>
@@ -1365,7 +1509,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>6</v>
@@ -1374,10 +1518,848 @@
         <v>10</v>
       </c>
       <c r="D46" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>5</v>
+      <c r="B48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1048576" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1048576" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1394,31 +2376,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0A9B38-0133-49CB-B00C-794F4CB74B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAEEBE44-6574-4E9C-AFCB-FBCB06937D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="52">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,115 +54,136 @@
     <t>Allianz - Cancelamento 10.10.2025</t>
   </si>
   <si>
-    <t>129752196</t>
-  </si>
-  <si>
-    <t>130091713</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 16.10.2025</t>
-  </si>
-  <si>
-    <t>134789473</t>
-  </si>
-  <si>
-    <t>134816014</t>
-  </si>
-  <si>
-    <t>130051378</t>
-  </si>
-  <si>
-    <t>134755684</t>
-  </si>
-  <si>
-    <t>130046121</t>
-  </si>
-  <si>
-    <t>134937566</t>
-  </si>
-  <si>
-    <t>134864663</t>
-  </si>
-  <si>
-    <t>134935216</t>
-  </si>
-  <si>
-    <t>134853989</t>
-  </si>
-  <si>
-    <t>134862422</t>
-  </si>
-  <si>
-    <t>134674438</t>
-  </si>
-  <si>
-    <t>134905583</t>
-  </si>
-  <si>
-    <t>134615892</t>
-  </si>
-  <si>
-    <t>134647579</t>
-  </si>
-  <si>
-    <t>134789313</t>
-  </si>
-  <si>
-    <t>134583555</t>
-  </si>
-  <si>
-    <t>129819610</t>
-  </si>
-  <si>
-    <t>130088338</t>
-  </si>
-  <si>
-    <t>134634812</t>
-  </si>
-  <si>
-    <t>129927354</t>
-  </si>
-  <si>
-    <t>134897759</t>
-  </si>
-  <si>
-    <t>134789327</t>
-  </si>
-  <si>
-    <t>129847979</t>
-  </si>
-  <si>
-    <t>134811691</t>
-  </si>
-  <si>
-    <t>129738318</t>
-  </si>
-  <si>
-    <t>134852479</t>
-  </si>
-  <si>
-    <t>131923596</t>
-  </si>
-  <si>
-    <t>134831267</t>
-  </si>
-  <si>
-    <t>134513102</t>
-  </si>
-  <si>
-    <t>133221540</t>
-  </si>
-  <si>
-    <t>134755346</t>
-  </si>
-  <si>
-    <t>129915369</t>
-  </si>
-  <si>
-    <t>131957697</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 16.10.2025</t>
+    <t>129859951</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 20.10.2025</t>
+  </si>
+  <si>
+    <t>134860680</t>
+  </si>
+  <si>
+    <t>134725816</t>
+  </si>
+  <si>
+    <t>134931949</t>
+  </si>
+  <si>
+    <t>129873772</t>
+  </si>
+  <si>
+    <t>130107714</t>
+  </si>
+  <si>
+    <t>134818587</t>
+  </si>
+  <si>
+    <t>134789381</t>
+  </si>
+  <si>
+    <t>130140267</t>
+  </si>
+  <si>
+    <t>130077233</t>
+  </si>
+  <si>
+    <t>129868131</t>
+  </si>
+  <si>
+    <t>134954244</t>
+  </si>
+  <si>
+    <t>130043450</t>
+  </si>
+  <si>
+    <t>134998920</t>
+  </si>
+  <si>
+    <t>134705153</t>
+  </si>
+  <si>
+    <t>129891456</t>
+  </si>
+  <si>
+    <t>134755194</t>
+  </si>
+  <si>
+    <t>130212810</t>
+  </si>
+  <si>
+    <t>134568400</t>
+  </si>
+  <si>
+    <t>134442319</t>
+  </si>
+  <si>
+    <t>134790782</t>
+  </si>
+  <si>
+    <t>134897085</t>
+  </si>
+  <si>
+    <t>130050619</t>
+  </si>
+  <si>
+    <t>134682256</t>
+  </si>
+  <si>
+    <t>130232523</t>
+  </si>
+  <si>
+    <t>130025257</t>
+  </si>
+  <si>
+    <t>129959811</t>
+  </si>
+  <si>
+    <t>134979487</t>
+  </si>
+  <si>
+    <t>134740475</t>
+  </si>
+  <si>
+    <t>134748785</t>
+  </si>
+  <si>
+    <t>134789199</t>
+  </si>
+  <si>
+    <t>134981455</t>
+  </si>
+  <si>
+    <t>135003383</t>
+  </si>
+  <si>
+    <t>129801269</t>
+  </si>
+  <si>
+    <t>135005148</t>
+  </si>
+  <si>
+    <t>134521420</t>
+  </si>
+  <si>
+    <t>129750167</t>
+  </si>
+  <si>
+    <t>134946767</t>
+  </si>
+  <si>
+    <t>134704341</t>
+  </si>
+  <si>
+    <t>134919494</t>
+  </si>
+  <si>
+    <t>131058253</t>
+  </si>
+  <si>
+    <t>130486049</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 20.10.2025</t>
   </si>
 </sst>
 </file>
@@ -558,7 +579,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -590,16 +611,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -607,16 +628,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -630,10 +651,10 @@
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -647,10 +668,10 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -664,10 +685,10 @@
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -681,10 +702,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -698,10 +719,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -715,10 +736,10 @@
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -732,10 +753,10 @@
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -749,10 +770,10 @@
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -766,10 +787,10 @@
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -783,10 +804,10 @@
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -800,10 +821,10 @@
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>5</v>
@@ -817,10 +838,10 @@
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>5</v>
@@ -834,10 +855,10 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>5</v>
@@ -851,10 +872,10 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>5</v>
@@ -868,10 +889,10 @@
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>5</v>
@@ -885,10 +906,10 @@
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>5</v>
@@ -902,10 +923,10 @@
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>5</v>
@@ -919,10 +940,10 @@
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>5</v>
@@ -936,10 +957,10 @@
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>5</v>
@@ -953,10 +974,10 @@
         <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>5</v>
@@ -970,10 +991,10 @@
         <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>5</v>
@@ -987,10 +1008,10 @@
         <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>5</v>
@@ -1004,10 +1025,10 @@
         <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>5</v>
@@ -1021,10 +1042,10 @@
         <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>5</v>
@@ -1038,10 +1059,10 @@
         <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>5</v>
@@ -1055,10 +1076,10 @@
         <v>6</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>5</v>
@@ -1072,10 +1093,10 @@
         <v>6</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>5</v>
@@ -1083,16 +1104,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>5</v>
@@ -1100,16 +1121,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>5</v>
@@ -1117,16 +1138,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>5</v>
@@ -1134,16 +1155,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>5</v>
@@ -1151,16 +1172,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>5</v>
@@ -1168,16 +1189,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>5</v>
@@ -1185,18 +1206,120 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E37" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1214,31 +1337,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAEEBE44-6574-4E9C-AFCB-FBCB06937D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFE1076-27A1-4A31-900F-C9321C1EA10D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="34">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,136 +54,82 @@
     <t>Allianz - Cancelamento 10.10.2025</t>
   </si>
   <si>
-    <t>129859951</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 20.10.2025</t>
-  </si>
-  <si>
-    <t>134860680</t>
-  </si>
-  <si>
-    <t>134725816</t>
-  </si>
-  <si>
-    <t>134931949</t>
-  </si>
-  <si>
-    <t>129873772</t>
-  </si>
-  <si>
-    <t>130107714</t>
-  </si>
-  <si>
-    <t>134818587</t>
-  </si>
-  <si>
-    <t>134789381</t>
-  </si>
-  <si>
-    <t>130140267</t>
-  </si>
-  <si>
-    <t>130077233</t>
-  </si>
-  <si>
-    <t>129868131</t>
-  </si>
-  <si>
-    <t>134954244</t>
-  </si>
-  <si>
-    <t>130043450</t>
-  </si>
-  <si>
-    <t>134998920</t>
-  </si>
-  <si>
-    <t>134705153</t>
-  </si>
-  <si>
-    <t>129891456</t>
-  </si>
-  <si>
-    <t>134755194</t>
-  </si>
-  <si>
-    <t>130212810</t>
-  </si>
-  <si>
-    <t>134568400</t>
-  </si>
-  <si>
-    <t>134442319</t>
-  </si>
-  <si>
-    <t>134790782</t>
-  </si>
-  <si>
-    <t>134897085</t>
-  </si>
-  <si>
-    <t>130050619</t>
-  </si>
-  <si>
-    <t>134682256</t>
-  </si>
-  <si>
-    <t>130232523</t>
-  </si>
-  <si>
-    <t>130025257</t>
-  </si>
-  <si>
-    <t>129959811</t>
-  </si>
-  <si>
-    <t>134979487</t>
-  </si>
-  <si>
-    <t>134740475</t>
-  </si>
-  <si>
-    <t>134748785</t>
-  </si>
-  <si>
-    <t>134789199</t>
-  </si>
-  <si>
-    <t>134981455</t>
-  </si>
-  <si>
-    <t>135003383</t>
-  </si>
-  <si>
-    <t>129801269</t>
-  </si>
-  <si>
-    <t>135005148</t>
-  </si>
-  <si>
-    <t>134521420</t>
-  </si>
-  <si>
-    <t>129750167</t>
-  </si>
-  <si>
-    <t>134946767</t>
-  </si>
-  <si>
-    <t>134704341</t>
-  </si>
-  <si>
-    <t>134919494</t>
-  </si>
-  <si>
-    <t>131058253</t>
-  </si>
-  <si>
-    <t>130486049</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 20.10.2025</t>
+    <t>134948867</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 21.10.2025</t>
+  </si>
+  <si>
+    <t>134795229</t>
+  </si>
+  <si>
+    <t>134789413</t>
+  </si>
+  <si>
+    <t>135032872</t>
+  </si>
+  <si>
+    <t>134937502</t>
+  </si>
+  <si>
+    <t>134747788</t>
+  </si>
+  <si>
+    <t>130163754</t>
+  </si>
+  <si>
+    <t>134897107</t>
+  </si>
+  <si>
+    <t>129917407</t>
+  </si>
+  <si>
+    <t>134901708</t>
+  </si>
+  <si>
+    <t>135003420</t>
+  </si>
+  <si>
+    <t>134814709</t>
+  </si>
+  <si>
+    <t>135004073</t>
+  </si>
+  <si>
+    <t>134935264</t>
+  </si>
+  <si>
+    <t>129795400</t>
+  </si>
+  <si>
+    <t>130116531</t>
+  </si>
+  <si>
+    <t>135002775</t>
+  </si>
+  <si>
+    <t>134897646</t>
+  </si>
+  <si>
+    <t>134927799</t>
+  </si>
+  <si>
+    <t>134854176</t>
+  </si>
+  <si>
+    <t>130134751</t>
+  </si>
+  <si>
+    <t>134897308</t>
+  </si>
+  <si>
+    <t>134519859</t>
+  </si>
+  <si>
+    <t>130094967</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 21.10.2025</t>
   </si>
 </sst>
 </file>
@@ -579,7 +525,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -620,7 +566,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -637,7 +583,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -654,7 +600,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -671,7 +617,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -688,7 +634,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -705,7 +651,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -722,7 +668,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -739,7 +685,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -756,7 +702,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -773,7 +719,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -790,7 +736,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -807,7 +753,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -824,7 +770,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>5</v>
@@ -841,7 +787,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>5</v>
@@ -858,7 +804,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>5</v>
@@ -875,7 +821,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>5</v>
@@ -892,7 +838,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>5</v>
@@ -909,7 +855,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>5</v>
@@ -926,7 +872,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>5</v>
@@ -943,7 +889,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>5</v>
@@ -960,7 +906,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>5</v>
@@ -977,7 +923,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>5</v>
@@ -994,7 +940,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>5</v>
@@ -1011,315 +957,9 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E43" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1337,31 +977,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFE1076-27A1-4A31-900F-C9321C1EA10D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD165BC2-1AC4-4F91-A5DE-598183CFC1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="49">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,82 +54,127 @@
     <t>Allianz - Cancelamento 10.10.2025</t>
   </si>
   <si>
-    <t>134948867</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 21.10.2025</t>
-  </si>
-  <si>
-    <t>134795229</t>
-  </si>
-  <si>
-    <t>134789413</t>
-  </si>
-  <si>
-    <t>135032872</t>
-  </si>
-  <si>
-    <t>134937502</t>
-  </si>
-  <si>
-    <t>134747788</t>
-  </si>
-  <si>
-    <t>130163754</t>
-  </si>
-  <si>
-    <t>134897107</t>
-  </si>
-  <si>
-    <t>129917407</t>
-  </si>
-  <si>
-    <t>134901708</t>
-  </si>
-  <si>
-    <t>135003420</t>
-  </si>
-  <si>
-    <t>134814709</t>
-  </si>
-  <si>
-    <t>135004073</t>
-  </si>
-  <si>
-    <t>134935264</t>
-  </si>
-  <si>
-    <t>129795400</t>
-  </si>
-  <si>
-    <t>130116531</t>
-  </si>
-  <si>
-    <t>135002775</t>
-  </si>
-  <si>
-    <t>134897646</t>
-  </si>
-  <si>
-    <t>134927799</t>
-  </si>
-  <si>
-    <t>134854176</t>
-  </si>
-  <si>
-    <t>130134751</t>
-  </si>
-  <si>
-    <t>134897308</t>
-  </si>
-  <si>
-    <t>134519859</t>
-  </si>
-  <si>
-    <t>130094967</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 21.10.2025</t>
+    <t>135003400</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 22.10.2025</t>
+  </si>
+  <si>
+    <t>135002527</t>
+  </si>
+  <si>
+    <t>134693268</t>
+  </si>
+  <si>
+    <t>135003801</t>
+  </si>
+  <si>
+    <t>134897240</t>
+  </si>
+  <si>
+    <t>134468253</t>
+  </si>
+  <si>
+    <t>134861740</t>
+  </si>
+  <si>
+    <t>134759777</t>
+  </si>
+  <si>
+    <t>135060333</t>
+  </si>
+  <si>
+    <t>134897182</t>
+  </si>
+  <si>
+    <t>134789323</t>
+  </si>
+  <si>
+    <t>135002987</t>
+  </si>
+  <si>
+    <t>130015111</t>
+  </si>
+  <si>
+    <t>129880001</t>
+  </si>
+  <si>
+    <t>134789385</t>
+  </si>
+  <si>
+    <t>134943264</t>
+  </si>
+  <si>
+    <t>135060239</t>
+  </si>
+  <si>
+    <t>135008774</t>
+  </si>
+  <si>
+    <t>130226189</t>
+  </si>
+  <si>
+    <t>135027604</t>
+  </si>
+  <si>
+    <t>135002873</t>
+  </si>
+  <si>
+    <t>130015140</t>
+  </si>
+  <si>
+    <t>130206543</t>
+  </si>
+  <si>
+    <t>129912518</t>
+  </si>
+  <si>
+    <t>134852299</t>
+  </si>
+  <si>
+    <t>134857935</t>
+  </si>
+  <si>
+    <t>130167572</t>
+  </si>
+  <si>
+    <t>134992158</t>
+  </si>
+  <si>
+    <t>134789343</t>
+  </si>
+  <si>
+    <t>135033178</t>
+  </si>
+  <si>
+    <t>130002259</t>
+  </si>
+  <si>
+    <t>134897628</t>
+  </si>
+  <si>
+    <t>134916589</t>
+  </si>
+  <si>
+    <t>134741473</t>
+  </si>
+  <si>
+    <t>135002656</t>
+  </si>
+  <si>
+    <t>134825819</t>
+  </si>
+  <si>
+    <t>135003577</t>
+  </si>
+  <si>
+    <t>130015156</t>
+  </si>
+  <si>
+    <t>134831012</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 22.10.2025</t>
   </si>
 </sst>
 </file>
@@ -525,7 +570,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -566,7 +611,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -583,7 +628,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -600,7 +645,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -617,7 +662,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -634,7 +679,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -651,7 +696,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -668,7 +713,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -685,7 +730,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -702,7 +747,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -719,7 +764,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -736,7 +781,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -753,7 +798,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -770,7 +815,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>5</v>
@@ -787,7 +832,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>5</v>
@@ -804,7 +849,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>5</v>
@@ -821,7 +866,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>5</v>
@@ -838,7 +883,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>5</v>
@@ -855,7 +900,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>5</v>
@@ -872,7 +917,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>5</v>
@@ -889,7 +934,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>5</v>
@@ -906,7 +951,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>5</v>
@@ -923,7 +968,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>5</v>
@@ -940,7 +985,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>5</v>
@@ -957,9 +1002,298 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -977,31 +1311,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD165BC2-1AC4-4F91-A5DE-598183CFC1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4647A94F-AE77-40CE-A34D-C1761C18B10D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1311,31 +1311,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4647A94F-AE77-40CE-A34D-C1761C18B10D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD483CEE-3319-4EBF-8ECB-BDEB845F8C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="53">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,127 +54,139 @@
     <t>Allianz - Cancelamento 10.10.2025</t>
   </si>
   <si>
-    <t>135003400</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 22.10.2025</t>
-  </si>
-  <si>
-    <t>135002527</t>
-  </si>
-  <si>
-    <t>134693268</t>
-  </si>
-  <si>
-    <t>135003801</t>
-  </si>
-  <si>
-    <t>134897240</t>
-  </si>
-  <si>
-    <t>134468253</t>
-  </si>
-  <si>
-    <t>134861740</t>
-  </si>
-  <si>
-    <t>134759777</t>
-  </si>
-  <si>
-    <t>135060333</t>
-  </si>
-  <si>
-    <t>134897182</t>
-  </si>
-  <si>
-    <t>134789323</t>
-  </si>
-  <si>
-    <t>135002987</t>
-  </si>
-  <si>
-    <t>130015111</t>
-  </si>
-  <si>
-    <t>129880001</t>
-  </si>
-  <si>
-    <t>134789385</t>
-  </si>
-  <si>
-    <t>134943264</t>
-  </si>
-  <si>
-    <t>135060239</t>
-  </si>
-  <si>
-    <t>135008774</t>
-  </si>
-  <si>
-    <t>130226189</t>
-  </si>
-  <si>
-    <t>135027604</t>
-  </si>
-  <si>
-    <t>135002873</t>
-  </si>
-  <si>
-    <t>130015140</t>
-  </si>
-  <si>
-    <t>130206543</t>
-  </si>
-  <si>
-    <t>129912518</t>
-  </si>
-  <si>
-    <t>134852299</t>
-  </si>
-  <si>
-    <t>134857935</t>
-  </si>
-  <si>
-    <t>130167572</t>
-  </si>
-  <si>
-    <t>134992158</t>
-  </si>
-  <si>
-    <t>134789343</t>
-  </si>
-  <si>
-    <t>135033178</t>
-  </si>
-  <si>
-    <t>130002259</t>
-  </si>
-  <si>
-    <t>134897628</t>
-  </si>
-  <si>
-    <t>134916589</t>
-  </si>
-  <si>
-    <t>134741473</t>
-  </si>
-  <si>
-    <t>135002656</t>
-  </si>
-  <si>
-    <t>134825819</t>
-  </si>
-  <si>
-    <t>135003577</t>
-  </si>
-  <si>
-    <t>130015156</t>
-  </si>
-  <si>
-    <t>134831012</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 22.10.2025</t>
+    <t>134861016</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 24.10.2025</t>
+  </si>
+  <si>
+    <t>135060030</t>
+  </si>
+  <si>
+    <t>134942814</t>
+  </si>
+  <si>
+    <t>135061072</t>
+  </si>
+  <si>
+    <t>134883564</t>
+  </si>
+  <si>
+    <t>130256733</t>
+  </si>
+  <si>
+    <t>135003672</t>
+  </si>
+  <si>
+    <t>134937646</t>
+  </si>
+  <si>
+    <t>134701963</t>
+  </si>
+  <si>
+    <t>135040166</t>
+  </si>
+  <si>
+    <t>134897838</t>
+  </si>
+  <si>
+    <t>130224921</t>
+  </si>
+  <si>
+    <t>134942424</t>
+  </si>
+  <si>
+    <t>134678887</t>
+  </si>
+  <si>
+    <t>135070771</t>
+  </si>
+  <si>
+    <t>135003303</t>
+  </si>
+  <si>
+    <t>130112389</t>
+  </si>
+  <si>
+    <t>135075580</t>
+  </si>
+  <si>
+    <t>134937547</t>
+  </si>
+  <si>
+    <t>135061099</t>
+  </si>
+  <si>
+    <t>135106784</t>
+  </si>
+  <si>
+    <t>130203399</t>
+  </si>
+  <si>
+    <t>134963451</t>
+  </si>
+  <si>
+    <t>134994340</t>
+  </si>
+  <si>
+    <t>134992485</t>
+  </si>
+  <si>
+    <t>130199743</t>
+  </si>
+  <si>
+    <t>130240521</t>
+  </si>
+  <si>
+    <t>134898280</t>
+  </si>
+  <si>
+    <t>135005230</t>
+  </si>
+  <si>
+    <t>134852924</t>
+  </si>
+  <si>
+    <t>135058343</t>
+  </si>
+  <si>
+    <t>135044479</t>
+  </si>
+  <si>
+    <t>134938173</t>
+  </si>
+  <si>
+    <t>135046529</t>
+  </si>
+  <si>
+    <t>134966962</t>
+  </si>
+  <si>
+    <t>129949268</t>
+  </si>
+  <si>
+    <t>134965193</t>
+  </si>
+  <si>
+    <t>134967347</t>
+  </si>
+  <si>
+    <t>135090745</t>
+  </si>
+  <si>
+    <t>135003889</t>
+  </si>
+  <si>
+    <t>134852722</t>
+  </si>
+  <si>
+    <t>134975036</t>
+  </si>
+  <si>
+    <t>132126230</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 24.10.2025</t>
   </si>
 </sst>
 </file>
@@ -570,7 +582,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -611,7 +623,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -628,7 +640,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -645,7 +657,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -662,7 +674,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -679,7 +691,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -696,7 +708,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -713,7 +725,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -730,7 +742,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -747,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -764,7 +776,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -781,7 +793,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -798,7 +810,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -815,7 +827,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>5</v>
@@ -832,7 +844,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>5</v>
@@ -849,7 +861,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>5</v>
@@ -866,7 +878,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>5</v>
@@ -883,7 +895,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>5</v>
@@ -900,7 +912,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>5</v>
@@ -917,7 +929,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>5</v>
@@ -934,7 +946,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>5</v>
@@ -951,7 +963,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>5</v>
@@ -968,7 +980,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>5</v>
@@ -985,7 +997,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>5</v>
@@ -1002,7 +1014,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>5</v>
@@ -1010,7 +1022,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>6</v>
@@ -1019,7 +1031,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>5</v>
@@ -1027,7 +1039,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>6</v>
@@ -1036,7 +1048,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>5</v>
@@ -1044,7 +1056,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>6</v>
@@ -1053,7 +1065,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>5</v>
@@ -1061,7 +1073,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>6</v>
@@ -1070,7 +1082,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>5</v>
@@ -1078,7 +1090,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>6</v>
@@ -1087,7 +1099,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>5</v>
@@ -1095,7 +1107,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>6</v>
@@ -1104,7 +1116,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>5</v>
@@ -1112,7 +1124,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>6</v>
@@ -1121,7 +1133,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>5</v>
@@ -1129,7 +1141,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>6</v>
@@ -1138,7 +1150,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>5</v>
@@ -1146,7 +1158,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>6</v>
@@ -1155,7 +1167,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>5</v>
@@ -1163,7 +1175,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>6</v>
@@ -1172,7 +1184,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>5</v>
@@ -1180,7 +1192,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>6</v>
@@ -1189,7 +1201,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>5</v>
@@ -1197,7 +1209,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>6</v>
@@ -1206,7 +1218,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>5</v>
@@ -1214,7 +1226,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>6</v>
@@ -1223,7 +1235,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>5</v>
@@ -1231,7 +1243,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>6</v>
@@ -1240,7 +1252,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>5</v>
@@ -1257,7 +1269,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>5</v>
@@ -1265,7 +1277,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>6</v>
@@ -1274,7 +1286,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>5</v>
@@ -1282,7 +1294,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>6</v>
@@ -1291,9 +1303,60 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E42" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1311,31 +1374,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD483CEE-3319-4EBF-8ECB-BDEB845F8C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DE5F83-3E60-4744-AE0F-2CC540EE117D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="51">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,139 +54,133 @@
     <t>Allianz - Cancelamento 10.10.2025</t>
   </si>
   <si>
-    <t>134861016</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 24.10.2025</t>
-  </si>
-  <si>
-    <t>135060030</t>
-  </si>
-  <si>
-    <t>134942814</t>
-  </si>
-  <si>
-    <t>135061072</t>
-  </si>
-  <si>
-    <t>134883564</t>
-  </si>
-  <si>
-    <t>130256733</t>
-  </si>
-  <si>
-    <t>135003672</t>
-  </si>
-  <si>
-    <t>134937646</t>
-  </si>
-  <si>
-    <t>134701963</t>
-  </si>
-  <si>
-    <t>135040166</t>
-  </si>
-  <si>
-    <t>134897838</t>
-  </si>
-  <si>
-    <t>130224921</t>
-  </si>
-  <si>
-    <t>134942424</t>
-  </si>
-  <si>
-    <t>134678887</t>
-  </si>
-  <si>
-    <t>135070771</t>
-  </si>
-  <si>
-    <t>135003303</t>
-  </si>
-  <si>
-    <t>130112389</t>
-  </si>
-  <si>
-    <t>135075580</t>
-  </si>
-  <si>
-    <t>134937547</t>
-  </si>
-  <si>
-    <t>135061099</t>
-  </si>
-  <si>
-    <t>135106784</t>
-  </si>
-  <si>
-    <t>130203399</t>
-  </si>
-  <si>
-    <t>134963451</t>
-  </si>
-  <si>
-    <t>134994340</t>
-  </si>
-  <si>
-    <t>134992485</t>
-  </si>
-  <si>
-    <t>130199743</t>
-  </si>
-  <si>
-    <t>130240521</t>
-  </si>
-  <si>
-    <t>134898280</t>
-  </si>
-  <si>
-    <t>135005230</t>
-  </si>
-  <si>
-    <t>134852924</t>
-  </si>
-  <si>
-    <t>135058343</t>
-  </si>
-  <si>
-    <t>135044479</t>
-  </si>
-  <si>
-    <t>134938173</t>
-  </si>
-  <si>
-    <t>135046529</t>
-  </si>
-  <si>
-    <t>134966962</t>
-  </si>
-  <si>
-    <t>129949268</t>
-  </si>
-  <si>
-    <t>134965193</t>
-  </si>
-  <si>
-    <t>134967347</t>
-  </si>
-  <si>
-    <t>135090745</t>
-  </si>
-  <si>
-    <t>135003889</t>
-  </si>
-  <si>
     <t>134852722</t>
   </si>
   <si>
-    <t>134975036</t>
-  </si>
-  <si>
-    <t>132126230</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 24.10.2025</t>
+    <t>134617606</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 27.10.2025</t>
+  </si>
+  <si>
+    <t>130257664</t>
+  </si>
+  <si>
+    <t>134697708</t>
+  </si>
+  <si>
+    <t>135092546</t>
+  </si>
+  <si>
+    <t>130310014</t>
+  </si>
+  <si>
+    <t>130014712</t>
+  </si>
+  <si>
+    <t>135061934</t>
+  </si>
+  <si>
+    <t>130066497</t>
+  </si>
+  <si>
+    <t>135003898</t>
+  </si>
+  <si>
+    <t>135014998</t>
+  </si>
+  <si>
+    <t>135003011</t>
+  </si>
+  <si>
+    <t>129867323</t>
+  </si>
+  <si>
+    <t>134976368</t>
+  </si>
+  <si>
+    <t>134595190</t>
+  </si>
+  <si>
+    <t>134981862</t>
+  </si>
+  <si>
+    <t>130277925</t>
+  </si>
+  <si>
+    <t>135100359</t>
+  </si>
+  <si>
+    <t>135107393</t>
+  </si>
+  <si>
+    <t>134858558</t>
+  </si>
+  <si>
+    <t>130068124</t>
+  </si>
+  <si>
+    <t>135029025</t>
+  </si>
+  <si>
+    <t>130086716</t>
+  </si>
+  <si>
+    <t>135088949</t>
+  </si>
+  <si>
+    <t>135000174</t>
+  </si>
+  <si>
+    <t>135079918</t>
+  </si>
+  <si>
+    <t>134611517</t>
+  </si>
+  <si>
+    <t>130194102</t>
+  </si>
+  <si>
+    <t>134988980</t>
+  </si>
+  <si>
+    <t>134852215</t>
+  </si>
+  <si>
+    <t>135040123</t>
+  </si>
+  <si>
+    <t>134810688</t>
+  </si>
+  <si>
+    <t>135027030</t>
+  </si>
+  <si>
+    <t>135100764</t>
+  </si>
+  <si>
+    <t>135111265</t>
+  </si>
+  <si>
+    <t>134864276</t>
+  </si>
+  <si>
+    <t>134865148</t>
+  </si>
+  <si>
+    <t>135002482</t>
+  </si>
+  <si>
+    <t>135057013</t>
+  </si>
+  <si>
+    <t>133669273</t>
+  </si>
+  <si>
+    <t>135095994</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 27.10.2025</t>
   </si>
 </sst>
 </file>
@@ -582,7 +576,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -614,16 +608,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -631,16 +625,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -648,16 +642,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -665,16 +659,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
@@ -682,16 +676,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>5</v>
@@ -705,10 +699,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -722,10 +716,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -739,10 +733,10 @@
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>5</v>
@@ -756,10 +750,10 @@
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>5</v>
@@ -773,10 +767,10 @@
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>5</v>
@@ -790,10 +784,10 @@
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>5</v>
@@ -807,10 +801,10 @@
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>5</v>
@@ -824,10 +818,10 @@
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>5</v>
@@ -841,10 +835,10 @@
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>5</v>
@@ -858,10 +852,10 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>5</v>
@@ -875,10 +869,10 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>5</v>
@@ -892,10 +886,10 @@
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>5</v>
@@ -909,10 +903,10 @@
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>5</v>
@@ -926,10 +920,10 @@
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>5</v>
@@ -943,10 +937,10 @@
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>5</v>
@@ -960,10 +954,10 @@
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>5</v>
@@ -977,10 +971,10 @@
         <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>5</v>
@@ -994,10 +988,10 @@
         <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>5</v>
@@ -1011,10 +1005,10 @@
         <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>5</v>
@@ -1028,10 +1022,10 @@
         <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>5</v>
@@ -1045,10 +1039,10 @@
         <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>5</v>
@@ -1062,10 +1056,10 @@
         <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>5</v>
@@ -1079,10 +1073,10 @@
         <v>6</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>5</v>
@@ -1096,10 +1090,10 @@
         <v>6</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>5</v>
@@ -1113,10 +1107,10 @@
         <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>5</v>
@@ -1130,10 +1124,10 @@
         <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>5</v>
@@ -1147,10 +1141,10 @@
         <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>5</v>
@@ -1164,10 +1158,10 @@
         <v>6</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>5</v>
@@ -1181,10 +1175,10 @@
         <v>6</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>5</v>
@@ -1198,10 +1192,10 @@
         <v>6</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>5</v>
@@ -1215,10 +1209,10 @@
         <v>6</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>5</v>
@@ -1232,10 +1226,10 @@
         <v>6</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>5</v>
@@ -1243,16 +1237,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>5</v>
@@ -1260,16 +1254,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>5</v>
@@ -1277,16 +1271,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>5</v>
@@ -1294,69 +1288,18 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E45" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1374,31 +1317,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7724B35-6B73-449F-8A3F-BD078A1455BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8767448E-2415-44F3-92DD-53419A53D14B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="59">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,241 +54,157 @@
     <t>1070</t>
   </si>
   <si>
-    <t>134048544</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 02.09.2025</t>
-  </si>
-  <si>
-    <t>129444403</t>
-  </si>
-  <si>
-    <t>129239077</t>
-  </si>
-  <si>
-    <t>133973269</t>
-  </si>
-  <si>
-    <t>129276671</t>
-  </si>
-  <si>
-    <t>129558773</t>
-  </si>
-  <si>
-    <t>134051488</t>
-  </si>
-  <si>
-    <t>133859982</t>
-  </si>
-  <si>
-    <t>129447191</t>
-  </si>
-  <si>
-    <t>134111484</t>
-  </si>
-  <si>
-    <t>134100099</t>
-  </si>
-  <si>
-    <t>129452370</t>
-  </si>
-  <si>
-    <t>133926272</t>
-  </si>
-  <si>
-    <t>134003861</t>
-  </si>
-  <si>
-    <t>133860289</t>
-  </si>
-  <si>
-    <t>133994237</t>
-  </si>
-  <si>
-    <t>129523315</t>
-  </si>
-  <si>
-    <t>134207033</t>
-  </si>
-  <si>
-    <t>129558973</t>
-  </si>
-  <si>
-    <t>129537920</t>
-  </si>
-  <si>
-    <t>134138433</t>
-  </si>
-  <si>
-    <t>129733520</t>
-  </si>
-  <si>
-    <t>134048759</t>
-  </si>
-  <si>
-    <t>134166001</t>
-  </si>
-  <si>
-    <t>133261755</t>
-  </si>
-  <si>
-    <t>134180763</t>
-  </si>
-  <si>
-    <t>133904761</t>
-  </si>
-  <si>
-    <t>134518741</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 03.09.2025</t>
-  </si>
-  <si>
-    <t>129955640</t>
-  </si>
-  <si>
-    <t>134696713</t>
-  </si>
-  <si>
-    <t>129570128</t>
-  </si>
-  <si>
-    <t>130011277</t>
-  </si>
-  <si>
-    <t>134760353</t>
-  </si>
-  <si>
-    <t>134351572</t>
-  </si>
-  <si>
-    <t>134465136</t>
-  </si>
-  <si>
-    <t>134696337</t>
-  </si>
-  <si>
-    <t>134465123</t>
-  </si>
-  <si>
-    <t>134629363</t>
-  </si>
-  <si>
-    <t>134473821</t>
-  </si>
-  <si>
-    <t>129788344</t>
-  </si>
-  <si>
-    <t>129886544</t>
-  </si>
-  <si>
-    <t>134517030</t>
-  </si>
-  <si>
-    <t>129875674</t>
-  </si>
-  <si>
-    <t>134465201</t>
-  </si>
-  <si>
-    <t>130076877</t>
-  </si>
-  <si>
-    <t>134511151</t>
-  </si>
-  <si>
-    <t>134514465</t>
-  </si>
-  <si>
-    <t>134583595</t>
-  </si>
-  <si>
-    <t>134726204</t>
-  </si>
-  <si>
-    <t>129711182</t>
-  </si>
-  <si>
-    <t>129778970</t>
-  </si>
-  <si>
-    <t>134443089</t>
-  </si>
-  <si>
-    <t>129771674</t>
-  </si>
-  <si>
-    <t>134515912</t>
-  </si>
-  <si>
-    <t>134465639</t>
-  </si>
-  <si>
-    <t>134487935</t>
-  </si>
-  <si>
-    <t>129797980</t>
-  </si>
-  <si>
-    <t>134239534</t>
-  </si>
-  <si>
-    <t>134658681</t>
-  </si>
-  <si>
-    <t>129690664</t>
-  </si>
-  <si>
-    <t>134770853</t>
-  </si>
-  <si>
-    <t>134751114</t>
-  </si>
-  <si>
-    <t>134756714</t>
-  </si>
-  <si>
-    <t>134772089</t>
-  </si>
-  <si>
-    <t>129959105</t>
-  </si>
-  <si>
-    <t>134674497</t>
-  </si>
-  <si>
-    <t>134745290</t>
-  </si>
-  <si>
-    <t>134443065</t>
-  </si>
-  <si>
-    <t>134628173</t>
-  </si>
-  <si>
-    <t>134279896</t>
-  </si>
-  <si>
-    <t>134696370</t>
-  </si>
-  <si>
-    <t>134678642</t>
-  </si>
-  <si>
-    <t>129728144</t>
-  </si>
-  <si>
-    <t>134515915</t>
-  </si>
-  <si>
-    <t>130248689</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 02.10.2025</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 03.10.2025</t>
+    <t>130954369</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 18.12.2025</t>
+  </si>
+  <si>
+    <t>135639473</t>
+  </si>
+  <si>
+    <t>135850583</t>
+  </si>
+  <si>
+    <t>130917498</t>
+  </si>
+  <si>
+    <t>135878515</t>
+  </si>
+  <si>
+    <t>135694289</t>
+  </si>
+  <si>
+    <t>135482058</t>
+  </si>
+  <si>
+    <t>135693326</t>
+  </si>
+  <si>
+    <t>135870815</t>
+  </si>
+  <si>
+    <t>130691031</t>
+  </si>
+  <si>
+    <t>135380862</t>
+  </si>
+  <si>
+    <t>135829887</t>
+  </si>
+  <si>
+    <t>130968238</t>
+  </si>
+  <si>
+    <t>130843688</t>
+  </si>
+  <si>
+    <t>135788305</t>
+  </si>
+  <si>
+    <t>130608272</t>
+  </si>
+  <si>
+    <t>135880115</t>
+  </si>
+  <si>
+    <t>135741562</t>
+  </si>
+  <si>
+    <t>135641268</t>
+  </si>
+  <si>
+    <t>135741537</t>
+  </si>
+  <si>
+    <t>135624621</t>
+  </si>
+  <si>
+    <t>135773164</t>
+  </si>
+  <si>
+    <t>135841920</t>
+  </si>
+  <si>
+    <t>135823672</t>
+  </si>
+  <si>
+    <t>130645688</t>
+  </si>
+  <si>
+    <t>135850603</t>
+  </si>
+  <si>
+    <t>135711526</t>
+  </si>
+  <si>
+    <t>135912334</t>
+  </si>
+  <si>
+    <t>130799513</t>
+  </si>
+  <si>
+    <t>130780269</t>
+  </si>
+  <si>
+    <t>135693201</t>
+  </si>
+  <si>
+    <t>130739672</t>
+  </si>
+  <si>
+    <t>135823918</t>
+  </si>
+  <si>
+    <t>130897315</t>
+  </si>
+  <si>
+    <t>135822252</t>
+  </si>
+  <si>
+    <t>130690970</t>
+  </si>
+  <si>
+    <t>135774607</t>
+  </si>
+  <si>
+    <t>135850368</t>
+  </si>
+  <si>
+    <t>135645356</t>
+  </si>
+  <si>
+    <t>130806990</t>
+  </si>
+  <si>
+    <t>135894726</t>
+  </si>
+  <si>
+    <t>135528159</t>
+  </si>
+  <si>
+    <t>130793075</t>
+  </si>
+  <si>
+    <t>130658288</t>
+  </si>
+  <si>
+    <t>135627178</t>
+  </si>
+  <si>
+    <t>130777681</t>
+  </si>
+  <si>
+    <t>135508852</t>
+  </si>
+  <si>
+    <t>130656241</t>
+  </si>
+  <si>
+    <t>135812151</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 18.12.2025</t>
   </si>
 </sst>
 </file>
@@ -684,7 +600,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -716,7 +632,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -725,7 +641,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -734,7 +650,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
@@ -743,7 +659,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -752,7 +668,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -761,7 +677,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -770,7 +686,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
@@ -779,7 +695,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -788,7 +704,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
@@ -797,7 +713,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -815,7 +731,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -833,7 +749,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -851,7 +767,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -869,7 +785,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -878,7 +794,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
@@ -887,7 +803,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -896,7 +812,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
@@ -905,7 +821,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -914,7 +830,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
@@ -923,7 +839,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -932,7 +848,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
@@ -941,7 +857,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -950,7 +866,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
@@ -959,7 +875,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -968,7 +884,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
@@ -977,7 +893,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -986,7 +902,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
@@ -995,7 +911,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -1004,7 +920,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
@@ -1013,7 +929,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1022,7 +938,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
@@ -1031,7 +947,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1040,7 +956,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
@@ -1049,7 +965,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1058,7 +974,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
@@ -1067,7 +983,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1076,7 +992,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
@@ -1085,7 +1001,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1094,7 +1010,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
@@ -1103,7 +1019,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1112,7 +1028,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
@@ -1121,7 +1037,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1130,7 +1046,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
@@ -1139,7 +1055,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1148,7 +1064,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
@@ -1157,7 +1073,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1166,7 +1082,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
@@ -1175,7 +1091,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1184,7 +1100,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
@@ -1193,7 +1109,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1202,7 +1118,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
@@ -1211,7 +1127,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1220,7 +1136,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
@@ -1229,7 +1145,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1238,7 +1154,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
@@ -1247,7 +1163,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1256,7 +1172,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
@@ -1265,7 +1181,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1274,7 +1190,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
@@ -1283,7 +1199,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1292,16 +1208,16 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1310,16 +1226,16 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1328,135 +1244,142 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F36"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F37"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F38"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F39"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F40"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F41"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F42"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1464,16 +1387,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1481,16 +1404,16 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1498,16 +1421,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1515,16 +1438,16 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1532,16 +1455,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1549,16 +1472,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1566,545 +1489,18 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E81" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2122,31 +1518,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_NUP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8767448E-2415-44F3-92DD-53419A53D14B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F7AADA-4BB7-483C-901F-A63407F557C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="74">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,157 +54,202 @@
     <t>1070</t>
   </si>
   <si>
-    <t>130954369</t>
-  </si>
-  <si>
-    <t>Nup- Cancelamento 18.12.2025</t>
-  </si>
-  <si>
-    <t>135639473</t>
-  </si>
-  <si>
-    <t>135850583</t>
-  </si>
-  <si>
-    <t>130917498</t>
-  </si>
-  <si>
-    <t>135878515</t>
-  </si>
-  <si>
-    <t>135694289</t>
-  </si>
-  <si>
-    <t>135482058</t>
-  </si>
-  <si>
-    <t>135693326</t>
-  </si>
-  <si>
-    <t>135870815</t>
-  </si>
-  <si>
-    <t>130691031</t>
-  </si>
-  <si>
-    <t>135380862</t>
-  </si>
-  <si>
-    <t>135829887</t>
-  </si>
-  <si>
-    <t>130968238</t>
-  </si>
-  <si>
-    <t>130843688</t>
-  </si>
-  <si>
-    <t>135788305</t>
-  </si>
-  <si>
-    <t>130608272</t>
-  </si>
-  <si>
-    <t>135880115</t>
-  </si>
-  <si>
-    <t>135741562</t>
-  </si>
-  <si>
-    <t>135641268</t>
-  </si>
-  <si>
-    <t>135741537</t>
-  </si>
-  <si>
-    <t>135624621</t>
-  </si>
-  <si>
-    <t>135773164</t>
-  </si>
-  <si>
-    <t>135841920</t>
-  </si>
-  <si>
-    <t>135823672</t>
-  </si>
-  <si>
-    <t>130645688</t>
-  </si>
-  <si>
-    <t>135850603</t>
-  </si>
-  <si>
-    <t>135711526</t>
-  </si>
-  <si>
-    <t>135912334</t>
-  </si>
-  <si>
-    <t>130799513</t>
-  </si>
-  <si>
-    <t>130780269</t>
-  </si>
-  <si>
-    <t>135693201</t>
-  </si>
-  <si>
-    <t>130739672</t>
-  </si>
-  <si>
-    <t>135823918</t>
-  </si>
-  <si>
-    <t>130897315</t>
-  </si>
-  <si>
-    <t>135822252</t>
-  </si>
-  <si>
-    <t>130690970</t>
-  </si>
-  <si>
-    <t>135774607</t>
-  </si>
-  <si>
-    <t>135850368</t>
-  </si>
-  <si>
-    <t>135645356</t>
-  </si>
-  <si>
-    <t>130806990</t>
-  </si>
-  <si>
-    <t>135894726</t>
-  </si>
-  <si>
-    <t>135528159</t>
-  </si>
-  <si>
-    <t>130793075</t>
-  </si>
-  <si>
-    <t>130658288</t>
-  </si>
-  <si>
-    <t>135627178</t>
-  </si>
-  <si>
-    <t>130777681</t>
-  </si>
-  <si>
-    <t>135508852</t>
-  </si>
-  <si>
-    <t>130656241</t>
-  </si>
-  <si>
-    <t>135812151</t>
-  </si>
-  <si>
-    <t>Allianz - Cancelamento 18.12.2025</t>
+    <t>141129589</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 01.10.2026</t>
+  </si>
+  <si>
+    <t>135170429</t>
+  </si>
+  <si>
+    <t>134971992</t>
+  </si>
+  <si>
+    <t>134756595</t>
+  </si>
+  <si>
+    <t>141050953</t>
+  </si>
+  <si>
+    <t>140878780</t>
+  </si>
+  <si>
+    <t>140901825</t>
+  </si>
+  <si>
+    <t>135120994</t>
+  </si>
+  <si>
+    <t>134878969</t>
+  </si>
+  <si>
+    <t>141040053</t>
+  </si>
+  <si>
+    <t>137863088</t>
+  </si>
+  <si>
+    <t>134795562</t>
+  </si>
+  <si>
+    <t>141051314</t>
+  </si>
+  <si>
+    <t>141129331</t>
+  </si>
+  <si>
+    <t>140830669</t>
+  </si>
+  <si>
+    <t>141103734</t>
+  </si>
+  <si>
+    <t>140878794</t>
+  </si>
+  <si>
+    <t>141080420</t>
+  </si>
+  <si>
+    <t>135099407</t>
+  </si>
+  <si>
+    <t>134829861</t>
+  </si>
+  <si>
+    <t>140989862</t>
+  </si>
+  <si>
+    <t>134847914</t>
+  </si>
+  <si>
+    <t>141112150</t>
+  </si>
+  <si>
+    <t>141175679</t>
+  </si>
+  <si>
+    <t>140830333</t>
+  </si>
+  <si>
+    <t>141088439</t>
+  </si>
+  <si>
+    <t>141011919</t>
+  </si>
+  <si>
+    <t>135053307</t>
+  </si>
+  <si>
+    <t>135179201</t>
+  </si>
+  <si>
+    <t>134941391</t>
+  </si>
+  <si>
+    <t>141137540</t>
+  </si>
+  <si>
+    <t>135162802</t>
+  </si>
+  <si>
+    <t>141175274</t>
+  </si>
+  <si>
+    <t>141083927</t>
+  </si>
+  <si>
+    <t>135163262</t>
+  </si>
+  <si>
+    <t>140663609</t>
+  </si>
+  <si>
+    <t>135071982</t>
+  </si>
+  <si>
+    <t>138494706</t>
+  </si>
+  <si>
+    <t>134998978</t>
+  </si>
+  <si>
+    <t>135017773</t>
+  </si>
+  <si>
+    <t>135180595</t>
+  </si>
+  <si>
+    <t>134990449</t>
+  </si>
+  <si>
+    <t>135514653</t>
+  </si>
+  <si>
+    <t>140774841</t>
+  </si>
+  <si>
+    <t>134897260</t>
+  </si>
+  <si>
+    <t>135069168</t>
+  </si>
+  <si>
+    <t>141103741</t>
+  </si>
+  <si>
+    <t>135304687</t>
+  </si>
+  <si>
+    <t>140902547</t>
+  </si>
+  <si>
+    <t>135127445</t>
+  </si>
+  <si>
+    <t>141129918</t>
+  </si>
+  <si>
+    <t>134794549</t>
+  </si>
+  <si>
+    <t>134835865</t>
+  </si>
+  <si>
+    <t>135034531</t>
+  </si>
+  <si>
+    <t>135072557</t>
+  </si>
+  <si>
+    <t>141056765</t>
+  </si>
+  <si>
+    <t>140926478</t>
+  </si>
+  <si>
+    <t>141052226</t>
+  </si>
+  <si>
+    <t>137480877</t>
+  </si>
+  <si>
+    <t>141041914</t>
+  </si>
+  <si>
+    <t>141111691</t>
+  </si>
+  <si>
+    <t>140642994</t>
+  </si>
+  <si>
+    <t>140922936</t>
+  </si>
+  <si>
+    <t>140674856</t>
+  </si>
+  <si>
+    <t>Allianz - Cancelamento 01.10.2026</t>
   </si>
 </sst>
 </file>
@@ -600,7 +645,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -632,7 +677,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -641,7 +686,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -650,7 +695,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
@@ -659,7 +704,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -668,7 +713,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -677,7 +722,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -686,7 +731,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
@@ -695,7 +740,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -704,7 +749,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
@@ -713,7 +758,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -731,7 +776,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -749,7 +794,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -767,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -785,7 +830,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -803,7 +848,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -821,7 +866,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -839,7 +884,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -857,7 +902,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -875,7 +920,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -893,7 +938,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -911,7 +956,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -929,7 +974,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -947,7 +992,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -965,7 +1010,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -983,7 +1028,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1001,7 +1046,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1019,7 +1064,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1037,7 +1082,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1055,7 +1100,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1073,7 +1118,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1091,7 +1136,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1109,7 +1154,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1127,7 +1172,7 @@
         <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1145,7 +1190,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1163,7 +1208,7 @@
         <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1181,7 +1226,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1199,7 +1244,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1217,7 +1262,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1235,7 +1280,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1253,7 +1298,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1271,7 +1316,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1289,7 +1334,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1307,7 +1352,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1325,7 +1370,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1343,7 +1388,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1361,7 +1406,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1379,11 +1424,12 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F43"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
@@ -1396,11 +1442,12 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F44"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
@@ -1413,11 +1460,12 @@
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F45"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
@@ -1430,7 +1478,7 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1447,7 +1495,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1464,7 +1512,7 @@
         <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1481,7 +1529,7 @@
         <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1498,9 +1546,264 @@
         <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1518,31 +1821,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>